--- a/artfynd/A 13423-2026 artfynd.xlsx
+++ b/artfynd/A 13423-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY100"/>
+  <dimension ref="A1:AY99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -996,48 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132623269</v>
+        <v>132623279</v>
       </c>
       <c r="B5" t="n">
-        <v>80424</v>
+        <v>97971</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>672834</v>
+        <v>672637</v>
       </c>
       <c r="R5" t="n">
-        <v>6981352</v>
+        <v>6981289</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1069,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1079,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,24 +1085,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1115,17 +1096,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132623279</v>
+        <v>132623293</v>
       </c>
       <c r="B6" t="n">
-        <v>97971</v>
+        <v>101312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,34 +1114,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>672637</v>
+        <v>672629</v>
       </c>
       <c r="R6" t="n">
-        <v>6981289</v>
+        <v>6981435</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1192,7 +1181,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1191,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1211,6 +1200,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1229,7 +1219,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132623293</v>
+        <v>132623296</v>
       </c>
       <c r="B7" t="n">
         <v>101312</v>
@@ -1272,13 +1262,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>672629</v>
+        <v>672649</v>
       </c>
       <c r="R7" t="n">
-        <v>6981435</v>
+        <v>6981516</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1307,7 +1297,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1317,7 +1307,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,42 +1335,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132623296</v>
+        <v>132617572</v>
       </c>
       <c r="B8" t="n">
-        <v>101312</v>
+        <v>57946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1388,13 +1378,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>672649</v>
+        <v>672701</v>
       </c>
       <c r="R8" t="n">
-        <v>6981516</v>
+        <v>6981350</v>
       </c>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1423,7 +1413,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1433,7 +1423,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,29 +1432,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132617572</v>
+        <v>132617551</v>
       </c>
       <c r="B9" t="n">
-        <v>57946</v>
+        <v>91898</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,42 +1461,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>672701</v>
+        <v>672976</v>
       </c>
       <c r="R9" t="n">
-        <v>6981350</v>
+        <v>6981217</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1539,7 +1520,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1530,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,32 +1557,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132617551</v>
+        <v>132623301</v>
       </c>
       <c r="B10" t="n">
-        <v>91898</v>
+        <v>97971</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,13 +1592,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672976</v>
+        <v>672767</v>
       </c>
       <c r="R10" t="n">
-        <v>6981217</v>
+        <v>6981492</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,7 +1627,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1637,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,22 +1652,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132623301</v>
+        <v>132623282</v>
       </c>
       <c r="B11" t="n">
-        <v>97971</v>
+        <v>101312</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,34 +1675,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672767</v>
+        <v>672633</v>
       </c>
       <c r="R11" t="n">
-        <v>6981492</v>
+        <v>6981324</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1753,7 +1742,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1752,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1772,6 +1761,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1790,42 +1780,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132623282</v>
+        <v>132617550</v>
       </c>
       <c r="B12" t="n">
-        <v>101312</v>
+        <v>57946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1833,13 +1823,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672633</v>
+        <v>672983</v>
       </c>
       <c r="R12" t="n">
-        <v>6981324</v>
+        <v>6981247</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1868,7 +1858,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1878,7 +1868,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,29 +1877,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132617550</v>
+        <v>132617605</v>
       </c>
       <c r="B13" t="n">
-        <v>57946</v>
+        <v>57949</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1917,16 +1906,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1934,25 +1923,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672983</v>
+        <v>672801</v>
       </c>
       <c r="R13" t="n">
-        <v>6981247</v>
+        <v>6981249</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -1984,7 +1981,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1994,7 +1991,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Två födosökande individer varav en hona</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2021,61 +2023,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132617605</v>
+        <v>132617579</v>
       </c>
       <c r="B14" t="n">
-        <v>57949</v>
+        <v>91861</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672801</v>
+        <v>672651</v>
       </c>
       <c r="R14" t="n">
-        <v>6981249</v>
+        <v>6981280</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2107,7 +2093,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2117,12 +2103,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Två födosökande individer varav en hona</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2149,32 +2130,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132617579</v>
+        <v>132617554</v>
       </c>
       <c r="B15" t="n">
-        <v>91861</v>
+        <v>91898</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2184,10 +2165,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672651</v>
+        <v>672912</v>
       </c>
       <c r="R15" t="n">
-        <v>6981280</v>
+        <v>6981315</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2219,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2229,7 +2210,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,10 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132617554</v>
+        <v>132617571</v>
       </c>
       <c r="B16" t="n">
-        <v>91898</v>
+        <v>57949</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2267,37 +2248,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672912</v>
+        <v>672713</v>
       </c>
       <c r="R16" t="n">
-        <v>6981315</v>
+        <v>6981357</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2326,7 +2315,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2336,7 +2325,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2363,10 +2357,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132617571</v>
+        <v>132617590</v>
       </c>
       <c r="B17" t="n">
-        <v>57949</v>
+        <v>91898</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,45 +2368,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672713</v>
+        <v>672706</v>
       </c>
       <c r="R17" t="n">
-        <v>6981357</v>
+        <v>6981525</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2441,7 +2427,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2451,12 +2437,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2483,32 +2464,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132617590</v>
+        <v>132617581</v>
       </c>
       <c r="B18" t="n">
-        <v>91898</v>
+        <v>91861</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2518,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672706</v>
+        <v>672612</v>
       </c>
       <c r="R18" t="n">
-        <v>6981525</v>
+        <v>6981244</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2553,7 +2534,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2563,7 +2544,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2590,10 +2571,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132617581</v>
+        <v>132623302</v>
       </c>
       <c r="B19" t="n">
-        <v>91861</v>
+        <v>101312</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,37 +2582,45 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672612</v>
+        <v>672746</v>
       </c>
       <c r="R19" t="n">
-        <v>6981244</v>
+        <v>6981560</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2660,7 +2649,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2670,7 +2659,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2679,25 +2668,26 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132623302</v>
+        <v>132623268</v>
       </c>
       <c r="B20" t="n">
         <v>101312</v>
@@ -2740,13 +2730,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>672746</v>
+        <v>672837</v>
       </c>
       <c r="R20" t="n">
-        <v>6981560</v>
+        <v>6981360</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2775,7 +2765,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2785,7 +2775,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132623268</v>
+        <v>132617548</v>
       </c>
       <c r="B21" t="n">
-        <v>101312</v>
+        <v>91861</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2824,45 +2814,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>672837</v>
+        <v>672935</v>
       </c>
       <c r="R21" t="n">
-        <v>6981360</v>
+        <v>6981231</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2891,7 +2873,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2901,7 +2883,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2910,26 +2892,25 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132617548</v>
+        <v>132617588</v>
       </c>
       <c r="B22" t="n">
         <v>91861</v>
@@ -2964,13 +2945,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>672935</v>
+        <v>672671</v>
       </c>
       <c r="R22" t="n">
-        <v>6981231</v>
+        <v>6981418</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2999,7 +2980,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3009,7 +2990,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3036,7 +3017,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132617588</v>
+        <v>132617593</v>
       </c>
       <c r="B23" t="n">
         <v>91861</v>
@@ -3071,10 +3052,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672671</v>
+        <v>672724</v>
       </c>
       <c r="R23" t="n">
-        <v>6981418</v>
+        <v>6981448</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3106,7 +3087,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3116,7 +3097,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3143,10 +3124,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132617593</v>
+        <v>132617601</v>
       </c>
       <c r="B24" t="n">
-        <v>91861</v>
+        <v>80384</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3154,37 +3135,40 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>229497</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>672724</v>
+        <v>672548</v>
       </c>
       <c r="R24" t="n">
-        <v>6981448</v>
+        <v>6981599</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3213,7 +3197,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3223,7 +3207,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3232,8 +3216,24 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3250,10 +3250,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132617601</v>
+        <v>132617600</v>
       </c>
       <c r="B25" t="n">
-        <v>80384</v>
+        <v>101312</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3261,37 +3261,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>672548</v>
+        <v>672651</v>
       </c>
       <c r="R25" t="n">
-        <v>6981599</v>
+        <v>6981546</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3323,7 +3320,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3333,7 +3330,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3342,24 +3339,8 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3376,7 +3357,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132617600</v>
+        <v>132623295</v>
       </c>
       <c r="B26" t="n">
         <v>101312</v>
@@ -3405,19 +3386,27 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>672651</v>
+        <v>672594</v>
       </c>
       <c r="R26" t="n">
-        <v>6981546</v>
+        <v>6981486</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3446,7 +3435,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3456,7 +3445,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3465,25 +3454,26 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132623295</v>
+        <v>132623272</v>
       </c>
       <c r="B27" t="n">
         <v>101312</v>
@@ -3526,13 +3516,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>672594</v>
+        <v>672787</v>
       </c>
       <c r="R27" t="n">
-        <v>6981486</v>
+        <v>6981316</v>
       </c>
       <c r="S27" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3561,7 +3551,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3571,7 +3561,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3599,10 +3589,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132623272</v>
+        <v>132623266</v>
       </c>
       <c r="B28" t="n">
-        <v>101312</v>
+        <v>97965</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3610,45 +3600,33 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>221944</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>672787</v>
+        <v>672878</v>
       </c>
       <c r="R28" t="n">
-        <v>6981316</v>
+        <v>6981334</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3677,7 +3655,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3687,7 +3665,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3708,51 +3686,75 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132623266</v>
+        <v>132617604</v>
       </c>
       <c r="B29" t="n">
-        <v>97965</v>
+        <v>57949</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221944</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672878</v>
+        <v>672698</v>
       </c>
       <c r="R29" t="n">
-        <v>6981334</v>
+        <v>6981511</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3781,7 +3783,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3791,7 +3793,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3800,84 +3802,63 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132617604</v>
+        <v>132617568</v>
       </c>
       <c r="B30" t="n">
-        <v>57949</v>
+        <v>97971</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672698</v>
+        <v>672748</v>
       </c>
       <c r="R30" t="n">
-        <v>6981511</v>
+        <v>6981368</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3909,7 +3890,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3919,7 +3900,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3946,32 +3927,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132617568</v>
+        <v>132617580</v>
       </c>
       <c r="B31" t="n">
-        <v>97971</v>
+        <v>91898</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3981,10 +3962,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>672748</v>
+        <v>672623</v>
       </c>
       <c r="R31" t="n">
-        <v>6981368</v>
+        <v>6981252</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -4016,7 +3997,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4026,7 +4007,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4053,32 +4034,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132617580</v>
+        <v>132623278</v>
       </c>
       <c r="B32" t="n">
-        <v>91898</v>
+        <v>97971</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4088,13 +4069,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>672623</v>
+        <v>672669</v>
       </c>
       <c r="R32" t="n">
-        <v>6981252</v>
+        <v>6981294</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4123,7 +4104,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4133,7 +4114,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4148,22 +4129,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132623278</v>
+        <v>132623274</v>
       </c>
       <c r="B33" t="n">
-        <v>97971</v>
+        <v>101312</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4171,37 +4152,45 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>672669</v>
+        <v>672744</v>
       </c>
       <c r="R33" t="n">
-        <v>6981294</v>
+        <v>6981271</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4230,7 +4219,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4240,7 +4229,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4249,6 +4238,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4267,10 +4257,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132623274</v>
+        <v>132617596</v>
       </c>
       <c r="B34" t="n">
-        <v>101312</v>
+        <v>97971</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4278,45 +4268,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>672744</v>
+        <v>672810</v>
       </c>
       <c r="R34" t="n">
-        <v>6981271</v>
+        <v>6981546</v>
       </c>
       <c r="S34" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4345,7 +4327,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4355,7 +4337,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4364,64 +4346,71 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132617596</v>
+        <v>132617582</v>
       </c>
       <c r="B35" t="n">
-        <v>97971</v>
+        <v>57946</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>672810</v>
+        <v>672612</v>
       </c>
       <c r="R35" t="n">
-        <v>6981546</v>
+        <v>6981238</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -4453,7 +4442,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4463,7 +4452,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4490,53 +4479,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132617582</v>
+        <v>132617586</v>
       </c>
       <c r="B36" t="n">
-        <v>57946</v>
+        <v>91861</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>672612</v>
+        <v>672660</v>
       </c>
       <c r="R36" t="n">
-        <v>6981238</v>
+        <v>6981395</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4568,7 +4549,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4578,7 +4559,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4605,10 +4586,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132617586</v>
+        <v>132623285</v>
       </c>
       <c r="B37" t="n">
-        <v>91861</v>
+        <v>101312</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4616,37 +4597,45 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>672660</v>
+        <v>672638</v>
       </c>
       <c r="R37" t="n">
-        <v>6981395</v>
+        <v>6981364</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4675,7 +4664,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4685,7 +4674,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4694,28 +4683,29 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132623285</v>
+        <v>132623290</v>
       </c>
       <c r="B38" t="n">
-        <v>101312</v>
+        <v>97971</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4723,45 +4713,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672638</v>
+        <v>672621</v>
       </c>
       <c r="R38" t="n">
-        <v>6981364</v>
+        <v>6981383</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4790,7 +4772,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4800,7 +4782,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4809,7 +4791,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4828,10 +4809,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132623290</v>
+        <v>132617557</v>
       </c>
       <c r="B39" t="n">
-        <v>97971</v>
+        <v>80384</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4839,37 +4820,40 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>229497</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>672621</v>
+        <v>672878</v>
       </c>
       <c r="R39" t="n">
-        <v>6981383</v>
+        <v>6981324</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4898,7 +4882,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4908,7 +4892,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4917,66 +4901,79 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132617557</v>
+        <v>132617564</v>
       </c>
       <c r="B40" t="n">
-        <v>80384</v>
+        <v>80424</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672878</v>
+        <v>672831</v>
       </c>
       <c r="R40" t="n">
-        <v>6981324</v>
+        <v>6981363</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -5008,7 +5005,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5018,7 +5015,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5027,24 +5024,8 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5061,10 +5042,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132617564</v>
+        <v>132617599</v>
       </c>
       <c r="B41" t="n">
-        <v>80424</v>
+        <v>79319</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5072,21 +5053,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5096,10 +5077,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>672831</v>
+        <v>672664</v>
       </c>
       <c r="R41" t="n">
-        <v>6981363</v>
+        <v>6981552</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -5131,7 +5112,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5141,7 +5122,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5168,32 +5149,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132617599</v>
+        <v>132617592</v>
       </c>
       <c r="B42" t="n">
-        <v>79319</v>
+        <v>80384</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5203,10 +5184,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>672664</v>
+        <v>672709</v>
       </c>
       <c r="R42" t="n">
-        <v>6981552</v>
+        <v>6981488</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -5238,7 +5219,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5248,7 +5229,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5275,42 +5256,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132623256</v>
+        <v>132617607</v>
       </c>
       <c r="B43" t="n">
-        <v>101312</v>
+        <v>79319</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5318,13 +5294,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672930</v>
+        <v>672712</v>
       </c>
       <c r="R43" t="n">
-        <v>6981133</v>
+        <v>6981164</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5353,7 +5329,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5363,7 +5339,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5376,47 +5352,62 @@
       <c r="AG43" t="b">
         <v>0</v>
       </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132617592</v>
+        <v>132617558</v>
       </c>
       <c r="B44" t="n">
-        <v>80384</v>
+        <v>80297</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229497</v>
+        <v>392</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5426,13 +5417,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672709</v>
+        <v>672873</v>
       </c>
       <c r="R44" t="n">
-        <v>6981488</v>
+        <v>6981339</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5461,7 +5452,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5471,7 +5462,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5498,37 +5489,42 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132617607</v>
+        <v>132623256</v>
       </c>
       <c r="B45" t="n">
-        <v>79319</v>
+        <v>101312</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5536,13 +5532,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672712</v>
+        <v>672930</v>
       </c>
       <c r="R45" t="n">
-        <v>6981164</v>
+        <v>6981133</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5571,7 +5567,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5581,7 +5577,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5594,78 +5590,71 @@
       <c r="AG45" t="b">
         <v>0</v>
       </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132617558</v>
+        <v>132623254</v>
       </c>
       <c r="B46" t="n">
-        <v>80297</v>
+        <v>101312</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>392</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>672873</v>
+        <v>672976</v>
       </c>
       <c r="R46" t="n">
-        <v>6981339</v>
+        <v>6981122</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5694,7 +5683,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5704,7 +5693,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5713,25 +5702,26 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132623254</v>
+        <v>132623294</v>
       </c>
       <c r="B47" t="n">
         <v>101312</v>
@@ -5774,10 +5764,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>672976</v>
+        <v>672601</v>
       </c>
       <c r="R47" t="n">
-        <v>6981122</v>
+        <v>6981439</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5809,7 +5799,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5819,7 +5809,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5847,7 +5837,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132623294</v>
+        <v>132623300</v>
       </c>
       <c r="B48" t="n">
         <v>101312</v>
@@ -5890,13 +5880,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>672601</v>
+        <v>672758</v>
       </c>
       <c r="R48" t="n">
-        <v>6981439</v>
+        <v>6981513</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5925,7 +5915,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5935,7 +5925,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5963,7 +5953,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132623300</v>
+        <v>132617546</v>
       </c>
       <c r="B49" t="n">
         <v>101312</v>
@@ -5992,27 +5982,19 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672758</v>
+        <v>672949</v>
       </c>
       <c r="R49" t="n">
-        <v>6981513</v>
+        <v>6981130</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6041,7 +6023,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6051,7 +6033,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6060,64 +6042,71 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132617546</v>
+        <v>132617576</v>
       </c>
       <c r="B50" t="n">
-        <v>101312</v>
+        <v>57949</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>672949</v>
+        <v>672684</v>
       </c>
       <c r="R50" t="n">
-        <v>6981130</v>
+        <v>6981289</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -6149,7 +6138,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6159,7 +6148,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6186,10 +6180,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132617576</v>
+        <v>132617567</v>
       </c>
       <c r="B51" t="n">
-        <v>57949</v>
+        <v>80424</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6197,31 +6191,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6229,13 +6218,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672684</v>
+        <v>672776</v>
       </c>
       <c r="R51" t="n">
-        <v>6981289</v>
+        <v>6981332</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6264,7 +6253,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6274,12 +6263,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6288,8 +6272,24 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6306,37 +6306,42 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132617567</v>
+        <v>132623292</v>
       </c>
       <c r="B52" t="n">
-        <v>80424</v>
+        <v>101312</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6344,13 +6349,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672776</v>
+        <v>672655</v>
       </c>
       <c r="R52" t="n">
-        <v>6981332</v>
+        <v>6981418</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6379,7 +6384,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6389,7 +6394,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6402,71 +6407,60 @@
       <c r="AG52" t="b">
         <v>0</v>
       </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132623292</v>
+        <v>132617589</v>
       </c>
       <c r="B53" t="n">
-        <v>101312</v>
+        <v>99106</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
@@ -6475,13 +6469,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>672655</v>
+        <v>672627</v>
       </c>
       <c r="R53" t="n">
-        <v>6981418</v>
+        <v>6981425</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6510,7 +6504,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6520,7 +6514,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6536,69 +6530,77 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132617589</v>
+        <v>132617603</v>
       </c>
       <c r="B54" t="n">
-        <v>99106</v>
+        <v>57949</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672627</v>
+        <v>672617</v>
       </c>
       <c r="R54" t="n">
-        <v>6981425</v>
+        <v>6981488</v>
       </c>
       <c r="S54" t="n">
         <v>2</v>
@@ -6630,7 +6632,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6640,7 +6642,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6649,7 +6651,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6668,10 +6669,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132617603</v>
+        <v>132617595</v>
       </c>
       <c r="B55" t="n">
-        <v>57949</v>
+        <v>79319</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6679,57 +6680,44 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672617</v>
+        <v>672745</v>
       </c>
       <c r="R55" t="n">
-        <v>6981488</v>
+        <v>6981544</v>
       </c>
       <c r="S55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6758,7 +6746,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6768,7 +6756,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6777,6 +6765,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6795,41 +6784,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132617595</v>
+        <v>132617566</v>
       </c>
       <c r="B56" t="n">
-        <v>79319</v>
+        <v>80384</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6837,13 +6822,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>672745</v>
+        <v>672774</v>
       </c>
       <c r="R56" t="n">
-        <v>6981544</v>
+        <v>6981334</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6872,7 +6857,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6882,7 +6867,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6894,6 +6879,21 @@
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -6910,10 +6910,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132617566</v>
+        <v>132623265</v>
       </c>
       <c r="B57" t="n">
-        <v>80384</v>
+        <v>101312</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6921,26 +6921,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6948,13 +6953,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>672774</v>
+        <v>672872</v>
       </c>
       <c r="R57" t="n">
-        <v>6981334</v>
+        <v>6981332</v>
       </c>
       <c r="S57" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6983,7 +6988,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6993,7 +6998,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7006,72 +7011,52 @@
       <c r="AG57" t="b">
         <v>0</v>
       </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132623265</v>
+        <v>132623271</v>
       </c>
       <c r="B58" t="n">
-        <v>101312</v>
+        <v>80424</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7079,13 +7064,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>672872</v>
+        <v>672780</v>
       </c>
       <c r="R58" t="n">
-        <v>6981332</v>
+        <v>6981331</v>
       </c>
       <c r="S58" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7114,7 +7099,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7124,7 +7109,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7137,6 +7122,21 @@
       <c r="AG58" t="b">
         <v>0</v>
       </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
@@ -7145,17 +7145,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132623271</v>
+        <v>132623303</v>
       </c>
       <c r="B59" t="n">
-        <v>80424</v>
+        <v>56518</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7163,40 +7163,49 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>672780</v>
+        <v>672560</v>
       </c>
       <c r="R59" t="n">
-        <v>6981331</v>
+        <v>6981577</v>
       </c>
       <c r="S59" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7225,7 +7234,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7235,7 +7244,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7244,24 +7253,8 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7271,64 +7264,60 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132623303</v>
+        <v>132623280</v>
       </c>
       <c r="B60" t="n">
-        <v>56518</v>
+        <v>101312</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>206004</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672560</v>
+        <v>672636</v>
       </c>
       <c r="R60" t="n">
-        <v>6981577</v>
+        <v>6981290</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7360,7 +7349,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7370,7 +7359,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7379,6 +7368,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7397,56 +7387,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132623280</v>
+        <v>132617555</v>
       </c>
       <c r="B61" t="n">
-        <v>101312</v>
+        <v>79319</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672636</v>
+        <v>672921</v>
       </c>
       <c r="R61" t="n">
-        <v>6981290</v>
+        <v>6981328</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7475,7 +7457,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7485,7 +7467,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7494,51 +7476,50 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132617555</v>
+        <v>132617606</v>
       </c>
       <c r="B62" t="n">
-        <v>79319</v>
+        <v>101312</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7548,10 +7529,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>672921</v>
+        <v>672733</v>
       </c>
       <c r="R62" t="n">
-        <v>6981328</v>
+        <v>6981160</v>
       </c>
       <c r="S62" t="n">
         <v>3</v>
@@ -7583,7 +7564,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7593,7 +7574,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7620,10 +7601,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132617606</v>
+        <v>132617602</v>
       </c>
       <c r="B63" t="n">
-        <v>101312</v>
+        <v>97971</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7631,21 +7612,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7655,10 +7636,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672733</v>
+        <v>672593</v>
       </c>
       <c r="R63" t="n">
-        <v>6981160</v>
+        <v>6981519</v>
       </c>
       <c r="S63" t="n">
         <v>3</v>
@@ -7690,7 +7671,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7700,7 +7681,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7727,45 +7708,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132617602</v>
+        <v>132617549</v>
       </c>
       <c r="B64" t="n">
-        <v>97971</v>
+        <v>80424</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>672593</v>
+        <v>672932</v>
       </c>
       <c r="R64" t="n">
-        <v>6981519</v>
+        <v>6981224</v>
       </c>
       <c r="S64" t="n">
         <v>3</v>
@@ -7797,7 +7781,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7807,7 +7791,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7816,8 +7800,24 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7834,7 +7834,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132617549</v>
+        <v>132617591</v>
       </c>
       <c r="B65" t="n">
         <v>80424</v>
@@ -7862,7 +7862,11 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
@@ -7872,10 +7876,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>672932</v>
+        <v>672709</v>
       </c>
       <c r="R65" t="n">
-        <v>6981224</v>
+        <v>6981489</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -7907,7 +7911,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7917,7 +7921,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Växandes på fyra närliggande aspträd</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7960,55 +7969,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132617591</v>
+        <v>132617560</v>
       </c>
       <c r="B66" t="n">
-        <v>80424</v>
+        <v>97971</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>672709</v>
+        <v>672883</v>
       </c>
       <c r="R66" t="n">
-        <v>6981489</v>
+        <v>6981346</v>
       </c>
       <c r="S66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8037,7 +8039,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8047,12 +8049,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Växandes på fyra närliggande aspträd</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8061,24 +8058,8 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8095,10 +8076,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132617560</v>
+        <v>132617574</v>
       </c>
       <c r="B67" t="n">
-        <v>97971</v>
+        <v>91861</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8106,21 +8087,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8130,13 +8111,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>672883</v>
+        <v>672695</v>
       </c>
       <c r="R67" t="n">
-        <v>6981346</v>
+        <v>6981312</v>
       </c>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8165,7 +8146,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8175,7 +8156,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8202,10 +8183,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132617574</v>
+        <v>132617553</v>
       </c>
       <c r="B68" t="n">
-        <v>91861</v>
+        <v>101312</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8213,21 +8194,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8237,10 +8218,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>672695</v>
+        <v>672931</v>
       </c>
       <c r="R68" t="n">
-        <v>6981312</v>
+        <v>6981286</v>
       </c>
       <c r="S68" t="n">
         <v>3</v>
@@ -8272,7 +8253,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8282,7 +8263,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8309,48 +8290,51 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132617553</v>
+        <v>132623267</v>
       </c>
       <c r="B69" t="n">
-        <v>101312</v>
+        <v>79319</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>672931</v>
+        <v>672869</v>
       </c>
       <c r="R69" t="n">
-        <v>6981286</v>
+        <v>6981357</v>
       </c>
       <c r="S69" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8379,7 +8363,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8389,7 +8373,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8398,55 +8382,76 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132623267</v>
+        <v>132623305</v>
       </c>
       <c r="B70" t="n">
-        <v>79319</v>
+        <v>101312</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8454,10 +8459,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>672869</v>
+        <v>672911</v>
       </c>
       <c r="R70" t="n">
-        <v>6981357</v>
+        <v>6981136</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8489,7 +8494,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8499,7 +8504,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8511,21 +8516,6 @@
       <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8542,7 +8532,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132623305</v>
+        <v>132623253</v>
       </c>
       <c r="B71" t="n">
         <v>101312</v>
@@ -8585,10 +8575,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672911</v>
+        <v>672918</v>
       </c>
       <c r="R71" t="n">
-        <v>6981136</v>
+        <v>6980944</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8620,7 +8610,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8630,7 +8620,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8658,42 +8648,37 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132623253</v>
+        <v>132623263</v>
       </c>
       <c r="B72" t="n">
-        <v>101312</v>
+        <v>79319</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8701,13 +8686,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>672918</v>
+        <v>672878</v>
       </c>
       <c r="R72" t="n">
-        <v>6980944</v>
+        <v>6981321</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8736,7 +8721,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8746,7 +8731,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8758,6 +8743,21 @@
       <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8774,10 +8774,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132623263</v>
+        <v>132617598</v>
       </c>
       <c r="B73" t="n">
-        <v>79319</v>
+        <v>92318</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8785,40 +8785,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>672878</v>
+        <v>672763</v>
       </c>
       <c r="R73" t="n">
-        <v>6981321</v>
+        <v>6981545</v>
       </c>
       <c r="S73" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8847,7 +8844,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8857,7 +8854,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8888,22 +8885,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132617598</v>
+        <v>132617556</v>
       </c>
       <c r="B74" t="n">
-        <v>92318</v>
+        <v>91898</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8911,21 +8908,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6040186</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8935,13 +8932,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>672763</v>
+        <v>672881</v>
       </c>
       <c r="R74" t="n">
-        <v>6981545</v>
+        <v>6981314</v>
       </c>
       <c r="S74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8970,7 +8967,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8980,7 +8977,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På stående död gran</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8989,24 +8991,8 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9023,7 +9009,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132617556</v>
+        <v>132617561</v>
       </c>
       <c r="B75" t="n">
         <v>91898</v>
@@ -9058,10 +9044,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672881</v>
+        <v>672878</v>
       </c>
       <c r="R75" t="n">
-        <v>6981314</v>
+        <v>6981375</v>
       </c>
       <c r="S75" t="n">
         <v>3</v>
@@ -9093,7 +9079,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9103,12 +9089,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>09:25</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På stående död gran</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9135,32 +9116,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132617561</v>
+        <v>132617584</v>
       </c>
       <c r="B76" t="n">
-        <v>91898</v>
+        <v>91861</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9170,10 +9151,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>672878</v>
+        <v>672639</v>
       </c>
       <c r="R76" t="n">
-        <v>6981375</v>
+        <v>6981355</v>
       </c>
       <c r="S76" t="n">
         <v>3</v>
@@ -9205,7 +9186,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9215,7 +9196,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9242,10 +9223,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132617584</v>
+        <v>132623275</v>
       </c>
       <c r="B77" t="n">
-        <v>91861</v>
+        <v>101312</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9253,37 +9234,45 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>672639</v>
+        <v>672670</v>
       </c>
       <c r="R77" t="n">
-        <v>6981355</v>
+        <v>6981289</v>
       </c>
       <c r="S77" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9312,7 +9301,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9322,7 +9311,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9331,28 +9320,29 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132623275</v>
+        <v>132623284</v>
       </c>
       <c r="B78" t="n">
-        <v>101312</v>
+        <v>97971</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9360,45 +9350,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>672670</v>
+        <v>672622</v>
       </c>
       <c r="R78" t="n">
-        <v>6981289</v>
+        <v>6981351</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9427,7 +9409,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9437,7 +9419,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9446,7 +9428,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -9465,10 +9446,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132623284</v>
+        <v>132623257</v>
       </c>
       <c r="B79" t="n">
-        <v>97971</v>
+        <v>101312</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9476,37 +9457,45 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>672622</v>
+        <v>672951</v>
       </c>
       <c r="R79" t="n">
-        <v>6981351</v>
+        <v>6981191</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9535,7 +9524,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9545,7 +9534,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9554,6 +9543,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -9572,10 +9562,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132623257</v>
+        <v>132617585</v>
       </c>
       <c r="B80" t="n">
-        <v>101312</v>
+        <v>80384</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9583,31 +9573,26 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -9615,13 +9600,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>672951</v>
+        <v>672635</v>
       </c>
       <c r="R80" t="n">
-        <v>6981191</v>
+        <v>6981376</v>
       </c>
       <c r="S80" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9650,7 +9635,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9660,7 +9645,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9673,25 +9658,40 @@
       <c r="AG80" t="b">
         <v>0</v>
       </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132617585</v>
+        <v>132617575</v>
       </c>
       <c r="B81" t="n">
-        <v>80384</v>
+        <v>57941</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9699,26 +9699,31 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229497</v>
+        <v>100110</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -9726,10 +9731,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>672635</v>
+        <v>672681</v>
       </c>
       <c r="R81" t="n">
-        <v>6981376</v>
+        <v>6981300</v>
       </c>
       <c r="S81" t="n">
         <v>3</v>
@@ -9761,7 +9766,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9771,7 +9776,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Sång i över en minut.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9780,24 +9790,8 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -9814,42 +9808,37 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132617575</v>
+        <v>132617559</v>
       </c>
       <c r="B82" t="n">
-        <v>57941</v>
+        <v>80424</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100110</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9857,13 +9846,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>672681</v>
+        <v>672887</v>
       </c>
       <c r="R82" t="n">
-        <v>6981300</v>
+        <v>6981335</v>
       </c>
       <c r="S82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9892,7 +9881,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9902,12 +9891,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Sång i över en minut.</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9916,8 +9900,24 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9934,10 +9934,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132617559</v>
+        <v>132617552</v>
       </c>
       <c r="B83" t="n">
-        <v>80424</v>
+        <v>57946</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9945,26 +9945,31 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9972,10 +9977,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>672887</v>
+        <v>672968</v>
       </c>
       <c r="R83" t="n">
-        <v>6981335</v>
+        <v>6981202</v>
       </c>
       <c r="S83" t="n">
         <v>1</v>
@@ -10007,7 +10012,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10017,7 +10022,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10026,24 +10031,8 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10060,42 +10049,42 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132617552</v>
+        <v>132623255</v>
       </c>
       <c r="B84" t="n">
-        <v>57946</v>
+        <v>101312</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -10103,13 +10092,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>672968</v>
+        <v>672955</v>
       </c>
       <c r="R84" t="n">
-        <v>6981202</v>
+        <v>6981134</v>
       </c>
       <c r="S84" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10138,7 +10127,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10148,7 +10137,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10157,28 +10146,29 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132623255</v>
+        <v>132617587</v>
       </c>
       <c r="B85" t="n">
-        <v>101312</v>
+        <v>80384</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10186,31 +10176,26 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -10218,13 +10203,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>672955</v>
+        <v>672655</v>
       </c>
       <c r="R85" t="n">
-        <v>6981134</v>
+        <v>6981378</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10253,7 +10238,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10263,7 +10248,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10276,47 +10261,62 @@
       <c r="AG85" t="b">
         <v>0</v>
       </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132617587</v>
+        <v>132617594</v>
       </c>
       <c r="B86" t="n">
-        <v>80384</v>
+        <v>91898</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10329,10 +10329,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>672655</v>
+        <v>672755</v>
       </c>
       <c r="R86" t="n">
-        <v>6981378</v>
+        <v>6981496</v>
       </c>
       <c r="S86" t="n">
         <v>3</v>
@@ -10364,7 +10364,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10386,21 +10386,6 @@
       <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -10417,37 +10402,42 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132617594</v>
+        <v>132623277</v>
       </c>
       <c r="B87" t="n">
-        <v>91898</v>
+        <v>101312</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -10455,13 +10445,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>672755</v>
+        <v>672659</v>
       </c>
       <c r="R87" t="n">
-        <v>6981496</v>
+        <v>6981298</v>
       </c>
       <c r="S87" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10490,7 +10480,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10500,7 +10490,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10516,19 +10506,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132623277</v>
+        <v>132623291</v>
       </c>
       <c r="B88" t="n">
         <v>101312</v>
@@ -10571,13 +10561,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>672659</v>
+        <v>672630</v>
       </c>
       <c r="R88" t="n">
-        <v>6981298</v>
+        <v>6981380</v>
       </c>
       <c r="S88" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10606,7 +10596,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10616,7 +10606,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10644,42 +10634,37 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132623291</v>
+        <v>132623270</v>
       </c>
       <c r="B89" t="n">
-        <v>101312</v>
+        <v>79319</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10687,10 +10672,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>672630</v>
+        <v>672831</v>
       </c>
       <c r="R89" t="n">
-        <v>6981380</v>
+        <v>6981355</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10722,7 +10707,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10732,7 +10717,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10744,6 +10729,21 @@
       <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -10760,37 +10760,42 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132623270</v>
+        <v>132623304</v>
       </c>
       <c r="B90" t="n">
-        <v>79319</v>
+        <v>101312</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -10798,13 +10803,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>672831</v>
+        <v>672732</v>
       </c>
       <c r="R90" t="n">
-        <v>6981355</v>
+        <v>6981161</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10833,7 +10838,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10843,7 +10848,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10855,21 +10860,6 @@
       <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -10886,42 +10876,37 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132623304</v>
+        <v>132617565</v>
       </c>
       <c r="B91" t="n">
-        <v>101312</v>
+        <v>80424</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -10929,13 +10914,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>672732</v>
+        <v>672833</v>
       </c>
       <c r="R91" t="n">
-        <v>6981161</v>
+        <v>6981355</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10964,7 +10949,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10974,7 +10959,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Växandes på björk.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10987,25 +10977,40 @@
       <c r="AG91" t="b">
         <v>0</v>
       </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132617565</v>
+        <v>132617583</v>
       </c>
       <c r="B92" t="n">
-        <v>80424</v>
+        <v>79319</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11013,37 +11018,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>672833</v>
+        <v>672577</v>
       </c>
       <c r="R92" t="n">
-        <v>6981355</v>
+        <v>6981292</v>
       </c>
       <c r="S92" t="n">
         <v>3</v>
@@ -11075,7 +11077,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11085,12 +11087,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:09</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Växandes på björk.</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11099,24 +11096,8 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -11133,32 +11114,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132617583</v>
+        <v>132617562</v>
       </c>
       <c r="B93" t="n">
-        <v>79319</v>
+        <v>91861</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11168,10 +11149,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>672577</v>
+        <v>672869</v>
       </c>
       <c r="R93" t="n">
-        <v>6981292</v>
+        <v>6981366</v>
       </c>
       <c r="S93" t="n">
         <v>3</v>
@@ -11203,7 +11184,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11213,7 +11194,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11240,32 +11221,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132617562</v>
+        <v>132617577</v>
       </c>
       <c r="B94" t="n">
-        <v>91861</v>
+        <v>91898</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11275,10 +11256,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>672869</v>
+        <v>672687</v>
       </c>
       <c r="R94" t="n">
-        <v>6981366</v>
+        <v>6981287</v>
       </c>
       <c r="S94" t="n">
         <v>3</v>
@@ -11310,7 +11291,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11320,7 +11301,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11347,32 +11333,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132617577</v>
+        <v>132617570</v>
       </c>
       <c r="B95" t="n">
-        <v>91898</v>
+        <v>97971</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11382,10 +11368,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>672687</v>
+        <v>672723</v>
       </c>
       <c r="R95" t="n">
-        <v>6981287</v>
+        <v>6981408</v>
       </c>
       <c r="S95" t="n">
         <v>3</v>
@@ -11417,7 +11403,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11427,12 +11413,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>På död stående gran</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11459,10 +11440,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132623258</v>
+        <v>132617563</v>
       </c>
       <c r="B96" t="n">
-        <v>101312</v>
+        <v>97971</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11470,45 +11451,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>672971</v>
+        <v>672858</v>
       </c>
       <c r="R96" t="n">
-        <v>6981202</v>
+        <v>6981365</v>
       </c>
       <c r="S96" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11537,7 +11510,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11547,7 +11520,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11556,26 +11529,25 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132623273</v>
+        <v>132623258</v>
       </c>
       <c r="B97" t="n">
         <v>101312</v>
@@ -11618,13 +11590,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>672774</v>
+        <v>672971</v>
       </c>
       <c r="R97" t="n">
-        <v>6981240</v>
+        <v>6981202</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11653,7 +11625,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11663,7 +11635,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11691,10 +11663,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132623299</v>
+        <v>132623273</v>
       </c>
       <c r="B98" t="n">
-        <v>97971</v>
+        <v>101312</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11702,37 +11674,45 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>672709</v>
+        <v>672774</v>
       </c>
       <c r="R98" t="n">
-        <v>6981494</v>
+        <v>6981240</v>
       </c>
       <c r="S98" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11761,7 +11741,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11771,7 +11751,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11780,6 +11760,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11798,7 +11779,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132617570</v>
+        <v>132623299</v>
       </c>
       <c r="B99" t="n">
         <v>97971</v>
@@ -11833,13 +11814,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>672723</v>
+        <v>672709</v>
       </c>
       <c r="R99" t="n">
-        <v>6981408</v>
+        <v>6981494</v>
       </c>
       <c r="S99" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11868,7 +11849,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11878,7 +11859,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11893,122 +11874,15 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>132617563</v>
-      </c>
-      <c r="B100" t="n">
-        <v>97971</v>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E100" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>Edsätter, Ång</t>
-        </is>
-      </c>
-      <c r="Q100" t="n">
-        <v>672858</v>
-      </c>
-      <c r="R100" t="n">
-        <v>6981365</v>
-      </c>
-      <c r="S100" t="n">
-        <v>3</v>
-      </c>
-      <c r="T100" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W100" t="inlineStr">
-        <is>
-          <t>Nordingrå</t>
-        </is>
-      </c>
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>10:02</t>
-        </is>
-      </c>
-      <c r="AA100" t="inlineStr">
-        <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>10:02</t>
-        </is>
-      </c>
-      <c r="AD100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT100" t="inlineStr"/>
-      <c r="AW100" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY100" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13423-2026 artfynd.xlsx
+++ b/artfynd/A 13423-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132617578</v>
       </c>
       <c r="B2" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132617547</v>
+        <v>132617597</v>
       </c>
       <c r="B3" t="n">
-        <v>79319</v>
+        <v>91871</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672932</v>
+        <v>672762</v>
       </c>
       <c r="R3" t="n">
-        <v>6981174</v>
+        <v>6981535</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132617597</v>
+        <v>132617547</v>
       </c>
       <c r="B4" t="n">
-        <v>91861</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672762</v>
+        <v>672932</v>
       </c>
       <c r="R4" t="n">
-        <v>6981535</v>
+        <v>6981174</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132623279</v>
+        <v>132623293</v>
       </c>
       <c r="B5" t="n">
-        <v>97971</v>
+        <v>101323</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1007,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>672637</v>
+        <v>672629</v>
       </c>
       <c r="R5" t="n">
-        <v>6981289</v>
+        <v>6981435</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1084,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,6 +1093,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1103,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132623293</v>
+        <v>132623296</v>
       </c>
       <c r="B6" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1146,13 +1155,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>672629</v>
+        <v>672649</v>
       </c>
       <c r="R6" t="n">
-        <v>6981435</v>
+        <v>6981516</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1181,7 +1190,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1191,7 +1200,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132623296</v>
+        <v>132623279</v>
       </c>
       <c r="B7" t="n">
-        <v>101312</v>
+        <v>97981</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1230,45 +1239,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>672649</v>
+        <v>672637</v>
       </c>
       <c r="R7" t="n">
-        <v>6981516</v>
+        <v>6981289</v>
       </c>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1297,7 +1298,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1307,7 +1308,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,7 +1317,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132617572</v>
+        <v>132617551</v>
       </c>
       <c r="B8" t="n">
-        <v>57946</v>
+        <v>91908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1346,42 +1346,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>672701</v>
+        <v>672976</v>
       </c>
       <c r="R8" t="n">
-        <v>6981350</v>
+        <v>6981217</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1413,7 +1405,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1423,7 +1415,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132617551</v>
+        <v>132617572</v>
       </c>
       <c r="B9" t="n">
-        <v>91898</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,34 +1453,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>672976</v>
+        <v>672701</v>
       </c>
       <c r="R9" t="n">
-        <v>6981217</v>
+        <v>6981350</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132623301</v>
+        <v>132617579</v>
       </c>
       <c r="B10" t="n">
-        <v>97971</v>
+        <v>91871</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,21 +1568,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1592,13 +1592,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672767</v>
+        <v>672651</v>
       </c>
       <c r="R10" t="n">
-        <v>6981492</v>
+        <v>6981280</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,54 +1652,54 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132623282</v>
+        <v>132617550</v>
       </c>
       <c r="B11" t="n">
-        <v>101312</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1707,13 +1707,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672633</v>
+        <v>672983</v>
       </c>
       <c r="R11" t="n">
-        <v>6981324</v>
+        <v>6981247</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,29 +1761,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132617550</v>
+        <v>132617554</v>
       </c>
       <c r="B12" t="n">
-        <v>57946</v>
+        <v>91908</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,42 +1790,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672983</v>
+        <v>672912</v>
       </c>
       <c r="R12" t="n">
-        <v>6981247</v>
+        <v>6981315</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1858,7 +1849,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1868,7 +1859,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1898,7 +1889,7 @@
         <v>132617605</v>
       </c>
       <c r="B13" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,48 +2014,56 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132617579</v>
+        <v>132617571</v>
       </c>
       <c r="B14" t="n">
-        <v>91861</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672651</v>
+        <v>672713</v>
       </c>
       <c r="R14" t="n">
-        <v>6981280</v>
+        <v>6981357</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2093,7 +2092,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2103,7 +2102,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,32 +2134,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132617554</v>
+        <v>132623301</v>
       </c>
       <c r="B15" t="n">
-        <v>91898</v>
+        <v>97981</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2165,13 +2169,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672912</v>
+        <v>672767</v>
       </c>
       <c r="R15" t="n">
-        <v>6981315</v>
+        <v>6981492</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2200,7 +2204,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,7 +2214,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2225,54 +2229,54 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132617571</v>
+        <v>132623282</v>
       </c>
       <c r="B16" t="n">
-        <v>57949</v>
+        <v>101323</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2280,13 +2284,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672713</v>
+        <v>672633</v>
       </c>
       <c r="R16" t="n">
-        <v>6981357</v>
+        <v>6981324</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2315,7 +2319,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2325,12 +2329,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2339,18 +2338,19 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2360,7 +2360,7 @@
         <v>132617590</v>
       </c>
       <c r="B17" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>132617581</v>
       </c>
       <c r="B18" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2571,10 +2571,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132623302</v>
+        <v>132617593</v>
       </c>
       <c r="B19" t="n">
-        <v>101312</v>
+        <v>91871</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,45 +2582,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672746</v>
+        <v>672724</v>
       </c>
       <c r="R19" t="n">
-        <v>6981560</v>
+        <v>6981448</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2649,7 +2641,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2659,7 +2651,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2668,29 +2660,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132623268</v>
+        <v>132617588</v>
       </c>
       <c r="B20" t="n">
-        <v>101312</v>
+        <v>91871</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2698,45 +2689,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>672837</v>
+        <v>672671</v>
       </c>
       <c r="R20" t="n">
-        <v>6981360</v>
+        <v>6981418</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2765,7 +2748,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2775,7 +2758,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2784,19 +2767,18 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2806,7 +2788,7 @@
         <v>132617548</v>
       </c>
       <c r="B21" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2910,10 +2892,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132617588</v>
+        <v>132617601</v>
       </c>
       <c r="B22" t="n">
-        <v>91861</v>
+        <v>80392</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2921,37 +2903,40 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>672671</v>
+        <v>672548</v>
       </c>
       <c r="R22" t="n">
-        <v>6981418</v>
+        <v>6981599</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2980,7 +2965,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2990,7 +2975,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2999,8 +2984,24 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3017,10 +3018,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132617593</v>
+        <v>132623302</v>
       </c>
       <c r="B23" t="n">
-        <v>91861</v>
+        <v>101323</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3028,37 +3029,45 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672724</v>
+        <v>672746</v>
       </c>
       <c r="R23" t="n">
-        <v>6981448</v>
+        <v>6981560</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3087,7 +3096,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3097,7 +3106,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3106,28 +3115,29 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132617601</v>
+        <v>132617600</v>
       </c>
       <c r="B24" t="n">
-        <v>80384</v>
+        <v>101323</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3135,37 +3145,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>672548</v>
+        <v>672651</v>
       </c>
       <c r="R24" t="n">
-        <v>6981599</v>
+        <v>6981546</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3197,7 +3204,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3207,7 +3214,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3216,24 +3223,8 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3250,10 +3241,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132617600</v>
+        <v>132623268</v>
       </c>
       <c r="B25" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3279,19 +3270,27 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>672651</v>
+        <v>672837</v>
       </c>
       <c r="R25" t="n">
-        <v>6981546</v>
+        <v>6981360</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3320,7 +3319,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3330,7 +3329,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3339,74 +3338,87 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132623295</v>
+        <v>132617604</v>
       </c>
       <c r="B26" t="n">
-        <v>101312</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>672594</v>
+        <v>672698</v>
       </c>
       <c r="R26" t="n">
-        <v>6981486</v>
+        <v>6981511</v>
       </c>
       <c r="S26" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3435,7 +3447,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3445,7 +3457,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3454,19 +3466,18 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3476,7 +3487,7 @@
         <v>132623272</v>
       </c>
       <c r="B27" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,10 +3600,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132623266</v>
+        <v>132623295</v>
       </c>
       <c r="B28" t="n">
-        <v>97965</v>
+        <v>101323</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3600,33 +3611,45 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221944</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>672878</v>
+        <v>672594</v>
       </c>
       <c r="R28" t="n">
-        <v>6981334</v>
+        <v>6981486</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3655,7 +3678,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3665,7 +3688,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3686,72 +3709,52 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132617604</v>
+        <v>132617568</v>
       </c>
       <c r="B29" t="n">
-        <v>57949</v>
+        <v>97981</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672698</v>
+        <v>672748</v>
       </c>
       <c r="R29" t="n">
-        <v>6981511</v>
+        <v>6981368</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3783,7 +3786,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3793,7 +3796,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3820,10 +3823,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132617568</v>
+        <v>132623266</v>
       </c>
       <c r="B30" t="n">
-        <v>97971</v>
+        <v>97975</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3831,23 +3834,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3855,13 +3854,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672748</v>
+        <v>672878</v>
       </c>
       <c r="R30" t="n">
-        <v>6981368</v>
+        <v>6981334</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3890,7 +3889,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3900,7 +3899,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3909,18 +3908,19 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3930,7 +3930,7 @@
         <v>132617580</v>
       </c>
       <c r="B31" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>132623278</v>
       </c>
       <c r="B32" t="n">
-        <v>97971</v>
+        <v>97981</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4141,10 +4141,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132623274</v>
+        <v>132617586</v>
       </c>
       <c r="B33" t="n">
-        <v>101312</v>
+        <v>91871</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4152,45 +4152,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>672744</v>
+        <v>672660</v>
       </c>
       <c r="R33" t="n">
-        <v>6981271</v>
+        <v>6981395</v>
       </c>
       <c r="S33" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4219,7 +4211,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4229,7 +4221,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4238,29 +4230,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132617596</v>
+        <v>132623274</v>
       </c>
       <c r="B34" t="n">
-        <v>97971</v>
+        <v>101323</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4268,37 +4259,45 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>672810</v>
+        <v>672744</v>
       </c>
       <c r="R34" t="n">
-        <v>6981546</v>
+        <v>6981271</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4327,7 +4326,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4337,7 +4336,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4346,18 +4345,19 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4367,7 +4367,7 @@
         <v>132617582</v>
       </c>
       <c r="B35" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4479,10 +4479,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132617586</v>
+        <v>132617596</v>
       </c>
       <c r="B36" t="n">
-        <v>91861</v>
+        <v>97981</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4490,21 +4490,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>672660</v>
+        <v>672810</v>
       </c>
       <c r="R36" t="n">
-        <v>6981395</v>
+        <v>6981546</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4586,56 +4586,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132623285</v>
+        <v>132617599</v>
       </c>
       <c r="B37" t="n">
-        <v>101312</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>672638</v>
+        <v>672664</v>
       </c>
       <c r="R37" t="n">
-        <v>6981364</v>
+        <v>6981552</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4664,7 +4656,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4674,7 +4666,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4683,51 +4675,50 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132623290</v>
+        <v>132617564</v>
       </c>
       <c r="B38" t="n">
-        <v>97971</v>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4737,13 +4728,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672621</v>
+        <v>672831</v>
       </c>
       <c r="R38" t="n">
-        <v>6981383</v>
+        <v>6981363</v>
       </c>
       <c r="S38" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4772,7 +4763,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4782,7 +4773,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4797,12 +4788,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4812,7 +4803,7 @@
         <v>132617557</v>
       </c>
       <c r="B39" t="n">
-        <v>80384</v>
+        <v>80392</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4935,32 +4926,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132617564</v>
+        <v>132623290</v>
       </c>
       <c r="B40" t="n">
-        <v>80424</v>
+        <v>97981</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4970,13 +4961,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672831</v>
+        <v>672621</v>
       </c>
       <c r="R40" t="n">
-        <v>6981363</v>
+        <v>6981383</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5005,7 +4996,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5015,7 +5006,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5030,60 +5021,68 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132617599</v>
+        <v>132623285</v>
       </c>
       <c r="B41" t="n">
-        <v>79319</v>
+        <v>101323</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>672664</v>
+        <v>672638</v>
       </c>
       <c r="R41" t="n">
-        <v>6981552</v>
+        <v>6981364</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5112,7 +5111,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5122,7 +5121,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5131,63 +5130,67 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132617592</v>
+        <v>132617607</v>
       </c>
       <c r="B42" t="n">
-        <v>80384</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>672709</v>
+        <v>672712</v>
       </c>
       <c r="R42" t="n">
-        <v>6981488</v>
+        <v>6981164</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -5219,7 +5222,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5229,7 +5232,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5238,8 +5241,24 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5256,51 +5275,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132617607</v>
+        <v>132617558</v>
       </c>
       <c r="B43" t="n">
-        <v>79319</v>
+        <v>80305</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672712</v>
+        <v>672873</v>
       </c>
       <c r="R43" t="n">
-        <v>6981164</v>
+        <v>6981339</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5329,7 +5345,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5339,7 +5355,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5348,24 +5364,8 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5382,32 +5382,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132617558</v>
+        <v>132617592</v>
       </c>
       <c r="B44" t="n">
-        <v>80297</v>
+        <v>80392</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>392</v>
+        <v>229497</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5417,13 +5417,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672873</v>
+        <v>672709</v>
       </c>
       <c r="R44" t="n">
-        <v>6981339</v>
+        <v>6981488</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5492,7 +5492,7 @@
         <v>132623256</v>
       </c>
       <c r="B45" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5605,42 +5605,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132623254</v>
+        <v>132617567</v>
       </c>
       <c r="B46" t="n">
-        <v>101312</v>
+        <v>80432</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5648,13 +5643,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>672976</v>
+        <v>672776</v>
       </c>
       <c r="R46" t="n">
-        <v>6981122</v>
+        <v>6981332</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5683,7 +5678,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5693,7 +5688,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5706,25 +5701,40 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132623294</v>
+        <v>132623254</v>
       </c>
       <c r="B47" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5764,10 +5774,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>672601</v>
+        <v>672976</v>
       </c>
       <c r="R47" t="n">
-        <v>6981439</v>
+        <v>6981122</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5799,7 +5809,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5809,7 +5819,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5837,10 +5847,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132623300</v>
+        <v>132623294</v>
       </c>
       <c r="B48" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5880,13 +5890,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>672758</v>
+        <v>672601</v>
       </c>
       <c r="R48" t="n">
-        <v>6981513</v>
+        <v>6981439</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5915,7 +5925,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5925,7 +5935,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5953,10 +5963,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132617546</v>
+        <v>132623300</v>
       </c>
       <c r="B49" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5982,19 +5992,27 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672949</v>
+        <v>672758</v>
       </c>
       <c r="R49" t="n">
-        <v>6981130</v>
+        <v>6981513</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6023,7 +6041,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6033,7 +6051,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6042,71 +6060,64 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132617576</v>
+        <v>132617546</v>
       </c>
       <c r="B50" t="n">
-        <v>57949</v>
+        <v>101323</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>672684</v>
+        <v>672949</v>
       </c>
       <c r="R50" t="n">
-        <v>6981289</v>
+        <v>6981130</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -6138,7 +6149,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6148,12 +6159,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6180,10 +6186,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132617567</v>
+        <v>132617576</v>
       </c>
       <c r="B51" t="n">
-        <v>80424</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6191,26 +6197,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6218,13 +6229,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672776</v>
+        <v>672684</v>
       </c>
       <c r="R51" t="n">
-        <v>6981332</v>
+        <v>6981289</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6253,7 +6264,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6263,7 +6274,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6272,24 +6288,8 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6306,41 +6306,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132623292</v>
+        <v>132617589</v>
       </c>
       <c r="B52" t="n">
-        <v>101312</v>
+        <v>99116</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
@@ -6349,13 +6353,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672655</v>
+        <v>672627</v>
       </c>
       <c r="R52" t="n">
-        <v>6981418</v>
+        <v>6981425</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6384,7 +6388,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6394,7 +6398,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6410,58 +6414,49 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132617589</v>
+        <v>132617566</v>
       </c>
       <c r="B53" t="n">
-        <v>99106</v>
+        <v>80392</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6469,10 +6464,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>672627</v>
+        <v>672774</v>
       </c>
       <c r="R53" t="n">
-        <v>6981425</v>
+        <v>6981334</v>
       </c>
       <c r="S53" t="n">
         <v>2</v>
@@ -6504,7 +6499,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6514,7 +6509,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6526,6 +6521,21 @@
       <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6542,68 +6552,56 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132617603</v>
+        <v>132623292</v>
       </c>
       <c r="B54" t="n">
-        <v>57949</v>
+        <v>101323</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672617</v>
+        <v>672655</v>
       </c>
       <c r="R54" t="n">
-        <v>6981488</v>
+        <v>6981418</v>
       </c>
       <c r="S54" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6632,7 +6630,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6642,7 +6640,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6651,18 +6649,19 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6672,7 +6671,7 @@
         <v>132617595</v>
       </c>
       <c r="B55" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6784,48 +6783,65 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132617566</v>
+        <v>132617603</v>
       </c>
       <c r="B56" t="n">
-        <v>80384</v>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>672774</v>
+        <v>672617</v>
       </c>
       <c r="R56" t="n">
-        <v>6981334</v>
+        <v>6981488</v>
       </c>
       <c r="S56" t="n">
         <v>2</v>
@@ -6857,7 +6873,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6867,7 +6883,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6876,24 +6892,8 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -6910,42 +6910,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132623265</v>
+        <v>132623271</v>
       </c>
       <c r="B57" t="n">
-        <v>101312</v>
+        <v>80432</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6953,13 +6948,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>672872</v>
+        <v>672780</v>
       </c>
       <c r="R57" t="n">
-        <v>6981332</v>
+        <v>6981331</v>
       </c>
       <c r="S57" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6988,7 +6983,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6998,7 +6993,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7011,6 +7006,21 @@
       <c r="AG57" t="b">
         <v>0</v>
       </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
@@ -7019,17 +7029,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132623271</v>
+        <v>132617555</v>
       </c>
       <c r="B58" t="n">
-        <v>80424</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7037,40 +7047,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>672780</v>
+        <v>672921</v>
       </c>
       <c r="R58" t="n">
-        <v>6981331</v>
+        <v>6981328</v>
       </c>
       <c r="S58" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7099,7 +7106,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7109,7 +7116,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7118,44 +7125,28 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132623303</v>
+        <v>132617549</v>
       </c>
       <c r="B59" t="n">
-        <v>56518</v>
+        <v>80432</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7163,49 +7154,40 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>672560</v>
+        <v>672932</v>
       </c>
       <c r="R59" t="n">
-        <v>6981577</v>
+        <v>6981224</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7234,7 +7216,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7244,7 +7226,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7253,28 +7235,44 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132623280</v>
+        <v>132617602</v>
       </c>
       <c r="B60" t="n">
-        <v>101312</v>
+        <v>97981</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7282,45 +7280,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672636</v>
+        <v>672593</v>
       </c>
       <c r="R60" t="n">
-        <v>6981290</v>
+        <v>6981519</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7349,7 +7339,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7359,7 +7349,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7368,29 +7358,28 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132617555</v>
+        <v>132623303</v>
       </c>
       <c r="B61" t="n">
-        <v>79319</v>
+        <v>56522</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7398,37 +7387,49 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672921</v>
+        <v>672560</v>
       </c>
       <c r="R61" t="n">
-        <v>6981328</v>
+        <v>6981577</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7457,7 +7458,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7467,7 +7468,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7482,22 +7483,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132617606</v>
+        <v>132623265</v>
       </c>
       <c r="B62" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7523,19 +7524,27 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>672733</v>
+        <v>672872</v>
       </c>
       <c r="R62" t="n">
-        <v>6981160</v>
+        <v>6981332</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7564,7 +7573,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7574,7 +7583,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7583,28 +7592,29 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132617602</v>
+        <v>132623280</v>
       </c>
       <c r="B63" t="n">
-        <v>97971</v>
+        <v>101323</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7612,37 +7622,45 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672593</v>
+        <v>672636</v>
       </c>
       <c r="R63" t="n">
-        <v>6981519</v>
+        <v>6981290</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7671,7 +7689,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7681,7 +7699,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7690,66 +7708,64 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132617549</v>
+        <v>132617606</v>
       </c>
       <c r="B64" t="n">
-        <v>80424</v>
+        <v>101323</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>672932</v>
+        <v>672733</v>
       </c>
       <c r="R64" t="n">
-        <v>6981224</v>
+        <v>6981160</v>
       </c>
       <c r="S64" t="n">
         <v>3</v>
@@ -7781,7 +7797,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7791,7 +7807,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7800,24 +7816,8 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7834,55 +7834,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132617591</v>
+        <v>132617560</v>
       </c>
       <c r="B65" t="n">
-        <v>80424</v>
+        <v>97981</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>672709</v>
+        <v>672883</v>
       </c>
       <c r="R65" t="n">
-        <v>6981489</v>
+        <v>6981346</v>
       </c>
       <c r="S65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7911,7 +7904,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7921,12 +7914,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Växandes på fyra närliggande aspträd</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7935,24 +7923,8 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -7969,10 +7941,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132617560</v>
+        <v>132617574</v>
       </c>
       <c r="B66" t="n">
-        <v>97971</v>
+        <v>91871</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7980,21 +7952,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8004,13 +7976,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>672883</v>
+        <v>672695</v>
       </c>
       <c r="R66" t="n">
-        <v>6981346</v>
+        <v>6981312</v>
       </c>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8039,7 +8011,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8049,7 +8021,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8076,45 +8048,52 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132617574</v>
+        <v>132617591</v>
       </c>
       <c r="B67" t="n">
-        <v>91861</v>
+        <v>80432</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>672695</v>
+        <v>672709</v>
       </c>
       <c r="R67" t="n">
-        <v>6981312</v>
+        <v>6981489</v>
       </c>
       <c r="S67" t="n">
         <v>3</v>
@@ -8146,7 +8125,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8156,7 +8135,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Växandes på fyra närliggande aspträd</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8165,8 +8149,24 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8186,7 +8186,7 @@
         <v>132617553</v>
       </c>
       <c r="B68" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8290,10 +8290,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132623267</v>
+        <v>132617598</v>
       </c>
       <c r="B69" t="n">
-        <v>79319</v>
+        <v>92328</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8301,40 +8301,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>672869</v>
+        <v>672763</v>
       </c>
       <c r="R69" t="n">
-        <v>6981357</v>
+        <v>6981545</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8363,7 +8360,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8373,7 +8370,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8404,22 +8401,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132623305</v>
+        <v>132617584</v>
       </c>
       <c r="B70" t="n">
-        <v>101312</v>
+        <v>91871</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8427,45 +8424,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>672911</v>
+        <v>672639</v>
       </c>
       <c r="R70" t="n">
-        <v>6981136</v>
+        <v>6981355</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8494,7 +8483,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8504,7 +8493,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8513,75 +8502,66 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132623253</v>
+        <v>132617556</v>
       </c>
       <c r="B71" t="n">
-        <v>101312</v>
+        <v>91908</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672918</v>
+        <v>672881</v>
       </c>
       <c r="R71" t="n">
-        <v>6980944</v>
+        <v>6981314</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8610,7 +8590,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8620,7 +8600,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På stående död gran</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8629,29 +8614,28 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132623263</v>
+        <v>132617561</v>
       </c>
       <c r="B72" t="n">
-        <v>79319</v>
+        <v>91908</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8659,27 +8643,24 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
@@ -8689,10 +8670,10 @@
         <v>672878</v>
       </c>
       <c r="R72" t="n">
-        <v>6981321</v>
+        <v>6981375</v>
       </c>
       <c r="S72" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8721,7 +8702,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8731,7 +8712,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8740,44 +8721,28 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132617598</v>
+        <v>132623267</v>
       </c>
       <c r="B73" t="n">
-        <v>92318</v>
+        <v>79327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8785,37 +8750,40 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>672763</v>
+        <v>672869</v>
       </c>
       <c r="R73" t="n">
-        <v>6981545</v>
+        <v>6981357</v>
       </c>
       <c r="S73" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8844,7 +8812,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8854,7 +8822,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8885,22 +8853,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132617556</v>
+        <v>132623263</v>
       </c>
       <c r="B74" t="n">
-        <v>91898</v>
+        <v>79327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8908,37 +8876,40 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>672881</v>
+        <v>672878</v>
       </c>
       <c r="R74" t="n">
-        <v>6981314</v>
+        <v>6981321</v>
       </c>
       <c r="S74" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8967,7 +8938,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8977,12 +8948,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:25</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På stående död gran</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8991,66 +8957,90 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132617561</v>
+        <v>132623305</v>
       </c>
       <c r="B75" t="n">
-        <v>91898</v>
+        <v>101323</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672878</v>
+        <v>672911</v>
       </c>
       <c r="R75" t="n">
-        <v>6981375</v>
+        <v>6981136</v>
       </c>
       <c r="S75" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9079,7 +9069,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9089,7 +9079,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9098,28 +9088,29 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132617584</v>
+        <v>132623253</v>
       </c>
       <c r="B76" t="n">
-        <v>91861</v>
+        <v>101323</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9127,37 +9118,45 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>672639</v>
+        <v>672918</v>
       </c>
       <c r="R76" t="n">
-        <v>6981355</v>
+        <v>6980944</v>
       </c>
       <c r="S76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9186,7 +9185,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9196,7 +9195,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9205,60 +9204,56 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132623275</v>
+        <v>132617559</v>
       </c>
       <c r="B77" t="n">
-        <v>101312</v>
+        <v>80432</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9266,13 +9261,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>672670</v>
+        <v>672887</v>
       </c>
       <c r="R77" t="n">
-        <v>6981289</v>
+        <v>6981335</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9301,7 +9296,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9311,7 +9306,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9324,25 +9319,40 @@
       <c r="AG77" t="b">
         <v>0</v>
       </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132623284</v>
+        <v>132617585</v>
       </c>
       <c r="B78" t="n">
-        <v>97971</v>
+        <v>80392</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9350,37 +9360,40 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221945</v>
+        <v>229497</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>672622</v>
+        <v>672635</v>
       </c>
       <c r="R78" t="n">
-        <v>6981351</v>
+        <v>6981376</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9409,7 +9422,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9419,7 +9432,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9428,28 +9441,44 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132623257</v>
+        <v>132623284</v>
       </c>
       <c r="B79" t="n">
-        <v>101312</v>
+        <v>97981</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9457,45 +9486,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>672951</v>
+        <v>672622</v>
       </c>
       <c r="R79" t="n">
-        <v>6981191</v>
+        <v>6981351</v>
       </c>
       <c r="S79" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9524,7 +9545,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9534,7 +9555,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9543,7 +9564,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -9562,10 +9582,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132617585</v>
+        <v>132617575</v>
       </c>
       <c r="B80" t="n">
-        <v>80384</v>
+        <v>57945</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9573,26 +9593,31 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229497</v>
+        <v>100110</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -9600,10 +9625,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>672635</v>
+        <v>672681</v>
       </c>
       <c r="R80" t="n">
-        <v>6981376</v>
+        <v>6981300</v>
       </c>
       <c r="S80" t="n">
         <v>3</v>
@@ -9635,7 +9660,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9645,7 +9670,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Sång i över en minut.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9654,24 +9684,8 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9688,32 +9702,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132617575</v>
+        <v>132617552</v>
       </c>
       <c r="B81" t="n">
-        <v>57941</v>
+        <v>57950</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100110</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9721,7 +9735,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -9731,13 +9745,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>672681</v>
+        <v>672968</v>
       </c>
       <c r="R81" t="n">
-        <v>6981300</v>
+        <v>6981202</v>
       </c>
       <c r="S81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9766,7 +9780,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9776,12 +9790,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Sång i över en minut.</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9808,37 +9817,42 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132617559</v>
+        <v>132623275</v>
       </c>
       <c r="B82" t="n">
-        <v>80424</v>
+        <v>101323</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9846,13 +9860,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>672887</v>
+        <v>672670</v>
       </c>
       <c r="R82" t="n">
-        <v>6981335</v>
+        <v>6981289</v>
       </c>
       <c r="S82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9881,7 +9895,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9891,7 +9905,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9904,72 +9918,57 @@
       <c r="AG82" t="b">
         <v>0</v>
       </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132617552</v>
+        <v>132623257</v>
       </c>
       <c r="B83" t="n">
-        <v>57946</v>
+        <v>101323</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9977,13 +9976,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>672968</v>
+        <v>672951</v>
       </c>
       <c r="R83" t="n">
-        <v>6981202</v>
+        <v>6981191</v>
       </c>
       <c r="S83" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10012,7 +10011,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10022,7 +10021,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10031,60 +10030,56 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132623255</v>
+        <v>132617594</v>
       </c>
       <c r="B84" t="n">
-        <v>101312</v>
+        <v>91908</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -10092,13 +10087,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>672955</v>
+        <v>672755</v>
       </c>
       <c r="R84" t="n">
-        <v>6981134</v>
+        <v>6981496</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10127,7 +10122,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10137,7 +10132,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10153,22 +10148,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132617587</v>
+        <v>132623255</v>
       </c>
       <c r="B85" t="n">
-        <v>80384</v>
+        <v>101323</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10176,26 +10171,31 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -10203,13 +10203,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>672655</v>
+        <v>672955</v>
       </c>
       <c r="R85" t="n">
-        <v>6981378</v>
+        <v>6981134</v>
       </c>
       <c r="S85" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10261,62 +10261,47 @@
       <c r="AG85" t="b">
         <v>0</v>
       </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132617594</v>
+        <v>132617587</v>
       </c>
       <c r="B86" t="n">
-        <v>91898</v>
+        <v>80392</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10329,10 +10314,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>672755</v>
+        <v>672655</v>
       </c>
       <c r="R86" t="n">
-        <v>6981496</v>
+        <v>6981378</v>
       </c>
       <c r="S86" t="n">
         <v>3</v>
@@ -10364,7 +10349,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10374,7 +10359,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10386,6 +10371,21 @@
       <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -10405,7 +10405,7 @@
         <v>132623277</v>
       </c>
       <c r="B87" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10518,10 +10518,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132623291</v>
+        <v>132617562</v>
       </c>
       <c r="B88" t="n">
-        <v>101312</v>
+        <v>91871</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10529,45 +10529,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>672630</v>
+        <v>672869</v>
       </c>
       <c r="R88" t="n">
-        <v>6981380</v>
+        <v>6981366</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10596,7 +10588,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10606,7 +10598,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10615,29 +10607,28 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132623270</v>
+        <v>132617583</v>
       </c>
       <c r="B89" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10663,22 +10654,19 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>672831</v>
+        <v>672577</v>
       </c>
       <c r="R89" t="n">
-        <v>6981355</v>
+        <v>6981292</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10707,7 +10695,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10717,7 +10705,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10726,76 +10714,55 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132623304</v>
+        <v>132623270</v>
       </c>
       <c r="B90" t="n">
-        <v>101312</v>
+        <v>79327</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -10803,13 +10770,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>672732</v>
+        <v>672831</v>
       </c>
       <c r="R90" t="n">
-        <v>6981161</v>
+        <v>6981355</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10838,7 +10805,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10848,7 +10815,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10860,6 +10827,21 @@
       <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -10879,7 +10861,7 @@
         <v>132617565</v>
       </c>
       <c r="B91" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11007,48 +10989,56 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132617583</v>
+        <v>132623291</v>
       </c>
       <c r="B92" t="n">
-        <v>79319</v>
+        <v>101323</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>672577</v>
+        <v>672630</v>
       </c>
       <c r="R92" t="n">
-        <v>6981292</v>
+        <v>6981380</v>
       </c>
       <c r="S92" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11077,7 +11067,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11087,7 +11077,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11096,28 +11086,29 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132617562</v>
+        <v>132623304</v>
       </c>
       <c r="B93" t="n">
-        <v>91861</v>
+        <v>101323</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11125,37 +11116,45 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>672869</v>
+        <v>672732</v>
       </c>
       <c r="R93" t="n">
-        <v>6981366</v>
+        <v>6981161</v>
       </c>
       <c r="S93" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11184,7 +11183,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11194,7 +11193,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11203,18 +11202,19 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -11224,7 +11224,7 @@
         <v>132617577</v>
       </c>
       <c r="B94" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11333,10 +11333,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132617570</v>
+        <v>132623258</v>
       </c>
       <c r="B95" t="n">
-        <v>97971</v>
+        <v>101323</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11344,37 +11344,45 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>672723</v>
+        <v>672971</v>
       </c>
       <c r="R95" t="n">
-        <v>6981408</v>
+        <v>6981202</v>
       </c>
       <c r="S95" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11403,7 +11411,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11413,7 +11421,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11422,28 +11430,29 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132617563</v>
+        <v>132623273</v>
       </c>
       <c r="B96" t="n">
-        <v>97971</v>
+        <v>101323</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11451,37 +11460,45 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>672858</v>
+        <v>672774</v>
       </c>
       <c r="R96" t="n">
-        <v>6981365</v>
+        <v>6981240</v>
       </c>
       <c r="S96" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11510,7 +11527,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11520,7 +11537,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11529,28 +11546,29 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132623258</v>
+        <v>132617563</v>
       </c>
       <c r="B97" t="n">
-        <v>101312</v>
+        <v>97981</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11558,45 +11576,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>672971</v>
+        <v>672858</v>
       </c>
       <c r="R97" t="n">
-        <v>6981202</v>
+        <v>6981365</v>
       </c>
       <c r="S97" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11625,7 +11635,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11635,7 +11645,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11644,29 +11654,28 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132623273</v>
+        <v>132617570</v>
       </c>
       <c r="B98" t="n">
-        <v>101312</v>
+        <v>97981</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11674,45 +11683,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>672774</v>
+        <v>672723</v>
       </c>
       <c r="R98" t="n">
-        <v>6981240</v>
+        <v>6981408</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11741,7 +11742,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11751,7 +11752,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11760,19 +11761,18 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -11782,7 +11782,7 @@
         <v>132623299</v>
       </c>
       <c r="B99" t="n">
-        <v>97971</v>
+        <v>97981</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 13423-2026 artfynd.xlsx
+++ b/artfynd/A 13423-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132617578</v>
       </c>
       <c r="B2" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132617597</v>
+        <v>132617547</v>
       </c>
       <c r="B3" t="n">
-        <v>91871</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672762</v>
+        <v>672932</v>
       </c>
       <c r="R3" t="n">
-        <v>6981535</v>
+        <v>6981174</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132617547</v>
+        <v>132617597</v>
       </c>
       <c r="B4" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672932</v>
+        <v>672762</v>
       </c>
       <c r="R4" t="n">
-        <v>6981174</v>
+        <v>6981535</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,56 +996,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132623293</v>
+        <v>132617551</v>
       </c>
       <c r="B5" t="n">
-        <v>101323</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>672629</v>
+        <v>672976</v>
       </c>
       <c r="R5" t="n">
-        <v>6981435</v>
+        <v>6981217</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,61 +1085,60 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132623296</v>
+        <v>132617572</v>
       </c>
       <c r="B6" t="n">
-        <v>101323</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1155,13 +1146,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>672649</v>
+        <v>672701</v>
       </c>
       <c r="R6" t="n">
-        <v>6981516</v>
+        <v>6981350</v>
       </c>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,7 +1181,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1200,7 +1191,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,19 +1200,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1231,7 +1221,7 @@
         <v>132623279</v>
       </c>
       <c r="B7" t="n">
-        <v>97981</v>
+        <v>97982</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,48 +1325,56 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132617551</v>
+        <v>132623293</v>
       </c>
       <c r="B8" t="n">
-        <v>91908</v>
+        <v>101324</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>672976</v>
+        <v>672629</v>
       </c>
       <c r="R8" t="n">
-        <v>6981217</v>
+        <v>6981435</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1405,7 +1403,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1415,7 +1413,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,60 +1422,61 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132617572</v>
+        <v>132623296</v>
       </c>
       <c r="B9" t="n">
-        <v>57950</v>
+        <v>101324</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1485,13 +1484,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>672701</v>
+        <v>672649</v>
       </c>
       <c r="R9" t="n">
-        <v>6981350</v>
+        <v>6981516</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1520,7 +1519,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1530,7 +1529,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,50 +1538,51 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132617579</v>
+        <v>132617554</v>
       </c>
       <c r="B10" t="n">
-        <v>91871</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672651</v>
+        <v>672912</v>
       </c>
       <c r="R10" t="n">
-        <v>6981280</v>
+        <v>6981315</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132617550</v>
+        <v>132617605</v>
       </c>
       <c r="B11" t="n">
-        <v>57950</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,16 +1675,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1692,25 +1692,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672983</v>
+        <v>672801</v>
       </c>
       <c r="R11" t="n">
-        <v>6981247</v>
+        <v>6981249</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1742,7 +1750,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1752,7 +1760,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Två födosökande individer varav en hona</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1779,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132617554</v>
+        <v>132617571</v>
       </c>
       <c r="B12" t="n">
-        <v>91908</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,37 +1803,45 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672912</v>
+        <v>672713</v>
       </c>
       <c r="R12" t="n">
-        <v>6981315</v>
+        <v>6981357</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1849,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1859,7 +1880,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1886,64 +1912,56 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132617605</v>
+        <v>132623282</v>
       </c>
       <c r="B13" t="n">
-        <v>57953</v>
+        <v>101324</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672801</v>
+        <v>672633</v>
       </c>
       <c r="R13" t="n">
-        <v>6981249</v>
+        <v>6981324</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,7 +1990,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,12 +2000,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Två födosökande individer varav en hona</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1996,74 +2009,67 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132617571</v>
+        <v>132617579</v>
       </c>
       <c r="B14" t="n">
-        <v>57953</v>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672713</v>
+        <v>672651</v>
       </c>
       <c r="R14" t="n">
-        <v>6981357</v>
+        <v>6981280</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2092,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2102,12 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2134,48 +2135,56 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132623301</v>
+        <v>132617550</v>
       </c>
       <c r="B15" t="n">
-        <v>97981</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672767</v>
+        <v>672983</v>
       </c>
       <c r="R15" t="n">
-        <v>6981492</v>
+        <v>6981247</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2204,7 +2213,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2214,7 +2223,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2229,22 +2238,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132623282</v>
+        <v>132623301</v>
       </c>
       <c r="B16" t="n">
-        <v>101323</v>
+        <v>97982</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,42 +2261,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672633</v>
+        <v>672767</v>
       </c>
       <c r="R16" t="n">
-        <v>6981324</v>
+        <v>6981492</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2319,7 +2320,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2329,7 +2330,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,7 +2339,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2360,7 +2360,7 @@
         <v>132617590</v>
       </c>
       <c r="B17" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>132617581</v>
       </c>
       <c r="B18" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2571,10 +2571,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132617593</v>
+        <v>132623302</v>
       </c>
       <c r="B19" t="n">
-        <v>91871</v>
+        <v>101324</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,37 +2582,45 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672724</v>
+        <v>672746</v>
       </c>
       <c r="R19" t="n">
-        <v>6981448</v>
+        <v>6981560</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2641,7 +2649,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2651,7 +2659,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2660,28 +2668,29 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132617588</v>
+        <v>132617600</v>
       </c>
       <c r="B20" t="n">
-        <v>91871</v>
+        <v>101324</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2689,21 +2698,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2713,13 +2722,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>672671</v>
+        <v>672651</v>
       </c>
       <c r="R20" t="n">
-        <v>6981418</v>
+        <v>6981546</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2748,7 +2757,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2758,7 +2767,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2785,10 +2794,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132617548</v>
+        <v>132623268</v>
       </c>
       <c r="B21" t="n">
-        <v>91871</v>
+        <v>101324</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,37 +2805,45 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>672935</v>
+        <v>672837</v>
       </c>
       <c r="R21" t="n">
-        <v>6981231</v>
+        <v>6981360</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2855,7 +2872,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2865,7 +2882,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2874,18 +2891,19 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3018,10 +3036,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132623302</v>
+        <v>132617593</v>
       </c>
       <c r="B23" t="n">
-        <v>101323</v>
+        <v>91872</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3029,45 +3047,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672746</v>
+        <v>672724</v>
       </c>
       <c r="R23" t="n">
-        <v>6981560</v>
+        <v>6981448</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3096,7 +3106,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3106,7 +3116,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3115,29 +3125,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132617600</v>
+        <v>132617588</v>
       </c>
       <c r="B24" t="n">
-        <v>101323</v>
+        <v>91872</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3145,21 +3154,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3169,13 +3178,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>672651</v>
+        <v>672671</v>
       </c>
       <c r="R24" t="n">
-        <v>6981546</v>
+        <v>6981418</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3204,7 +3213,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3214,7 +3223,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3241,10 +3250,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132623268</v>
+        <v>132617548</v>
       </c>
       <c r="B25" t="n">
-        <v>101323</v>
+        <v>91872</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3252,45 +3261,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>672837</v>
+        <v>672935</v>
       </c>
       <c r="R25" t="n">
-        <v>6981360</v>
+        <v>6981231</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3319,7 +3320,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3329,7 +3330,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3338,87 +3339,74 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132617604</v>
+        <v>132623272</v>
       </c>
       <c r="B26" t="n">
-        <v>57953</v>
+        <v>101324</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>672698</v>
+        <v>672787</v>
       </c>
       <c r="R26" t="n">
-        <v>6981511</v>
+        <v>6981316</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3447,7 +3435,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3457,7 +3445,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3466,74 +3454,67 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132623272</v>
+        <v>132617580</v>
       </c>
       <c r="B27" t="n">
-        <v>101323</v>
+        <v>91909</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>672787</v>
+        <v>672623</v>
       </c>
       <c r="R27" t="n">
-        <v>6981316</v>
+        <v>6981252</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3562,7 +3543,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3572,7 +3553,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3581,75 +3562,86 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132623295</v>
+        <v>132617604</v>
       </c>
       <c r="B28" t="n">
-        <v>101323</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>672594</v>
+        <v>672698</v>
       </c>
       <c r="R28" t="n">
-        <v>6981486</v>
+        <v>6981511</v>
       </c>
       <c r="S28" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3678,7 +3670,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3688,7 +3680,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3697,19 +3689,18 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3719,7 +3710,7 @@
         <v>132617568</v>
       </c>
       <c r="B29" t="n">
-        <v>97981</v>
+        <v>97982</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3826,7 +3817,7 @@
         <v>132623266</v>
       </c>
       <c r="B30" t="n">
-        <v>97975</v>
+        <v>97976</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3927,48 +3918,56 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132617580</v>
+        <v>132623295</v>
       </c>
       <c r="B31" t="n">
-        <v>91908</v>
+        <v>101324</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>672623</v>
+        <v>672594</v>
       </c>
       <c r="R31" t="n">
-        <v>6981252</v>
+        <v>6981486</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3997,7 +3996,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4007,7 +4006,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4016,18 +4015,19 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4037,7 +4037,7 @@
         <v>132623278</v>
       </c>
       <c r="B32" t="n">
-        <v>97981</v>
+        <v>97982</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>132617586</v>
       </c>
       <c r="B33" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4248,10 +4248,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132623274</v>
+        <v>132617596</v>
       </c>
       <c r="B34" t="n">
-        <v>101323</v>
+        <v>97982</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4259,45 +4259,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>672744</v>
+        <v>672810</v>
       </c>
       <c r="R34" t="n">
-        <v>6981271</v>
+        <v>6981546</v>
       </c>
       <c r="S34" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4326,7 +4318,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4336,7 +4328,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4345,19 +4337,18 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4479,10 +4470,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132617596</v>
+        <v>132623274</v>
       </c>
       <c r="B36" t="n">
-        <v>97981</v>
+        <v>101324</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4490,37 +4481,45 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>672810</v>
+        <v>672744</v>
       </c>
       <c r="R36" t="n">
-        <v>6981546</v>
+        <v>6981271</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4549,7 +4548,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4559,7 +4558,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4568,50 +4567,51 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132617599</v>
+        <v>132623290</v>
       </c>
       <c r="B37" t="n">
-        <v>79327</v>
+        <v>97982</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4621,13 +4621,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>672664</v>
+        <v>672621</v>
       </c>
       <c r="R37" t="n">
-        <v>6981552</v>
+        <v>6981383</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4681,60 +4681,68 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132617564</v>
+        <v>132623285</v>
       </c>
       <c r="B38" t="n">
-        <v>80432</v>
+        <v>101324</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672831</v>
+        <v>672638</v>
       </c>
       <c r="R38" t="n">
-        <v>6981363</v>
+        <v>6981364</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4763,7 +4771,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4773,7 +4781,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4782,18 +4790,19 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4926,32 +4935,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132623290</v>
+        <v>132617564</v>
       </c>
       <c r="B40" t="n">
-        <v>97981</v>
+        <v>80432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4961,13 +4970,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672621</v>
+        <v>672831</v>
       </c>
       <c r="R40" t="n">
-        <v>6981383</v>
+        <v>6981363</v>
       </c>
       <c r="S40" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4996,7 +5005,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5006,7 +5015,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5021,68 +5030,60 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132623285</v>
+        <v>132617599</v>
       </c>
       <c r="B41" t="n">
-        <v>101323</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>672638</v>
+        <v>672664</v>
       </c>
       <c r="R41" t="n">
-        <v>6981364</v>
+        <v>6981552</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5111,7 +5112,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5121,7 +5122,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5130,70 +5131,66 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132617607</v>
+        <v>132617558</v>
       </c>
       <c r="B42" t="n">
-        <v>79327</v>
+        <v>80305</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>672712</v>
+        <v>672873</v>
       </c>
       <c r="R42" t="n">
-        <v>6981164</v>
+        <v>6981339</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5222,7 +5219,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5232,7 +5229,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5241,24 +5238,8 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5275,48 +5256,51 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132617558</v>
+        <v>132617607</v>
       </c>
       <c r="B43" t="n">
-        <v>80305</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672873</v>
+        <v>672712</v>
       </c>
       <c r="R43" t="n">
-        <v>6981339</v>
+        <v>6981164</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5345,7 +5329,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5355,7 +5339,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5364,8 +5348,24 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5382,10 +5382,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132617592</v>
+        <v>132623256</v>
       </c>
       <c r="B44" t="n">
-        <v>80392</v>
+        <v>101324</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5393,37 +5393,45 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672709</v>
+        <v>672930</v>
       </c>
       <c r="R44" t="n">
-        <v>6981488</v>
+        <v>6981133</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5452,7 +5460,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5462,7 +5470,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5471,28 +5479,29 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132623256</v>
+        <v>132617592</v>
       </c>
       <c r="B45" t="n">
-        <v>101323</v>
+        <v>80392</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5500,45 +5509,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672930</v>
+        <v>672709</v>
       </c>
       <c r="R45" t="n">
-        <v>6981133</v>
+        <v>6981488</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5567,7 +5568,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5577,7 +5578,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5586,56 +5587,60 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132617567</v>
+        <v>132623254</v>
       </c>
       <c r="B46" t="n">
-        <v>80432</v>
+        <v>101324</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5643,13 +5648,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>672776</v>
+        <v>672976</v>
       </c>
       <c r="R46" t="n">
-        <v>6981332</v>
+        <v>6981122</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5678,7 +5683,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5688,7 +5693,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5701,40 +5706,25 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132623254</v>
+        <v>132623294</v>
       </c>
       <c r="B47" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5774,10 +5764,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>672976</v>
+        <v>672601</v>
       </c>
       <c r="R47" t="n">
-        <v>6981122</v>
+        <v>6981439</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5809,7 +5799,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5819,7 +5809,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5847,10 +5837,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132623294</v>
+        <v>132623300</v>
       </c>
       <c r="B48" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5890,13 +5880,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>672601</v>
+        <v>672758</v>
       </c>
       <c r="R48" t="n">
-        <v>6981439</v>
+        <v>6981513</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5925,7 +5915,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5935,7 +5925,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5963,10 +5953,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132623300</v>
+        <v>132617546</v>
       </c>
       <c r="B49" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5992,27 +5982,19 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672758</v>
+        <v>672949</v>
       </c>
       <c r="R49" t="n">
-        <v>6981513</v>
+        <v>6981130</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6041,7 +6023,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6051,7 +6033,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6060,67 +6042,69 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132617546</v>
+        <v>132617567</v>
       </c>
       <c r="B50" t="n">
-        <v>101323</v>
+        <v>80432</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>672949</v>
+        <v>672776</v>
       </c>
       <c r="R50" t="n">
-        <v>6981130</v>
+        <v>6981332</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6149,7 +6133,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6159,7 +6143,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6168,8 +6152,24 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6306,46 +6306,41 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132617589</v>
+        <v>132617595</v>
       </c>
       <c r="B52" t="n">
-        <v>99116</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6353,13 +6348,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672627</v>
+        <v>672745</v>
       </c>
       <c r="R52" t="n">
-        <v>6981425</v>
+        <v>6981544</v>
       </c>
       <c r="S52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6388,7 +6383,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6398,7 +6393,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6552,56 +6547,68 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132623292</v>
+        <v>132617603</v>
       </c>
       <c r="B54" t="n">
-        <v>101323</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672655</v>
+        <v>672617</v>
       </c>
       <c r="R54" t="n">
-        <v>6981418</v>
+        <v>6981488</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6630,7 +6637,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6640,7 +6647,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6649,60 +6656,64 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132617595</v>
+        <v>132617589</v>
       </c>
       <c r="B55" t="n">
-        <v>79327</v>
+        <v>99117</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6710,13 +6721,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672745</v>
+        <v>672627</v>
       </c>
       <c r="R55" t="n">
-        <v>6981544</v>
+        <v>6981425</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6745,7 +6756,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6755,7 +6766,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6783,68 +6794,56 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132617603</v>
+        <v>132623292</v>
       </c>
       <c r="B56" t="n">
-        <v>57953</v>
+        <v>101324</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>672617</v>
+        <v>672655</v>
       </c>
       <c r="R56" t="n">
-        <v>6981488</v>
+        <v>6981418</v>
       </c>
       <c r="S56" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6873,7 +6872,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6883,7 +6882,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6892,28 +6891,29 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132623271</v>
+        <v>132617555</v>
       </c>
       <c r="B57" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6921,40 +6921,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>672780</v>
+        <v>672921</v>
       </c>
       <c r="R57" t="n">
-        <v>6981331</v>
+        <v>6981328</v>
       </c>
       <c r="S57" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6983,7 +6980,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6993,7 +6990,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7002,44 +6999,28 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132617555</v>
+        <v>132617549</v>
       </c>
       <c r="B58" t="n">
-        <v>79327</v>
+        <v>80432</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7047,34 +7028,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>672921</v>
+        <v>672932</v>
       </c>
       <c r="R58" t="n">
-        <v>6981328</v>
+        <v>6981224</v>
       </c>
       <c r="S58" t="n">
         <v>3</v>
@@ -7106,7 +7090,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7116,7 +7100,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7125,8 +7109,24 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7143,7 +7143,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132617549</v>
+        <v>132623271</v>
       </c>
       <c r="B59" t="n">
         <v>80432</v>
@@ -7181,13 +7181,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>672932</v>
+        <v>672780</v>
       </c>
       <c r="R59" t="n">
-        <v>6981224</v>
+        <v>6981331</v>
       </c>
       <c r="S59" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7257,12 +7257,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7272,7 +7272,7 @@
         <v>132617602</v>
       </c>
       <c r="B60" t="n">
-        <v>97981</v>
+        <v>97982</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>132623265</v>
       </c>
       <c r="B62" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>132623280</v>
       </c>
       <c r="B63" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>132617606</v>
       </c>
       <c r="B64" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7834,10 +7834,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132617560</v>
+        <v>132617553</v>
       </c>
       <c r="B65" t="n">
-        <v>97981</v>
+        <v>101324</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7845,21 +7845,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7869,13 +7869,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>672883</v>
+        <v>672931</v>
       </c>
       <c r="R65" t="n">
-        <v>6981346</v>
+        <v>6981286</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7941,45 +7941,52 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132617574</v>
+        <v>132617591</v>
       </c>
       <c r="B66" t="n">
-        <v>91871</v>
+        <v>80432</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>672695</v>
+        <v>672709</v>
       </c>
       <c r="R66" t="n">
-        <v>6981312</v>
+        <v>6981489</v>
       </c>
       <c r="S66" t="n">
         <v>3</v>
@@ -8011,7 +8018,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8021,7 +8028,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Växandes på fyra närliggande aspträd</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8030,8 +8042,24 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8048,52 +8076,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132617591</v>
+        <v>132617574</v>
       </c>
       <c r="B67" t="n">
-        <v>80432</v>
+        <v>91872</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>672709</v>
+        <v>672695</v>
       </c>
       <c r="R67" t="n">
-        <v>6981489</v>
+        <v>6981312</v>
       </c>
       <c r="S67" t="n">
         <v>3</v>
@@ -8125,7 +8146,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8135,12 +8156,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Växandes på fyra närliggande aspträd</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8149,24 +8165,8 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8183,10 +8183,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132617553</v>
+        <v>132617560</v>
       </c>
       <c r="B68" t="n">
-        <v>101323</v>
+        <v>97982</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8194,21 +8194,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8218,13 +8218,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>672931</v>
+        <v>672883</v>
       </c>
       <c r="R68" t="n">
-        <v>6981286</v>
+        <v>6981346</v>
       </c>
       <c r="S68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8290,10 +8290,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132617598</v>
+        <v>132623263</v>
       </c>
       <c r="B69" t="n">
-        <v>92328</v>
+        <v>79327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8301,37 +8301,40 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>672763</v>
+        <v>672878</v>
       </c>
       <c r="R69" t="n">
-        <v>6981545</v>
+        <v>6981321</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8360,7 +8363,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8370,7 +8373,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8401,60 +8404,63 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132617584</v>
+        <v>132623267</v>
       </c>
       <c r="B70" t="n">
-        <v>91871</v>
+        <v>79327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>672639</v>
+        <v>672869</v>
       </c>
       <c r="R70" t="n">
-        <v>6981355</v>
+        <v>6981357</v>
       </c>
       <c r="S70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8483,7 +8489,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8493,7 +8499,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8502,18 +8508,34 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8523,7 +8545,7 @@
         <v>132617556</v>
       </c>
       <c r="B71" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8635,7 +8657,7 @@
         <v>132617561</v>
       </c>
       <c r="B72" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8739,51 +8761,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132623267</v>
+        <v>132617584</v>
       </c>
       <c r="B73" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>672869</v>
+        <v>672639</v>
       </c>
       <c r="R73" t="n">
-        <v>6981357</v>
+        <v>6981355</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8812,7 +8831,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8822,7 +8841,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8831,71 +8850,60 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132623263</v>
+        <v>132623305</v>
       </c>
       <c r="B74" t="n">
-        <v>79327</v>
+        <v>101324</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8903,13 +8911,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>672878</v>
+        <v>672911</v>
       </c>
       <c r="R74" t="n">
-        <v>6981321</v>
+        <v>6981136</v>
       </c>
       <c r="S74" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8938,7 +8946,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8948,7 +8956,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8960,21 +8968,6 @@
       <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8991,10 +8984,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132623305</v>
+        <v>132623253</v>
       </c>
       <c r="B75" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9034,10 +9027,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672911</v>
+        <v>672918</v>
       </c>
       <c r="R75" t="n">
-        <v>6981136</v>
+        <v>6980944</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9069,7 +9062,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9079,7 +9072,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9107,56 +9100,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132623253</v>
+        <v>132617598</v>
       </c>
       <c r="B76" t="n">
-        <v>101323</v>
+        <v>92329</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222498</v>
+        <v>6040186</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>672918</v>
+        <v>672763</v>
       </c>
       <c r="R76" t="n">
-        <v>6980944</v>
+        <v>6981545</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9185,7 +9170,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9195,7 +9180,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9208,66 +9193,78 @@
       <c r="AG76" t="b">
         <v>0</v>
       </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132617559</v>
+        <v>132623284</v>
       </c>
       <c r="B77" t="n">
-        <v>80432</v>
+        <v>97982</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>672887</v>
+        <v>672622</v>
       </c>
       <c r="R77" t="n">
-        <v>6981335</v>
+        <v>6981351</v>
       </c>
       <c r="S77" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9296,7 +9293,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9306,7 +9303,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9315,44 +9312,28 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132617585</v>
+        <v>132623275</v>
       </c>
       <c r="B78" t="n">
-        <v>80392</v>
+        <v>101324</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9360,26 +9341,31 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -9387,13 +9373,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>672635</v>
+        <v>672670</v>
       </c>
       <c r="R78" t="n">
-        <v>6981376</v>
+        <v>6981289</v>
       </c>
       <c r="S78" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9422,7 +9408,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9432,7 +9418,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9445,40 +9431,25 @@
       <c r="AG78" t="b">
         <v>0</v>
       </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132623284</v>
+        <v>132623257</v>
       </c>
       <c r="B79" t="n">
-        <v>97981</v>
+        <v>101324</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9486,37 +9457,45 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>672622</v>
+        <v>672951</v>
       </c>
       <c r="R79" t="n">
-        <v>6981351</v>
+        <v>6981191</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9545,7 +9524,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9555,7 +9534,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9564,6 +9543,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -9582,10 +9562,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132617575</v>
+        <v>132617585</v>
       </c>
       <c r="B80" t="n">
-        <v>57945</v>
+        <v>80392</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9593,31 +9573,26 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100110</v>
+        <v>229497</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -9625,10 +9600,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>672681</v>
+        <v>672635</v>
       </c>
       <c r="R80" t="n">
-        <v>6981300</v>
+        <v>6981376</v>
       </c>
       <c r="S80" t="n">
         <v>3</v>
@@ -9660,7 +9635,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9670,12 +9645,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Sång i över en minut.</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9684,8 +9654,24 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9702,10 +9688,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132617552</v>
+        <v>132617559</v>
       </c>
       <c r="B81" t="n">
-        <v>57950</v>
+        <v>80432</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9713,31 +9699,26 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -9745,10 +9726,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>672968</v>
+        <v>672887</v>
       </c>
       <c r="R81" t="n">
-        <v>6981202</v>
+        <v>6981335</v>
       </c>
       <c r="S81" t="n">
         <v>1</v>
@@ -9780,7 +9761,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9790,7 +9771,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9799,8 +9780,24 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -9817,10 +9814,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132623275</v>
+        <v>132617575</v>
       </c>
       <c r="B82" t="n">
-        <v>101323</v>
+        <v>57945</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9828,31 +9825,31 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222498</v>
+        <v>100110</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9860,13 +9857,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>672670</v>
+        <v>672681</v>
       </c>
       <c r="R82" t="n">
-        <v>6981289</v>
+        <v>6981300</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9895,7 +9892,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9905,7 +9902,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Sång i över en minut.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9914,61 +9916,60 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132623257</v>
+        <v>132617552</v>
       </c>
       <c r="B83" t="n">
-        <v>101323</v>
+        <v>57950</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9976,13 +9977,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>672951</v>
+        <v>672968</v>
       </c>
       <c r="R83" t="n">
-        <v>6981191</v>
+        <v>6981202</v>
       </c>
       <c r="S83" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10011,7 +10012,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10021,7 +10022,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10030,19 +10031,18 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -10052,7 +10052,7 @@
         <v>132617594</v>
       </c>
       <c r="B84" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         <v>132623255</v>
       </c>
       <c r="B85" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>132623277</v>
       </c>
       <c r="B87" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10518,32 +10518,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132617562</v>
+        <v>132617577</v>
       </c>
       <c r="B88" t="n">
-        <v>91871</v>
+        <v>91909</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10553,10 +10553,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>672869</v>
+        <v>672687</v>
       </c>
       <c r="R88" t="n">
-        <v>6981366</v>
+        <v>6981287</v>
       </c>
       <c r="S88" t="n">
         <v>3</v>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10598,7 +10598,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10625,10 +10630,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132617583</v>
+        <v>132617565</v>
       </c>
       <c r="B89" t="n">
-        <v>79327</v>
+        <v>80432</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10636,34 +10641,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>672577</v>
+        <v>672833</v>
       </c>
       <c r="R89" t="n">
-        <v>6981292</v>
+        <v>6981355</v>
       </c>
       <c r="S89" t="n">
         <v>3</v>
@@ -10695,7 +10703,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10705,7 +10713,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Växandes på björk.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10714,8 +10727,24 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -10858,10 +10887,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132617565</v>
+        <v>132617583</v>
       </c>
       <c r="B91" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10869,37 +10898,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>672833</v>
+        <v>672577</v>
       </c>
       <c r="R91" t="n">
-        <v>6981355</v>
+        <v>6981292</v>
       </c>
       <c r="S91" t="n">
         <v>3</v>
@@ -10931,7 +10957,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10941,12 +10967,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:09</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Växandes på björk.</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10955,24 +10976,8 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
@@ -10989,10 +10994,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132623291</v>
+        <v>132617562</v>
       </c>
       <c r="B92" t="n">
-        <v>101323</v>
+        <v>91872</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11000,45 +11005,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>672630</v>
+        <v>672869</v>
       </c>
       <c r="R92" t="n">
-        <v>6981380</v>
+        <v>6981366</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11067,7 +11064,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11077,7 +11074,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11086,29 +11083,28 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132623304</v>
+        <v>132623291</v>
       </c>
       <c r="B93" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11148,13 +11144,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>672732</v>
+        <v>672630</v>
       </c>
       <c r="R93" t="n">
-        <v>6981161</v>
+        <v>6981380</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11183,7 +11179,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11193,7 +11189,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11221,48 +11217,56 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132617577</v>
+        <v>132623304</v>
       </c>
       <c r="B94" t="n">
-        <v>91908</v>
+        <v>101324</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>672687</v>
+        <v>672732</v>
       </c>
       <c r="R94" t="n">
-        <v>6981287</v>
+        <v>6981161</v>
       </c>
       <c r="S94" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11291,7 +11295,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11301,12 +11305,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>På död stående gran</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11315,28 +11314,29 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132623258</v>
+        <v>132617563</v>
       </c>
       <c r="B95" t="n">
-        <v>101323</v>
+        <v>97982</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11344,45 +11344,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>672971</v>
+        <v>672858</v>
       </c>
       <c r="R95" t="n">
-        <v>6981202</v>
+        <v>6981365</v>
       </c>
       <c r="S95" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11411,7 +11403,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11421,7 +11413,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11430,29 +11422,28 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132623273</v>
+        <v>132617570</v>
       </c>
       <c r="B96" t="n">
-        <v>101323</v>
+        <v>97982</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11460,45 +11451,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>672774</v>
+        <v>672723</v>
       </c>
       <c r="R96" t="n">
-        <v>6981240</v>
+        <v>6981408</v>
       </c>
       <c r="S96" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11527,7 +11510,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11537,7 +11520,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11546,29 +11529,28 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132617563</v>
+        <v>132623299</v>
       </c>
       <c r="B97" t="n">
-        <v>97981</v>
+        <v>97982</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11600,13 +11582,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>672858</v>
+        <v>672709</v>
       </c>
       <c r="R97" t="n">
-        <v>6981365</v>
+        <v>6981494</v>
       </c>
       <c r="S97" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11635,7 +11617,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11645,7 +11627,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11660,22 +11642,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132617570</v>
+        <v>132623258</v>
       </c>
       <c r="B98" t="n">
-        <v>97981</v>
+        <v>101324</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11683,37 +11665,45 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>672723</v>
+        <v>672971</v>
       </c>
       <c r="R98" t="n">
-        <v>6981408</v>
+        <v>6981202</v>
       </c>
       <c r="S98" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11742,7 +11732,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11752,7 +11742,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11761,28 +11751,29 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132623299</v>
+        <v>132623273</v>
       </c>
       <c r="B99" t="n">
-        <v>97981</v>
+        <v>101324</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11790,37 +11781,45 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>672709</v>
+        <v>672774</v>
       </c>
       <c r="R99" t="n">
-        <v>6981494</v>
+        <v>6981240</v>
       </c>
       <c r="S99" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11849,7 +11848,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11859,7 +11858,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11868,6 +11867,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13423-2026 artfynd.xlsx
+++ b/artfynd/A 13423-2026 artfynd.xlsx
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132617547</v>
+        <v>132617597</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672932</v>
+        <v>672762</v>
       </c>
       <c r="R3" t="n">
-        <v>6981174</v>
+        <v>6981535</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132617597</v>
+        <v>132617547</v>
       </c>
       <c r="B4" t="n">
-        <v>91872</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672762</v>
+        <v>672932</v>
       </c>
       <c r="R4" t="n">
-        <v>6981535</v>
+        <v>6981174</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132617551</v>
+        <v>132617572</v>
       </c>
       <c r="B5" t="n">
-        <v>91909</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1007,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>672976</v>
+        <v>672701</v>
       </c>
       <c r="R5" t="n">
-        <v>6981217</v>
+        <v>6981350</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1066,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1084,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132617572</v>
+        <v>132617551</v>
       </c>
       <c r="B6" t="n">
-        <v>57950</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,42 +1122,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>672701</v>
+        <v>672976</v>
       </c>
       <c r="R6" t="n">
-        <v>6981350</v>
+        <v>6981217</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,7 +1221,7 @@
         <v>132623279</v>
       </c>
       <c r="B7" t="n">
-        <v>97982</v>
+        <v>97983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>132623293</v>
       </c>
       <c r="B8" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>132623296</v>
       </c>
       <c r="B9" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,32 +1557,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132617554</v>
+        <v>132617579</v>
       </c>
       <c r="B10" t="n">
-        <v>91909</v>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672912</v>
+        <v>672651</v>
       </c>
       <c r="R10" t="n">
-        <v>6981315</v>
+        <v>6981280</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132617605</v>
+        <v>132617550</v>
       </c>
       <c r="B11" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,16 +1675,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1692,33 +1692,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672801</v>
+        <v>672983</v>
       </c>
       <c r="R11" t="n">
-        <v>6981249</v>
+        <v>6981247</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1750,7 +1742,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1760,12 +1752,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Två födosökande individer varav en hona</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1792,10 +1779,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132617571</v>
+        <v>132617554</v>
       </c>
       <c r="B12" t="n">
-        <v>57953</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,45 +1790,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672713</v>
+        <v>672912</v>
       </c>
       <c r="R12" t="n">
-        <v>6981357</v>
+        <v>6981315</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,7 +1849,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,12 +1859,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,56 +1886,64 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132623282</v>
+        <v>132617605</v>
       </c>
       <c r="B13" t="n">
-        <v>101324</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672633</v>
+        <v>672801</v>
       </c>
       <c r="R13" t="n">
-        <v>6981324</v>
+        <v>6981249</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1990,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2000,7 +1982,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Två födosökande individer varav en hona</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2009,67 +1996,74 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132617579</v>
+        <v>132617571</v>
       </c>
       <c r="B14" t="n">
-        <v>91872</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672651</v>
+        <v>672713</v>
       </c>
       <c r="R14" t="n">
-        <v>6981280</v>
+        <v>6981357</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2098,7 +2092,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2102,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2135,56 +2134,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132617550</v>
+        <v>132623301</v>
       </c>
       <c r="B15" t="n">
-        <v>57950</v>
+        <v>97983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672983</v>
+        <v>672767</v>
       </c>
       <c r="R15" t="n">
-        <v>6981247</v>
+        <v>6981492</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2213,7 +2204,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2223,7 +2214,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2238,22 +2229,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132623301</v>
+        <v>132623282</v>
       </c>
       <c r="B16" t="n">
-        <v>97982</v>
+        <v>101325</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,34 +2252,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672767</v>
+        <v>672633</v>
       </c>
       <c r="R16" t="n">
-        <v>6981492</v>
+        <v>6981324</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2320,7 +2319,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2330,7 +2329,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2339,6 +2338,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2357,32 +2357,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132617590</v>
+        <v>132617581</v>
       </c>
       <c r="B17" t="n">
-        <v>91909</v>
+        <v>91872</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672706</v>
+        <v>672612</v>
       </c>
       <c r="R17" t="n">
-        <v>6981525</v>
+        <v>6981244</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2464,32 +2464,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132617581</v>
+        <v>132617590</v>
       </c>
       <c r="B18" t="n">
-        <v>91872</v>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672612</v>
+        <v>672706</v>
       </c>
       <c r="R18" t="n">
-        <v>6981244</v>
+        <v>6981525</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2571,10 +2571,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132623302</v>
+        <v>132617588</v>
       </c>
       <c r="B19" t="n">
-        <v>101324</v>
+        <v>91872</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,45 +2582,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672746</v>
+        <v>672671</v>
       </c>
       <c r="R19" t="n">
-        <v>6981560</v>
+        <v>6981418</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2649,7 +2641,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2659,7 +2651,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2668,29 +2660,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132617600</v>
+        <v>132617548</v>
       </c>
       <c r="B20" t="n">
-        <v>101324</v>
+        <v>91872</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2698,21 +2689,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2722,10 +2713,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>672651</v>
+        <v>672935</v>
       </c>
       <c r="R20" t="n">
-        <v>6981546</v>
+        <v>6981231</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2757,7 +2748,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2767,7 +2758,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2794,10 +2785,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132623268</v>
+        <v>132617593</v>
       </c>
       <c r="B21" t="n">
-        <v>101324</v>
+        <v>91872</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2805,45 +2796,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>672837</v>
+        <v>672724</v>
       </c>
       <c r="R21" t="n">
-        <v>6981360</v>
+        <v>6981448</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2872,7 +2855,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2882,7 +2865,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2891,19 +2874,18 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3036,10 +3018,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132617593</v>
+        <v>132623302</v>
       </c>
       <c r="B23" t="n">
-        <v>91872</v>
+        <v>101325</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3047,37 +3029,45 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672724</v>
+        <v>672746</v>
       </c>
       <c r="R23" t="n">
-        <v>6981448</v>
+        <v>6981560</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3106,7 +3096,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3116,7 +3106,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3125,28 +3115,29 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132617588</v>
+        <v>132617600</v>
       </c>
       <c r="B24" t="n">
-        <v>91872</v>
+        <v>101325</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3154,21 +3145,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3178,13 +3169,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>672671</v>
+        <v>672651</v>
       </c>
       <c r="R24" t="n">
-        <v>6981418</v>
+        <v>6981546</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3213,7 +3204,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3223,7 +3214,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3250,10 +3241,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132617548</v>
+        <v>132623268</v>
       </c>
       <c r="B25" t="n">
-        <v>91872</v>
+        <v>101325</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3261,37 +3252,45 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>672935</v>
+        <v>672837</v>
       </c>
       <c r="R25" t="n">
-        <v>6981231</v>
+        <v>6981360</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3320,7 +3319,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3330,7 +3329,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3339,74 +3338,67 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132623272</v>
+        <v>132617580</v>
       </c>
       <c r="B26" t="n">
-        <v>101324</v>
+        <v>91909</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>672787</v>
+        <v>672623</v>
       </c>
       <c r="R26" t="n">
-        <v>6981316</v>
+        <v>6981252</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3435,7 +3427,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3445,7 +3437,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3454,29 +3446,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132617580</v>
+        <v>132617604</v>
       </c>
       <c r="B27" t="n">
-        <v>91909</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3484,34 +3475,54 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>672623</v>
+        <v>672698</v>
       </c>
       <c r="R27" t="n">
-        <v>6981252</v>
+        <v>6981511</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3543,7 +3554,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3553,7 +3564,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3580,68 +3591,44 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132617604</v>
+        <v>132623266</v>
       </c>
       <c r="B28" t="n">
-        <v>57953</v>
+        <v>97977</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>221944</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>672698</v>
+        <v>672878</v>
       </c>
       <c r="R28" t="n">
-        <v>6981511</v>
+        <v>6981334</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3670,7 +3657,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3680,7 +3667,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3689,18 +3676,19 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3710,7 +3698,7 @@
         <v>132617568</v>
       </c>
       <c r="B29" t="n">
-        <v>97982</v>
+        <v>97983</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,10 +3802,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132623266</v>
+        <v>132623295</v>
       </c>
       <c r="B30" t="n">
-        <v>97976</v>
+        <v>101325</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3825,33 +3813,45 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221944</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672878</v>
+        <v>672594</v>
       </c>
       <c r="R30" t="n">
-        <v>6981334</v>
+        <v>6981486</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3911,17 +3911,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132623295</v>
+        <v>132623272</v>
       </c>
       <c r="B31" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3961,13 +3961,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>672594</v>
+        <v>672787</v>
       </c>
       <c r="R31" t="n">
-        <v>6981486</v>
+        <v>6981316</v>
       </c>
       <c r="S31" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4037,7 +4037,7 @@
         <v>132623278</v>
       </c>
       <c r="B32" t="n">
-        <v>97982</v>
+        <v>97983</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4141,10 +4141,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132617586</v>
+        <v>132623274</v>
       </c>
       <c r="B33" t="n">
-        <v>91872</v>
+        <v>101325</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4152,37 +4152,45 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>672660</v>
+        <v>672744</v>
       </c>
       <c r="R33" t="n">
-        <v>6981395</v>
+        <v>6981271</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4211,7 +4219,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4221,7 +4229,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4230,28 +4238,29 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132617596</v>
+        <v>132617586</v>
       </c>
       <c r="B34" t="n">
-        <v>97982</v>
+        <v>91872</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4259,21 +4268,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4283,10 +4292,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>672810</v>
+        <v>672660</v>
       </c>
       <c r="R34" t="n">
-        <v>6981546</v>
+        <v>6981395</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -4318,7 +4327,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4328,7 +4337,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4470,10 +4479,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132623274</v>
+        <v>132617596</v>
       </c>
       <c r="B36" t="n">
-        <v>101324</v>
+        <v>97983</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4481,45 +4490,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>672744</v>
+        <v>672810</v>
       </c>
       <c r="R36" t="n">
-        <v>6981271</v>
+        <v>6981546</v>
       </c>
       <c r="S36" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4548,7 +4549,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4558,7 +4559,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4567,51 +4568,50 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132623290</v>
+        <v>132617564</v>
       </c>
       <c r="B37" t="n">
-        <v>97982</v>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4621,13 +4621,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>672621</v>
+        <v>672831</v>
       </c>
       <c r="R37" t="n">
-        <v>6981383</v>
+        <v>6981363</v>
       </c>
       <c r="S37" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4681,68 +4681,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132623285</v>
+        <v>132617599</v>
       </c>
       <c r="B38" t="n">
-        <v>101324</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672638</v>
+        <v>672664</v>
       </c>
       <c r="R38" t="n">
-        <v>6981364</v>
+        <v>6981552</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4771,7 +4763,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4781,7 +4773,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4790,29 +4782,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132617557</v>
+        <v>132623290</v>
       </c>
       <c r="B39" t="n">
-        <v>80392</v>
+        <v>97983</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4820,40 +4811,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229497</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>672878</v>
+        <v>672621</v>
       </c>
       <c r="R39" t="n">
-        <v>6981324</v>
+        <v>6981383</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4882,7 +4870,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4892,7 +4880,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4901,79 +4889,66 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132617564</v>
+        <v>132617557</v>
       </c>
       <c r="B40" t="n">
-        <v>80432</v>
+        <v>80392</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672831</v>
+        <v>672878</v>
       </c>
       <c r="R40" t="n">
-        <v>6981363</v>
+        <v>6981324</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -5005,7 +4980,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5015,7 +4990,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5024,8 +4999,24 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5042,48 +5033,56 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132617599</v>
+        <v>132623285</v>
       </c>
       <c r="B41" t="n">
-        <v>79327</v>
+        <v>101325</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>672664</v>
+        <v>672638</v>
       </c>
       <c r="R41" t="n">
-        <v>6981552</v>
+        <v>6981364</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5112,7 +5111,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5122,7 +5121,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5131,18 +5130,19 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5256,48 +5256,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132617607</v>
+        <v>132617592</v>
       </c>
       <c r="B43" t="n">
-        <v>79327</v>
+        <v>80392</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672712</v>
+        <v>672709</v>
       </c>
       <c r="R43" t="n">
-        <v>6981164</v>
+        <v>6981488</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -5329,7 +5326,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5339,7 +5336,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5348,24 +5345,8 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5382,42 +5363,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132623256</v>
+        <v>132617607</v>
       </c>
       <c r="B44" t="n">
-        <v>101324</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5425,13 +5401,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672930</v>
+        <v>672712</v>
       </c>
       <c r="R44" t="n">
-        <v>6981133</v>
+        <v>6981164</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5460,7 +5436,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5470,7 +5446,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5483,25 +5459,40 @@
       <c r="AG44" t="b">
         <v>0</v>
       </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132617592</v>
+        <v>132623256</v>
       </c>
       <c r="B45" t="n">
-        <v>80392</v>
+        <v>101325</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5509,37 +5500,45 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672709</v>
+        <v>672930</v>
       </c>
       <c r="R45" t="n">
-        <v>6981488</v>
+        <v>6981133</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5568,7 +5567,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5578,7 +5577,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5587,60 +5586,56 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132623254</v>
+        <v>132617567</v>
       </c>
       <c r="B46" t="n">
-        <v>101324</v>
+        <v>80432</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5648,13 +5643,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>672976</v>
+        <v>672776</v>
       </c>
       <c r="R46" t="n">
-        <v>6981122</v>
+        <v>6981332</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5683,7 +5678,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5693,7 +5688,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5706,57 +5701,72 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132623294</v>
+        <v>132617576</v>
       </c>
       <c r="B47" t="n">
-        <v>101324</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5764,13 +5774,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>672601</v>
+        <v>672684</v>
       </c>
       <c r="R47" t="n">
-        <v>6981439</v>
+        <v>6981289</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5799,7 +5809,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5809,7 +5819,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5818,29 +5833,28 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132623300</v>
+        <v>132623254</v>
       </c>
       <c r="B48" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5880,13 +5894,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>672758</v>
+        <v>672976</v>
       </c>
       <c r="R48" t="n">
-        <v>6981513</v>
+        <v>6981122</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5915,7 +5929,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5925,7 +5939,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5953,10 +5967,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132617546</v>
+        <v>132623294</v>
       </c>
       <c r="B49" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5982,19 +5996,27 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672949</v>
+        <v>672601</v>
       </c>
       <c r="R49" t="n">
-        <v>6981130</v>
+        <v>6981439</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6023,7 +6045,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6033,7 +6055,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6042,55 +6064,61 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132617567</v>
+        <v>132623300</v>
       </c>
       <c r="B50" t="n">
-        <v>80432</v>
+        <v>101325</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6098,13 +6126,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>672776</v>
+        <v>672758</v>
       </c>
       <c r="R50" t="n">
-        <v>6981332</v>
+        <v>6981513</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6133,7 +6161,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6143,7 +6171,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6156,83 +6184,60 @@
       <c r="AG50" t="b">
         <v>0</v>
       </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132617576</v>
+        <v>132617546</v>
       </c>
       <c r="B51" t="n">
-        <v>57953</v>
+        <v>101325</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672684</v>
+        <v>672949</v>
       </c>
       <c r="R51" t="n">
-        <v>6981289</v>
+        <v>6981130</v>
       </c>
       <c r="S51" t="n">
         <v>3</v>
@@ -6264,7 +6269,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6274,12 +6279,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6306,10 +6306,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132617595</v>
+        <v>132617603</v>
       </c>
       <c r="B52" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6317,44 +6317,57 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672745</v>
+        <v>672617</v>
       </c>
       <c r="R52" t="n">
-        <v>6981544</v>
+        <v>6981488</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6383,7 +6396,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6393,7 +6406,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6402,7 +6415,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6421,37 +6433,46 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132617566</v>
+        <v>132617589</v>
       </c>
       <c r="B53" t="n">
-        <v>80392</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6459,10 +6480,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>672774</v>
+        <v>672627</v>
       </c>
       <c r="R53" t="n">
-        <v>6981334</v>
+        <v>6981425</v>
       </c>
       <c r="S53" t="n">
         <v>2</v>
@@ -6494,7 +6515,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6504,7 +6525,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6516,21 +6537,6 @@
       <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6547,10 +6553,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132617603</v>
+        <v>132617595</v>
       </c>
       <c r="B54" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6558,57 +6564,44 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672617</v>
+        <v>672745</v>
       </c>
       <c r="R54" t="n">
-        <v>6981488</v>
+        <v>6981544</v>
       </c>
       <c r="S54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6637,7 +6630,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6647,7 +6640,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6656,6 +6649,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6674,45 +6668,41 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132617589</v>
+        <v>132623292</v>
       </c>
       <c r="B55" t="n">
-        <v>99117</v>
+        <v>101325</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
@@ -6721,13 +6711,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672627</v>
+        <v>672655</v>
       </c>
       <c r="R55" t="n">
-        <v>6981425</v>
+        <v>6981418</v>
       </c>
       <c r="S55" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6756,7 +6746,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6766,7 +6756,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6782,22 +6772,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132623292</v>
+        <v>132617566</v>
       </c>
       <c r="B56" t="n">
-        <v>101324</v>
+        <v>80392</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6805,31 +6795,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6837,13 +6822,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>672655</v>
+        <v>672774</v>
       </c>
       <c r="R56" t="n">
-        <v>6981418</v>
+        <v>6981334</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6872,7 +6857,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6882,7 +6867,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6895,47 +6880,62 @@
       <c r="AG56" t="b">
         <v>0</v>
       </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132617555</v>
+        <v>132617602</v>
       </c>
       <c r="B57" t="n">
-        <v>79327</v>
+        <v>97983</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6945,10 +6945,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>672921</v>
+        <v>672593</v>
       </c>
       <c r="R57" t="n">
-        <v>6981328</v>
+        <v>6981519</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7017,10 +7017,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132617549</v>
+        <v>132623303</v>
       </c>
       <c r="B58" t="n">
-        <v>80432</v>
+        <v>56522</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7028,40 +7028,49 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>672932</v>
+        <v>672560</v>
       </c>
       <c r="R58" t="n">
-        <v>6981224</v>
+        <v>6981577</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7090,7 +7099,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7100,7 +7109,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7109,71 +7118,60 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132623271</v>
+        <v>132623265</v>
       </c>
       <c r="B59" t="n">
-        <v>80432</v>
+        <v>101325</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7181,13 +7179,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>672780</v>
+        <v>672872</v>
       </c>
       <c r="R59" t="n">
-        <v>6981331</v>
+        <v>6981332</v>
       </c>
       <c r="S59" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7216,7 +7214,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7226,7 +7224,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7239,21 +7237,6 @@
       <c r="AG59" t="b">
         <v>0</v>
       </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
@@ -7262,17 +7245,17 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132617602</v>
+        <v>132623280</v>
       </c>
       <c r="B60" t="n">
-        <v>97982</v>
+        <v>101325</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7280,37 +7263,45 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672593</v>
+        <v>672636</v>
       </c>
       <c r="R60" t="n">
-        <v>6981519</v>
+        <v>6981290</v>
       </c>
       <c r="S60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7339,7 +7330,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7349,7 +7340,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7358,78 +7349,67 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132623303</v>
+        <v>132617606</v>
       </c>
       <c r="B61" t="n">
-        <v>56522</v>
+        <v>101325</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>206004</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672560</v>
+        <v>672733</v>
       </c>
       <c r="R61" t="n">
-        <v>6981577</v>
+        <v>6981160</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7458,7 +7438,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7468,7 +7448,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7483,68 +7463,60 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132623265</v>
+        <v>132617555</v>
       </c>
       <c r="B62" t="n">
-        <v>101324</v>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>672872</v>
+        <v>672921</v>
       </c>
       <c r="R62" t="n">
-        <v>6981332</v>
+        <v>6981328</v>
       </c>
       <c r="S62" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7573,7 +7545,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7583,7 +7555,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7592,61 +7564,55 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132623280</v>
+        <v>132617549</v>
       </c>
       <c r="B63" t="n">
-        <v>101324</v>
+        <v>80432</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7654,13 +7620,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672636</v>
+        <v>672932</v>
       </c>
       <c r="R63" t="n">
-        <v>6981290</v>
+        <v>6981224</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7689,7 +7655,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7699,7 +7665,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7712,63 +7678,81 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132617606</v>
+        <v>132623271</v>
       </c>
       <c r="B64" t="n">
-        <v>101324</v>
+        <v>80432</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>672733</v>
+        <v>672780</v>
       </c>
       <c r="R64" t="n">
-        <v>6981160</v>
+        <v>6981331</v>
       </c>
       <c r="S64" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7797,7 +7781,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7807,7 +7791,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7816,28 +7800,44 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132617553</v>
+        <v>132617574</v>
       </c>
       <c r="B65" t="n">
-        <v>101324</v>
+        <v>91872</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7845,21 +7845,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7869,10 +7869,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>672931</v>
+        <v>672695</v>
       </c>
       <c r="R65" t="n">
-        <v>6981286</v>
+        <v>6981312</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8076,10 +8076,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132617574</v>
+        <v>132617560</v>
       </c>
       <c r="B67" t="n">
-        <v>91872</v>
+        <v>97983</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8087,21 +8087,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8111,13 +8111,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>672695</v>
+        <v>672883</v>
       </c>
       <c r="R67" t="n">
-        <v>6981312</v>
+        <v>6981346</v>
       </c>
       <c r="S67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8183,10 +8183,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132617560</v>
+        <v>132617553</v>
       </c>
       <c r="B68" t="n">
-        <v>97982</v>
+        <v>101325</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8194,21 +8194,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8218,13 +8218,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>672883</v>
+        <v>672931</v>
       </c>
       <c r="R68" t="n">
-        <v>6981346</v>
+        <v>6981286</v>
       </c>
       <c r="S68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8290,10 +8290,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132623263</v>
+        <v>132617556</v>
       </c>
       <c r="B69" t="n">
-        <v>79327</v>
+        <v>91909</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8301,40 +8301,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>672878</v>
+        <v>672881</v>
       </c>
       <c r="R69" t="n">
-        <v>6981321</v>
+        <v>6981314</v>
       </c>
       <c r="S69" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8363,7 +8360,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8373,7 +8370,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På stående död gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8382,44 +8384,28 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132623267</v>
+        <v>132617561</v>
       </c>
       <c r="B70" t="n">
-        <v>79327</v>
+        <v>91909</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8427,40 +8413,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>672869</v>
+        <v>672878</v>
       </c>
       <c r="R70" t="n">
-        <v>6981357</v>
+        <v>6981375</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8489,7 +8472,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8499,7 +8482,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8508,44 +8491,28 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132617556</v>
+        <v>132623263</v>
       </c>
       <c r="B71" t="n">
-        <v>91909</v>
+        <v>79327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8553,37 +8520,40 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672881</v>
+        <v>672878</v>
       </c>
       <c r="R71" t="n">
-        <v>6981314</v>
+        <v>6981321</v>
       </c>
       <c r="S71" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8612,7 +8582,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8622,12 +8592,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:25</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På stående död gran</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8636,50 +8601,66 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132617561</v>
+        <v>132617584</v>
       </c>
       <c r="B72" t="n">
-        <v>91909</v>
+        <v>91872</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8689,10 +8670,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>672878</v>
+        <v>672639</v>
       </c>
       <c r="R72" t="n">
-        <v>6981375</v>
+        <v>6981355</v>
       </c>
       <c r="S72" t="n">
         <v>3</v>
@@ -8724,7 +8705,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8734,7 +8715,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8761,48 +8742,51 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132617584</v>
+        <v>132623267</v>
       </c>
       <c r="B73" t="n">
-        <v>91872</v>
+        <v>79327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>672639</v>
+        <v>672869</v>
       </c>
       <c r="R73" t="n">
-        <v>6981355</v>
+        <v>6981357</v>
       </c>
       <c r="S73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8831,7 +8815,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8841,7 +8825,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8850,18 +8834,34 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8871,7 +8871,7 @@
         <v>132623305</v>
       </c>
       <c r="B74" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>132623253</v>
       </c>
       <c r="B75" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9223,10 +9223,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132623284</v>
+        <v>132617575</v>
       </c>
       <c r="B77" t="n">
-        <v>97982</v>
+        <v>57945</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9234,37 +9234,45 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221945</v>
+        <v>100110</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>672622</v>
+        <v>672681</v>
       </c>
       <c r="R77" t="n">
-        <v>6981351</v>
+        <v>6981300</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9293,7 +9301,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9303,7 +9311,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Sång i över en minut.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9318,54 +9331,49 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132623275</v>
+        <v>132617559</v>
       </c>
       <c r="B78" t="n">
-        <v>101324</v>
+        <v>80432</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -9373,13 +9381,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>672670</v>
+        <v>672887</v>
       </c>
       <c r="R78" t="n">
-        <v>6981289</v>
+        <v>6981335</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9408,7 +9416,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9418,7 +9426,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9431,25 +9439,40 @@
       <c r="AG78" t="b">
         <v>0</v>
       </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132623257</v>
+        <v>132617585</v>
       </c>
       <c r="B79" t="n">
-        <v>101324</v>
+        <v>80392</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9457,31 +9480,26 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -9489,13 +9507,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>672951</v>
+        <v>672635</v>
       </c>
       <c r="R79" t="n">
-        <v>6981191</v>
+        <v>6981376</v>
       </c>
       <c r="S79" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9524,7 +9542,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9534,7 +9552,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9547,25 +9565,40 @@
       <c r="AG79" t="b">
         <v>0</v>
       </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132617585</v>
+        <v>132623275</v>
       </c>
       <c r="B80" t="n">
-        <v>80392</v>
+        <v>101325</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9573,26 +9606,31 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -9600,13 +9638,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>672635</v>
+        <v>672670</v>
       </c>
       <c r="R80" t="n">
-        <v>6981376</v>
+        <v>6981289</v>
       </c>
       <c r="S80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9635,7 +9673,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9645,7 +9683,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9658,67 +9696,57 @@
       <c r="AG80" t="b">
         <v>0</v>
       </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132617559</v>
+        <v>132623257</v>
       </c>
       <c r="B81" t="n">
-        <v>80432</v>
+        <v>101325</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -9726,13 +9754,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>672887</v>
+        <v>672951</v>
       </c>
       <c r="R81" t="n">
-        <v>6981335</v>
+        <v>6981191</v>
       </c>
       <c r="S81" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9761,7 +9789,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9771,7 +9799,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9784,40 +9812,25 @@
       <c r="AG81" t="b">
         <v>0</v>
       </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132617575</v>
+        <v>132623284</v>
       </c>
       <c r="B82" t="n">
-        <v>57945</v>
+        <v>97983</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9825,45 +9838,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100110</v>
+        <v>221945</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>672681</v>
+        <v>672622</v>
       </c>
       <c r="R82" t="n">
-        <v>6981300</v>
+        <v>6981351</v>
       </c>
       <c r="S82" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9892,7 +9897,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9902,12 +9907,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Sång i över en minut.</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9922,12 +9922,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -10160,10 +10160,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132623255</v>
+        <v>132617587</v>
       </c>
       <c r="B85" t="n">
-        <v>101324</v>
+        <v>80392</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10171,31 +10171,26 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -10203,13 +10198,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>672955</v>
+        <v>672655</v>
       </c>
       <c r="R85" t="n">
-        <v>6981134</v>
+        <v>6981378</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10238,7 +10233,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10248,7 +10243,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10261,25 +10256,40 @@
       <c r="AG85" t="b">
         <v>0</v>
       </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132617587</v>
+        <v>132623255</v>
       </c>
       <c r="B86" t="n">
-        <v>80392</v>
+        <v>101325</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10287,26 +10297,31 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -10314,13 +10329,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>672655</v>
+        <v>672955</v>
       </c>
       <c r="R86" t="n">
-        <v>6981378</v>
+        <v>6981134</v>
       </c>
       <c r="S86" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10349,7 +10364,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10359,7 +10374,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10372,30 +10387,15 @@
       <c r="AG86" t="b">
         <v>0</v>
       </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -10405,7 +10405,7 @@
         <v>132623277</v>
       </c>
       <c r="B87" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10518,10 +10518,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132617577</v>
+        <v>132617565</v>
       </c>
       <c r="B88" t="n">
-        <v>91909</v>
+        <v>80432</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10529,34 +10529,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>672687</v>
+        <v>672833</v>
       </c>
       <c r="R88" t="n">
-        <v>6981287</v>
+        <v>6981355</v>
       </c>
       <c r="S88" t="n">
         <v>3</v>
@@ -10588,7 +10591,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10598,12 +10601,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>Växandes på björk.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10612,8 +10615,24 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -10630,10 +10649,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132617565</v>
+        <v>132623270</v>
       </c>
       <c r="B89" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10641,21 +10660,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10668,13 +10687,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>672833</v>
+        <v>672831</v>
       </c>
       <c r="R89" t="n">
         <v>6981355</v>
       </c>
       <c r="S89" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10703,7 +10722,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10713,12 +10732,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:09</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Växandes på björk.</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10733,79 +10747,76 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132623270</v>
+        <v>132617562</v>
       </c>
       <c r="B90" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>672831</v>
+        <v>672869</v>
       </c>
       <c r="R90" t="n">
-        <v>6981355</v>
+        <v>6981366</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10834,7 +10845,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10844,7 +10855,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10853,34 +10864,18 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -10994,32 +10989,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132617562</v>
+        <v>132617577</v>
       </c>
       <c r="B92" t="n">
-        <v>91872</v>
+        <v>91909</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11029,10 +11024,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>672869</v>
+        <v>672687</v>
       </c>
       <c r="R92" t="n">
-        <v>6981366</v>
+        <v>6981287</v>
       </c>
       <c r="S92" t="n">
         <v>3</v>
@@ -11064,7 +11059,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11074,7 +11069,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11104,7 +11104,7 @@
         <v>132623291</v>
       </c>
       <c r="B93" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>132623304</v>
       </c>
       <c r="B94" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>132617563</v>
       </c>
       <c r="B95" t="n">
-        <v>97982</v>
+        <v>97983</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>132617570</v>
       </c>
       <c r="B96" t="n">
-        <v>97982</v>
+        <v>97983</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11547,10 +11547,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132623299</v>
+        <v>132623258</v>
       </c>
       <c r="B97" t="n">
-        <v>97982</v>
+        <v>101325</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11558,37 +11558,45 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>672709</v>
+        <v>672971</v>
       </c>
       <c r="R97" t="n">
-        <v>6981494</v>
+        <v>6981202</v>
       </c>
       <c r="S97" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11617,7 +11625,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11627,7 +11635,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11636,6 +11644,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -11654,10 +11663,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132623258</v>
+        <v>132623273</v>
       </c>
       <c r="B98" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11697,13 +11706,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>672971</v>
+        <v>672774</v>
       </c>
       <c r="R98" t="n">
-        <v>6981202</v>
+        <v>6981240</v>
       </c>
       <c r="S98" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11732,7 +11741,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11742,7 +11751,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11770,10 +11779,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132623273</v>
+        <v>132623299</v>
       </c>
       <c r="B99" t="n">
-        <v>101324</v>
+        <v>97983</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11781,45 +11790,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>672774</v>
+        <v>672709</v>
       </c>
       <c r="R99" t="n">
-        <v>6981240</v>
+        <v>6981494</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11848,7 +11849,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11858,7 +11859,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11867,7 +11868,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13423-2026 artfynd.xlsx
+++ b/artfynd/A 13423-2026 artfynd.xlsx
@@ -2571,10 +2571,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132617588</v>
+        <v>132617601</v>
       </c>
       <c r="B19" t="n">
-        <v>91872</v>
+        <v>80392</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,37 +2582,40 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>229497</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672671</v>
+        <v>672548</v>
       </c>
       <c r="R19" t="n">
-        <v>6981418</v>
+        <v>6981599</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2641,7 +2644,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2651,7 +2654,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2660,8 +2663,24 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2678,7 +2697,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132617548</v>
+        <v>132617588</v>
       </c>
       <c r="B20" t="n">
         <v>91872</v>
@@ -2713,13 +2732,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>672935</v>
+        <v>672671</v>
       </c>
       <c r="R20" t="n">
-        <v>6981231</v>
+        <v>6981418</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2748,7 +2767,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2758,7 +2777,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2785,7 +2804,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132617593</v>
+        <v>132617548</v>
       </c>
       <c r="B21" t="n">
         <v>91872</v>
@@ -2820,13 +2839,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>672724</v>
+        <v>672935</v>
       </c>
       <c r="R21" t="n">
-        <v>6981448</v>
+        <v>6981231</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2855,7 +2874,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2865,7 +2884,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2892,10 +2911,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132617601</v>
+        <v>132617593</v>
       </c>
       <c r="B22" t="n">
-        <v>80392</v>
+        <v>91872</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2903,40 +2922,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>672548</v>
+        <v>672724</v>
       </c>
       <c r="R22" t="n">
-        <v>6981599</v>
+        <v>6981448</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2965,7 +2981,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2975,7 +2991,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2984,24 +3000,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -4141,10 +4141,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132623274</v>
+        <v>132617586</v>
       </c>
       <c r="B33" t="n">
-        <v>101325</v>
+        <v>91872</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4152,45 +4152,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>672744</v>
+        <v>672660</v>
       </c>
       <c r="R33" t="n">
-        <v>6981271</v>
+        <v>6981395</v>
       </c>
       <c r="S33" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4219,7 +4211,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4229,7 +4221,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4238,64 +4230,71 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132617586</v>
+        <v>132617582</v>
       </c>
       <c r="B34" t="n">
-        <v>91872</v>
+        <v>57950</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>672660</v>
+        <v>672612</v>
       </c>
       <c r="R34" t="n">
-        <v>6981395</v>
+        <v>6981238</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -4327,7 +4326,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4337,7 +4336,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4364,53 +4363,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132617582</v>
+        <v>132617596</v>
       </c>
       <c r="B35" t="n">
-        <v>57950</v>
+        <v>97983</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>672612</v>
+        <v>672810</v>
       </c>
       <c r="R35" t="n">
-        <v>6981238</v>
+        <v>6981546</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -4442,7 +4433,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4452,7 +4443,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4479,10 +4470,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132617596</v>
+        <v>132623274</v>
       </c>
       <c r="B36" t="n">
-        <v>97983</v>
+        <v>101325</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4490,37 +4481,45 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>672810</v>
+        <v>672744</v>
       </c>
       <c r="R36" t="n">
-        <v>6981546</v>
+        <v>6981271</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4549,7 +4548,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4559,7 +4558,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4568,18 +4567,19 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -6910,32 +6910,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132617602</v>
+        <v>132617555</v>
       </c>
       <c r="B57" t="n">
-        <v>97983</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6945,10 +6945,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>672593</v>
+        <v>672921</v>
       </c>
       <c r="R57" t="n">
-        <v>6981519</v>
+        <v>6981328</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7017,10 +7017,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132623303</v>
+        <v>132617549</v>
       </c>
       <c r="B58" t="n">
-        <v>56522</v>
+        <v>80432</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7028,49 +7028,40 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>672560</v>
+        <v>672932</v>
       </c>
       <c r="R58" t="n">
-        <v>6981577</v>
+        <v>6981224</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7099,7 +7090,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7109,7 +7100,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7118,60 +7109,71 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132623265</v>
+        <v>132623271</v>
       </c>
       <c r="B59" t="n">
-        <v>101325</v>
+        <v>80432</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7179,13 +7181,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>672872</v>
+        <v>672780</v>
       </c>
       <c r="R59" t="n">
-        <v>6981332</v>
+        <v>6981331</v>
       </c>
       <c r="S59" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7214,7 +7216,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7224,7 +7226,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7237,6 +7239,21 @@
       <c r="AG59" t="b">
         <v>0</v>
       </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
@@ -7245,17 +7262,17 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132623280</v>
+        <v>132617602</v>
       </c>
       <c r="B60" t="n">
-        <v>101325</v>
+        <v>97983</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7263,45 +7280,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672636</v>
+        <v>672593</v>
       </c>
       <c r="R60" t="n">
-        <v>6981290</v>
+        <v>6981519</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7330,7 +7339,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7340,7 +7349,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7349,67 +7358,78 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132617606</v>
+        <v>132623303</v>
       </c>
       <c r="B61" t="n">
-        <v>101325</v>
+        <v>56522</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>206004</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672733</v>
+        <v>672560</v>
       </c>
       <c r="R61" t="n">
-        <v>6981160</v>
+        <v>6981577</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7438,7 +7458,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7448,7 +7468,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7463,60 +7483,68 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132617555</v>
+        <v>132623265</v>
       </c>
       <c r="B62" t="n">
-        <v>79327</v>
+        <v>101325</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>672921</v>
+        <v>672872</v>
       </c>
       <c r="R62" t="n">
-        <v>6981328</v>
+        <v>6981332</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7545,7 +7573,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7555,7 +7583,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7564,55 +7592,61 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132617549</v>
+        <v>132623280</v>
       </c>
       <c r="B63" t="n">
-        <v>80432</v>
+        <v>101325</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7620,13 +7654,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672932</v>
+        <v>672636</v>
       </c>
       <c r="R63" t="n">
-        <v>6981224</v>
+        <v>6981290</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7655,7 +7689,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7665,7 +7699,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7678,81 +7712,63 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132623271</v>
+        <v>132617606</v>
       </c>
       <c r="B64" t="n">
-        <v>80432</v>
+        <v>101325</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>672780</v>
+        <v>672733</v>
       </c>
       <c r="R64" t="n">
-        <v>6981331</v>
+        <v>6981160</v>
       </c>
       <c r="S64" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7781,7 +7797,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7791,7 +7807,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7800,34 +7816,18 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -8509,10 +8509,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132623263</v>
+        <v>132617598</v>
       </c>
       <c r="B71" t="n">
-        <v>79327</v>
+        <v>92329</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8520,40 +8520,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672878</v>
+        <v>672763</v>
       </c>
       <c r="R71" t="n">
-        <v>6981321</v>
+        <v>6981545</v>
       </c>
       <c r="S71" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8582,7 +8579,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8592,7 +8589,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8623,60 +8620,63 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132617584</v>
+        <v>132623263</v>
       </c>
       <c r="B72" t="n">
-        <v>91872</v>
+        <v>79327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>672639</v>
+        <v>672878</v>
       </c>
       <c r="R72" t="n">
-        <v>6981355</v>
+        <v>6981321</v>
       </c>
       <c r="S72" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8724,69 +8724,82 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132623267</v>
+        <v>132617584</v>
       </c>
       <c r="B73" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>672869</v>
+        <v>672639</v>
       </c>
       <c r="R73" t="n">
-        <v>6981357</v>
+        <v>6981355</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8815,7 +8828,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8825,7 +8838,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8834,76 +8847,55 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132623305</v>
+        <v>132623267</v>
       </c>
       <c r="B74" t="n">
-        <v>101325</v>
+        <v>79327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8911,10 +8903,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>672911</v>
+        <v>672869</v>
       </c>
       <c r="R74" t="n">
-        <v>6981136</v>
+        <v>6981357</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8946,7 +8938,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8956,7 +8948,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8968,6 +8960,21 @@
       <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8984,7 +8991,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132623253</v>
+        <v>132623305</v>
       </c>
       <c r="B75" t="n">
         <v>101325</v>
@@ -9027,10 +9034,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672918</v>
+        <v>672911</v>
       </c>
       <c r="R75" t="n">
-        <v>6980944</v>
+        <v>6981136</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9062,7 +9069,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9072,7 +9079,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9100,48 +9107,56 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132617598</v>
+        <v>132623253</v>
       </c>
       <c r="B76" t="n">
-        <v>92329</v>
+        <v>101325</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6040186</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>672763</v>
+        <v>672918</v>
       </c>
       <c r="R76" t="n">
-        <v>6981545</v>
+        <v>6980944</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9170,7 +9185,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9180,7 +9195,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9193,72 +9208,52 @@
       <c r="AG76" t="b">
         <v>0</v>
       </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132617575</v>
+        <v>132617559</v>
       </c>
       <c r="B77" t="n">
-        <v>57945</v>
+        <v>80432</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100110</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9266,13 +9261,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>672681</v>
+        <v>672887</v>
       </c>
       <c r="R77" t="n">
-        <v>6981300</v>
+        <v>6981335</v>
       </c>
       <c r="S77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9301,7 +9296,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9311,12 +9306,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Sång i över en minut.</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9325,8 +9315,24 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9343,37 +9349,42 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132617559</v>
+        <v>132617575</v>
       </c>
       <c r="B78" t="n">
-        <v>80432</v>
+        <v>57945</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>100110</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -9381,13 +9392,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>672887</v>
+        <v>672681</v>
       </c>
       <c r="R78" t="n">
-        <v>6981335</v>
+        <v>6981300</v>
       </c>
       <c r="S78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9416,7 +9427,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9426,7 +9437,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Sång i över en minut.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9435,24 +9451,8 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9469,10 +9469,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132617585</v>
+        <v>132623284</v>
       </c>
       <c r="B79" t="n">
-        <v>80392</v>
+        <v>97983</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9480,40 +9480,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229497</v>
+        <v>221945</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>672635</v>
+        <v>672622</v>
       </c>
       <c r="R79" t="n">
-        <v>6981376</v>
+        <v>6981351</v>
       </c>
       <c r="S79" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9542,7 +9539,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9552,7 +9549,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9561,34 +9558,18 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9827,48 +9808,56 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132623284</v>
+        <v>132617552</v>
       </c>
       <c r="B82" t="n">
-        <v>97983</v>
+        <v>57950</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>672622</v>
+        <v>672968</v>
       </c>
       <c r="R82" t="n">
-        <v>6981351</v>
+        <v>6981202</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9897,7 +9886,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9907,7 +9896,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9922,54 +9911,49 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132617552</v>
+        <v>132617585</v>
       </c>
       <c r="B83" t="n">
-        <v>57950</v>
+        <v>80392</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9977,13 +9961,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>672968</v>
+        <v>672635</v>
       </c>
       <c r="R83" t="n">
-        <v>6981202</v>
+        <v>6981376</v>
       </c>
       <c r="S83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10012,7 +9996,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10022,7 +10006,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10031,8 +10015,24 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">

--- a/artfynd/A 13423-2026 artfynd.xlsx
+++ b/artfynd/A 13423-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132617578</v>
+        <v>132617547</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672651</v>
+        <v>672932</v>
       </c>
       <c r="R2" t="n">
-        <v>6981280</v>
+        <v>6981174</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132617547</v>
+        <v>132617578</v>
       </c>
       <c r="B4" t="n">
-        <v>79327</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672932</v>
+        <v>672651</v>
       </c>
       <c r="R4" t="n">
-        <v>6981174</v>
+        <v>6981280</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132617572</v>
+        <v>132617551</v>
       </c>
       <c r="B5" t="n">
-        <v>57950</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,42 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>672701</v>
+        <v>672976</v>
       </c>
       <c r="R5" t="n">
-        <v>6981350</v>
+        <v>6981217</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1074,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132617551</v>
+        <v>132617572</v>
       </c>
       <c r="B6" t="n">
-        <v>91909</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1122,34 +1114,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>672976</v>
+        <v>672701</v>
       </c>
       <c r="R6" t="n">
-        <v>6981217</v>
+        <v>6981350</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132623279</v>
+        <v>132623293</v>
       </c>
       <c r="B7" t="n">
-        <v>97983</v>
+        <v>101326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,34 +1229,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>672637</v>
+        <v>672629</v>
       </c>
       <c r="R7" t="n">
-        <v>6981289</v>
+        <v>6981435</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1288,7 +1296,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1298,7 +1306,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,6 +1315,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1325,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132623293</v>
+        <v>132623296</v>
       </c>
       <c r="B8" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,13 +1377,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>672629</v>
+        <v>672649</v>
       </c>
       <c r="R8" t="n">
-        <v>6981435</v>
+        <v>6981516</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1403,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1413,7 +1422,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132623296</v>
+        <v>132623279</v>
       </c>
       <c r="B9" t="n">
-        <v>101325</v>
+        <v>97983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1452,45 +1461,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>672649</v>
+        <v>672637</v>
       </c>
       <c r="R9" t="n">
-        <v>6981516</v>
+        <v>6981289</v>
       </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1519,7 +1520,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1529,7 +1530,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,7 +1539,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132617550</v>
+        <v>132617605</v>
       </c>
       <c r="B11" t="n">
-        <v>57950</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,16 +1675,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1692,25 +1692,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672983</v>
+        <v>672801</v>
       </c>
       <c r="R11" t="n">
-        <v>6981247</v>
+        <v>6981249</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1742,7 +1750,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1752,7 +1760,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Två födosökande individer varav en hona</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1779,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132617554</v>
+        <v>132617571</v>
       </c>
       <c r="B12" t="n">
-        <v>91909</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,37 +1803,45 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672912</v>
+        <v>672713</v>
       </c>
       <c r="R12" t="n">
-        <v>6981315</v>
+        <v>6981357</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1849,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1859,7 +1880,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1886,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132617605</v>
+        <v>132617554</v>
       </c>
       <c r="B13" t="n">
-        <v>57953</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,50 +1923,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672801</v>
+        <v>672912</v>
       </c>
       <c r="R13" t="n">
-        <v>6981249</v>
+        <v>6981315</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -1972,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,12 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Två födosökande individer varav en hona</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132617571</v>
+        <v>132617550</v>
       </c>
       <c r="B14" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2025,16 +2030,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2047,7 +2052,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2057,13 +2062,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672713</v>
+        <v>672983</v>
       </c>
       <c r="R14" t="n">
-        <v>6981357</v>
+        <v>6981247</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2092,7 +2097,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2102,12 +2107,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2134,10 +2134,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132623301</v>
+        <v>132623282</v>
       </c>
       <c r="B15" t="n">
-        <v>97983</v>
+        <v>101326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,34 +2145,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672767</v>
+        <v>672633</v>
       </c>
       <c r="R15" t="n">
-        <v>6981492</v>
+        <v>6981324</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2204,7 +2212,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2214,7 +2222,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2223,6 +2231,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2241,10 +2250,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132623282</v>
+        <v>132623301</v>
       </c>
       <c r="B16" t="n">
-        <v>101325</v>
+        <v>97983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,42 +2261,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672633</v>
+        <v>672767</v>
       </c>
       <c r="R16" t="n">
-        <v>6981324</v>
+        <v>6981492</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2319,7 +2320,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2329,7 +2330,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,7 +2339,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2571,10 +2571,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132617601</v>
+        <v>132617593</v>
       </c>
       <c r="B19" t="n">
-        <v>80392</v>
+        <v>91872</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,40 +2582,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672548</v>
+        <v>672724</v>
       </c>
       <c r="R19" t="n">
-        <v>6981599</v>
+        <v>6981448</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2644,7 +2641,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2654,7 +2651,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2663,24 +2660,8 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2911,10 +2892,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132617593</v>
+        <v>132623302</v>
       </c>
       <c r="B22" t="n">
-        <v>91872</v>
+        <v>101326</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2922,37 +2903,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>672724</v>
+        <v>672746</v>
       </c>
       <c r="R22" t="n">
-        <v>6981448</v>
+        <v>6981560</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2981,7 +2970,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2991,7 +2980,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3000,28 +2989,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132623302</v>
+        <v>132617600</v>
       </c>
       <c r="B23" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3047,27 +3037,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672746</v>
+        <v>672651</v>
       </c>
       <c r="R23" t="n">
-        <v>6981560</v>
+        <v>6981546</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3096,7 +3078,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3106,7 +3088,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3115,29 +3097,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132617600</v>
+        <v>132623268</v>
       </c>
       <c r="B24" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3163,19 +3144,27 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>672651</v>
+        <v>672837</v>
       </c>
       <c r="R24" t="n">
-        <v>6981546</v>
+        <v>6981360</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3204,7 +3193,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3214,7 +3203,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3223,28 +3212,29 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132623268</v>
+        <v>132617601</v>
       </c>
       <c r="B25" t="n">
-        <v>101325</v>
+        <v>80392</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3252,31 +3242,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3284,13 +3269,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>672837</v>
+        <v>672548</v>
       </c>
       <c r="R25" t="n">
-        <v>6981360</v>
+        <v>6981599</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3319,7 +3304,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3329,7 +3314,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3342,25 +3327,40 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132617580</v>
+        <v>132617604</v>
       </c>
       <c r="B26" t="n">
-        <v>91909</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3368,34 +3368,54 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>672623</v>
+        <v>672698</v>
       </c>
       <c r="R26" t="n">
-        <v>6981252</v>
+        <v>6981511</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3427,7 +3447,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3437,7 +3457,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3464,65 +3484,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132617604</v>
+        <v>132617568</v>
       </c>
       <c r="B27" t="n">
-        <v>57953</v>
+        <v>97983</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>672698</v>
+        <v>672748</v>
       </c>
       <c r="R27" t="n">
-        <v>6981511</v>
+        <v>6981368</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3695,32 +3695,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132617568</v>
+        <v>132617580</v>
       </c>
       <c r="B29" t="n">
-        <v>97983</v>
+        <v>91909</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3730,10 +3730,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672748</v>
+        <v>672623</v>
       </c>
       <c r="R29" t="n">
-        <v>6981368</v>
+        <v>6981252</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3805,7 +3805,7 @@
         <v>132623295</v>
       </c>
       <c r="B30" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>132623272</v>
       </c>
       <c r="B31" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4141,10 +4141,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132617586</v>
+        <v>132623274</v>
       </c>
       <c r="B33" t="n">
-        <v>91872</v>
+        <v>101326</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4152,37 +4152,45 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>672660</v>
+        <v>672744</v>
       </c>
       <c r="R33" t="n">
-        <v>6981395</v>
+        <v>6981271</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4211,7 +4219,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4221,7 +4229,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4230,71 +4238,64 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132617582</v>
+        <v>132617586</v>
       </c>
       <c r="B34" t="n">
-        <v>57950</v>
+        <v>91872</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>672612</v>
+        <v>672660</v>
       </c>
       <c r="R34" t="n">
-        <v>6981238</v>
+        <v>6981395</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -4326,7 +4327,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4336,7 +4337,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4363,45 +4364,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132617596</v>
+        <v>132617582</v>
       </c>
       <c r="B35" t="n">
-        <v>97983</v>
+        <v>57950</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>672810</v>
+        <v>672612</v>
       </c>
       <c r="R35" t="n">
-        <v>6981546</v>
+        <v>6981238</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -4433,7 +4442,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4443,7 +4452,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4470,10 +4479,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132623274</v>
+        <v>132617596</v>
       </c>
       <c r="B36" t="n">
-        <v>101325</v>
+        <v>97983</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4481,45 +4490,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>672744</v>
+        <v>672810</v>
       </c>
       <c r="R36" t="n">
-        <v>6981271</v>
+        <v>6981546</v>
       </c>
       <c r="S36" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4548,7 +4549,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4558,7 +4559,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4567,19 +4568,18 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4800,10 +4800,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132623290</v>
+        <v>132623285</v>
       </c>
       <c r="B39" t="n">
-        <v>97983</v>
+        <v>101326</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4811,37 +4811,45 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>672621</v>
+        <v>672638</v>
       </c>
       <c r="R39" t="n">
-        <v>6981383</v>
+        <v>6981364</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4870,7 +4878,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4880,7 +4888,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4889,6 +4897,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5033,10 +5042,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132623285</v>
+        <v>132623290</v>
       </c>
       <c r="B41" t="n">
-        <v>101325</v>
+        <v>97983</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5044,45 +5053,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>672638</v>
+        <v>672621</v>
       </c>
       <c r="R41" t="n">
-        <v>6981364</v>
+        <v>6981383</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5111,7 +5112,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5121,7 +5122,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5130,7 +5131,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5149,48 +5149,51 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132617558</v>
+        <v>132617607</v>
       </c>
       <c r="B42" t="n">
-        <v>80305</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>672873</v>
+        <v>672712</v>
       </c>
       <c r="R42" t="n">
-        <v>6981339</v>
+        <v>6981164</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5219,7 +5222,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5229,7 +5232,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5238,8 +5241,24 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5256,10 +5275,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132617592</v>
+        <v>132623256</v>
       </c>
       <c r="B43" t="n">
-        <v>80392</v>
+        <v>101326</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5267,37 +5286,45 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672709</v>
+        <v>672930</v>
       </c>
       <c r="R43" t="n">
-        <v>6981488</v>
+        <v>6981133</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5326,7 +5353,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5336,7 +5363,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5345,66 +5372,64 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132617607</v>
+        <v>132617592</v>
       </c>
       <c r="B44" t="n">
-        <v>79327</v>
+        <v>80392</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672712</v>
+        <v>672709</v>
       </c>
       <c r="R44" t="n">
-        <v>6981164</v>
+        <v>6981488</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -5436,7 +5461,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5446,7 +5471,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5455,24 +5480,8 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5489,56 +5498,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132623256</v>
+        <v>132617558</v>
       </c>
       <c r="B45" t="n">
-        <v>101325</v>
+        <v>80305</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>392</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672930</v>
+        <v>672873</v>
       </c>
       <c r="R45" t="n">
-        <v>6981133</v>
+        <v>6981339</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5567,7 +5568,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5577,7 +5578,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5586,19 +5587,18 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5854,7 +5854,7 @@
         <v>132623254</v>
       </c>
       <c r="B48" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
         <v>132623294</v>
       </c>
       <c r="B49" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>132623300</v>
       </c>
       <c r="B50" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>132617546</v>
       </c>
       <c r="B51" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6306,68 +6306,56 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132617603</v>
+        <v>132623292</v>
       </c>
       <c r="B52" t="n">
-        <v>57953</v>
+        <v>101326</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672617</v>
+        <v>672655</v>
       </c>
       <c r="R52" t="n">
-        <v>6981488</v>
+        <v>6981418</v>
       </c>
       <c r="S52" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6396,7 +6384,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6406,7 +6394,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6415,64 +6403,60 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132617589</v>
+        <v>132617595</v>
       </c>
       <c r="B53" t="n">
-        <v>99118</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6480,13 +6464,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>672627</v>
+        <v>672745</v>
       </c>
       <c r="R53" t="n">
-        <v>6981425</v>
+        <v>6981544</v>
       </c>
       <c r="S53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6515,7 +6499,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6525,7 +6509,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6553,10 +6537,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132617595</v>
+        <v>132617603</v>
       </c>
       <c r="B54" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6564,44 +6548,57 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672745</v>
+        <v>672617</v>
       </c>
       <c r="R54" t="n">
-        <v>6981544</v>
+        <v>6981488</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6630,7 +6627,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6640,7 +6637,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6649,7 +6646,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6668,41 +6664,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132623292</v>
+        <v>132617589</v>
       </c>
       <c r="B55" t="n">
-        <v>101325</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672655</v>
+        <v>672627</v>
       </c>
       <c r="R55" t="n">
-        <v>6981418</v>
+        <v>6981425</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6772,12 +6772,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -7269,48 +7269,60 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132617602</v>
+        <v>132623303</v>
       </c>
       <c r="B60" t="n">
-        <v>97983</v>
+        <v>56522</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>206004</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672593</v>
+        <v>672560</v>
       </c>
       <c r="R60" t="n">
-        <v>6981519</v>
+        <v>6981577</v>
       </c>
       <c r="S60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7339,7 +7351,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7349,7 +7361,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7364,72 +7376,68 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132623303</v>
+        <v>132623265</v>
       </c>
       <c r="B61" t="n">
-        <v>56522</v>
+        <v>101326</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>206004</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672560</v>
+        <v>672872</v>
       </c>
       <c r="R61" t="n">
-        <v>6981577</v>
+        <v>6981332</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7458,7 +7466,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7468,7 +7476,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7477,6 +7485,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7495,10 +7504,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132623265</v>
+        <v>132623280</v>
       </c>
       <c r="B62" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7538,13 +7547,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>672872</v>
+        <v>672636</v>
       </c>
       <c r="R62" t="n">
-        <v>6981332</v>
+        <v>6981290</v>
       </c>
       <c r="S62" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7573,7 +7582,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7583,7 +7592,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7611,10 +7620,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132623280</v>
+        <v>132617606</v>
       </c>
       <c r="B63" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7640,27 +7649,19 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672636</v>
+        <v>672733</v>
       </c>
       <c r="R63" t="n">
-        <v>6981290</v>
+        <v>6981160</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7689,7 +7690,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7699,7 +7700,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7708,29 +7709,28 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132617606</v>
+        <v>132617602</v>
       </c>
       <c r="B64" t="n">
-        <v>101325</v>
+        <v>97983</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7738,21 +7738,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7762,10 +7762,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>672733</v>
+        <v>672593</v>
       </c>
       <c r="R64" t="n">
-        <v>6981160</v>
+        <v>6981519</v>
       </c>
       <c r="S64" t="n">
         <v>3</v>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7834,45 +7834,52 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132617574</v>
+        <v>132617591</v>
       </c>
       <c r="B65" t="n">
-        <v>91872</v>
+        <v>80432</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>672695</v>
+        <v>672709</v>
       </c>
       <c r="R65" t="n">
-        <v>6981312</v>
+        <v>6981489</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -7904,7 +7911,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7914,7 +7921,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Växandes på fyra närliggande aspträd</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7923,8 +7935,24 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -7941,52 +7969,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132617591</v>
+        <v>132617574</v>
       </c>
       <c r="B66" t="n">
-        <v>80432</v>
+        <v>91872</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>672709</v>
+        <v>672695</v>
       </c>
       <c r="R66" t="n">
-        <v>6981489</v>
+        <v>6981312</v>
       </c>
       <c r="S66" t="n">
         <v>3</v>
@@ -8018,7 +8039,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8028,12 +8049,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Växandes på fyra närliggande aspträd</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8042,24 +8058,8 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8076,10 +8076,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132617560</v>
+        <v>132617553</v>
       </c>
       <c r="B67" t="n">
-        <v>97983</v>
+        <v>101326</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8087,21 +8087,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8111,13 +8111,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>672883</v>
+        <v>672931</v>
       </c>
       <c r="R67" t="n">
-        <v>6981346</v>
+        <v>6981286</v>
       </c>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8183,10 +8183,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132617553</v>
+        <v>132617560</v>
       </c>
       <c r="B68" t="n">
-        <v>101325</v>
+        <v>97983</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8194,21 +8194,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8218,13 +8218,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>672931</v>
+        <v>672883</v>
       </c>
       <c r="R68" t="n">
-        <v>6981286</v>
+        <v>6981346</v>
       </c>
       <c r="S68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8290,10 +8290,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132617556</v>
+        <v>132623263</v>
       </c>
       <c r="B69" t="n">
-        <v>91909</v>
+        <v>79327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8301,37 +8301,40 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>672881</v>
+        <v>672878</v>
       </c>
       <c r="R69" t="n">
-        <v>6981314</v>
+        <v>6981321</v>
       </c>
       <c r="S69" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8360,7 +8363,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8370,12 +8373,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:25</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På stående död gran</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8384,28 +8382,44 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132617561</v>
+        <v>132623267</v>
       </c>
       <c r="B70" t="n">
-        <v>91909</v>
+        <v>79327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8413,37 +8427,40 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>672878</v>
+        <v>672869</v>
       </c>
       <c r="R70" t="n">
-        <v>6981375</v>
+        <v>6981357</v>
       </c>
       <c r="S70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8472,7 +8489,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8482,7 +8499,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8491,50 +8508,66 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132617598</v>
+        <v>132617584</v>
       </c>
       <c r="B71" t="n">
-        <v>92329</v>
+        <v>91872</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6040186</v>
+        <v>5447</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8544,13 +8577,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672763</v>
+        <v>672639</v>
       </c>
       <c r="R71" t="n">
-        <v>6981545</v>
+        <v>6981355</v>
       </c>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8579,7 +8612,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8589,7 +8622,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8598,24 +8631,8 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8632,10 +8649,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132623263</v>
+        <v>132617598</v>
       </c>
       <c r="B72" t="n">
-        <v>79327</v>
+        <v>92329</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8643,40 +8660,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>672878</v>
+        <v>672763</v>
       </c>
       <c r="R72" t="n">
-        <v>6981321</v>
+        <v>6981545</v>
       </c>
       <c r="S72" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8705,7 +8719,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8715,7 +8729,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8746,44 +8760,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132617584</v>
+        <v>132617556</v>
       </c>
       <c r="B73" t="n">
-        <v>91872</v>
+        <v>91909</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8793,10 +8807,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>672639</v>
+        <v>672881</v>
       </c>
       <c r="R73" t="n">
-        <v>6981355</v>
+        <v>6981314</v>
       </c>
       <c r="S73" t="n">
         <v>3</v>
@@ -8828,7 +8842,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8838,7 +8852,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På stående död gran</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8865,10 +8884,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132623267</v>
+        <v>132617561</v>
       </c>
       <c r="B74" t="n">
-        <v>79327</v>
+        <v>91909</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8876,40 +8895,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>672869</v>
+        <v>672878</v>
       </c>
       <c r="R74" t="n">
-        <v>6981357</v>
+        <v>6981375</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8938,7 +8954,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8948,7 +8964,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8957,34 +8973,18 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8994,7 +8994,7 @@
         <v>132623305</v>
       </c>
       <c r="B75" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>132623253</v>
       </c>
       <c r="B76" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9349,32 +9349,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132617575</v>
+        <v>132617552</v>
       </c>
       <c r="B78" t="n">
-        <v>57945</v>
+        <v>57950</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100110</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9382,7 +9382,7 @@
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -9392,13 +9392,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>672681</v>
+        <v>672968</v>
       </c>
       <c r="R78" t="n">
-        <v>6981300</v>
+        <v>6981202</v>
       </c>
       <c r="S78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9437,12 +9437,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Sång i över en minut.</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9469,10 +9464,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132623284</v>
+        <v>132617585</v>
       </c>
       <c r="B79" t="n">
-        <v>97983</v>
+        <v>80392</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9480,37 +9475,40 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221945</v>
+        <v>229497</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>672622</v>
+        <v>672635</v>
       </c>
       <c r="R79" t="n">
-        <v>6981351</v>
+        <v>6981376</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9539,7 +9537,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9549,7 +9547,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9558,28 +9556,44 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132623275</v>
+        <v>132623284</v>
       </c>
       <c r="B80" t="n">
-        <v>101325</v>
+        <v>97983</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9587,45 +9601,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>672670</v>
+        <v>672622</v>
       </c>
       <c r="R80" t="n">
-        <v>6981289</v>
+        <v>6981351</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9654,7 +9660,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9664,7 +9670,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9673,7 +9679,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9692,10 +9697,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132623257</v>
+        <v>132617575</v>
       </c>
       <c r="B81" t="n">
-        <v>101325</v>
+        <v>57945</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9703,31 +9708,31 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>100110</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -9735,13 +9740,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>672951</v>
+        <v>672681</v>
       </c>
       <c r="R81" t="n">
-        <v>6981191</v>
+        <v>6981300</v>
       </c>
       <c r="S81" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9770,7 +9775,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9780,7 +9785,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Sång i över en minut.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9789,61 +9799,60 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132617552</v>
+        <v>132623275</v>
       </c>
       <c r="B82" t="n">
-        <v>57950</v>
+        <v>101326</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9851,13 +9860,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>672968</v>
+        <v>672670</v>
       </c>
       <c r="R82" t="n">
-        <v>6981202</v>
+        <v>6981289</v>
       </c>
       <c r="S82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9886,7 +9895,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9896,7 +9905,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9905,28 +9914,29 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132617585</v>
+        <v>132623257</v>
       </c>
       <c r="B83" t="n">
-        <v>80392</v>
+        <v>101326</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9934,26 +9944,31 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9961,13 +9976,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>672635</v>
+        <v>672951</v>
       </c>
       <c r="R83" t="n">
-        <v>6981376</v>
+        <v>6981191</v>
       </c>
       <c r="S83" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9996,7 +10011,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10006,7 +10021,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10019,30 +10034,15 @@
       <c r="AG83" t="b">
         <v>0</v>
       </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -10160,10 +10160,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132617587</v>
+        <v>132623255</v>
       </c>
       <c r="B85" t="n">
-        <v>80392</v>
+        <v>101326</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10171,26 +10171,31 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -10198,13 +10203,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>672655</v>
+        <v>672955</v>
       </c>
       <c r="R85" t="n">
-        <v>6981378</v>
+        <v>6981134</v>
       </c>
       <c r="S85" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10233,7 +10238,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10243,7 +10248,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10256,40 +10261,25 @@
       <c r="AG85" t="b">
         <v>0</v>
       </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132623255</v>
+        <v>132617587</v>
       </c>
       <c r="B86" t="n">
-        <v>101325</v>
+        <v>80392</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10297,31 +10287,26 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -10329,13 +10314,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>672955</v>
+        <v>672655</v>
       </c>
       <c r="R86" t="n">
-        <v>6981134</v>
+        <v>6981378</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10364,7 +10349,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10374,7 +10359,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10387,15 +10372,30 @@
       <c r="AG86" t="b">
         <v>0</v>
       </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -10405,7 +10405,7 @@
         <v>132623277</v>
       </c>
       <c r="B87" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10518,10 +10518,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132617565</v>
+        <v>132617577</v>
       </c>
       <c r="B88" t="n">
-        <v>80432</v>
+        <v>91909</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10529,37 +10529,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>672833</v>
+        <v>672687</v>
       </c>
       <c r="R88" t="n">
-        <v>6981355</v>
+        <v>6981287</v>
       </c>
       <c r="S88" t="n">
         <v>3</v>
@@ -10591,7 +10588,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10601,12 +10598,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Växandes på björk.</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10615,24 +10612,8 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -10649,37 +10630,42 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132623270</v>
+        <v>132623291</v>
       </c>
       <c r="B89" t="n">
-        <v>79327</v>
+        <v>101326</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10687,10 +10673,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>672831</v>
+        <v>672630</v>
       </c>
       <c r="R89" t="n">
-        <v>6981355</v>
+        <v>6981380</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10722,7 +10708,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10732,7 +10718,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10744,21 +10730,6 @@
       <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -10775,10 +10746,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132617562</v>
+        <v>132623304</v>
       </c>
       <c r="B90" t="n">
-        <v>91872</v>
+        <v>101326</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10786,37 +10757,45 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>672869</v>
+        <v>672732</v>
       </c>
       <c r="R90" t="n">
-        <v>6981366</v>
+        <v>6981161</v>
       </c>
       <c r="S90" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10845,7 +10824,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10855,7 +10834,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10864,28 +10843,29 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132617583</v>
+        <v>132617565</v>
       </c>
       <c r="B91" t="n">
-        <v>79327</v>
+        <v>80432</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10893,34 +10873,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>672577</v>
+        <v>672833</v>
       </c>
       <c r="R91" t="n">
-        <v>6981292</v>
+        <v>6981355</v>
       </c>
       <c r="S91" t="n">
         <v>3</v>
@@ -10952,7 +10935,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10962,7 +10945,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Växandes på björk.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10971,8 +10959,24 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
@@ -10989,10 +10993,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132617577</v>
+        <v>132623270</v>
       </c>
       <c r="B92" t="n">
-        <v>91909</v>
+        <v>79327</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11000,37 +11004,40 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>672687</v>
+        <v>672831</v>
       </c>
       <c r="R92" t="n">
-        <v>6981287</v>
+        <v>6981355</v>
       </c>
       <c r="S92" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11059,7 +11066,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11069,12 +11076,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>På död stående gran</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11083,74 +11085,82 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132623291</v>
+        <v>132617583</v>
       </c>
       <c r="B93" t="n">
-        <v>101325</v>
+        <v>79327</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>672630</v>
+        <v>672577</v>
       </c>
       <c r="R93" t="n">
-        <v>6981380</v>
+        <v>6981292</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11179,7 +11189,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11189,7 +11199,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11198,29 +11208,28 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132623304</v>
+        <v>132617562</v>
       </c>
       <c r="B94" t="n">
-        <v>101325</v>
+        <v>91872</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11228,45 +11237,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>672732</v>
+        <v>672869</v>
       </c>
       <c r="R94" t="n">
-        <v>6981161</v>
+        <v>6981366</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11295,7 +11296,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11305,7 +11306,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11314,29 +11315,28 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132617563</v>
+        <v>132623258</v>
       </c>
       <c r="B95" t="n">
-        <v>97983</v>
+        <v>101326</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11344,37 +11344,45 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>672858</v>
+        <v>672971</v>
       </c>
       <c r="R95" t="n">
-        <v>6981365</v>
+        <v>6981202</v>
       </c>
       <c r="S95" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11403,7 +11411,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11413,7 +11421,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11422,28 +11430,29 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132617570</v>
+        <v>132623273</v>
       </c>
       <c r="B96" t="n">
-        <v>97983</v>
+        <v>101326</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11451,37 +11460,45 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>672723</v>
+        <v>672774</v>
       </c>
       <c r="R96" t="n">
-        <v>6981408</v>
+        <v>6981240</v>
       </c>
       <c r="S96" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11510,7 +11527,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11520,7 +11537,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11529,28 +11546,29 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132623258</v>
+        <v>132617563</v>
       </c>
       <c r="B97" t="n">
-        <v>101325</v>
+        <v>97983</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11558,45 +11576,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>672971</v>
+        <v>672858</v>
       </c>
       <c r="R97" t="n">
-        <v>6981202</v>
+        <v>6981365</v>
       </c>
       <c r="S97" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11625,7 +11635,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11635,7 +11645,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11644,29 +11654,28 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132623273</v>
+        <v>132617570</v>
       </c>
       <c r="B98" t="n">
-        <v>101325</v>
+        <v>97983</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11674,45 +11683,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>672774</v>
+        <v>672723</v>
       </c>
       <c r="R98" t="n">
-        <v>6981240</v>
+        <v>6981408</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11741,7 +11742,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11751,7 +11752,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11760,19 +11761,18 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>

--- a/artfynd/A 13423-2026 artfynd.xlsx
+++ b/artfynd/A 13423-2026 artfynd.xlsx
@@ -2357,32 +2357,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132617581</v>
+        <v>132617590</v>
       </c>
       <c r="B17" t="n">
-        <v>91872</v>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672612</v>
+        <v>672706</v>
       </c>
       <c r="R17" t="n">
-        <v>6981244</v>
+        <v>6981525</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2464,32 +2464,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132617590</v>
+        <v>132617581</v>
       </c>
       <c r="B18" t="n">
-        <v>91909</v>
+        <v>91872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672706</v>
+        <v>672612</v>
       </c>
       <c r="R18" t="n">
-        <v>6981525</v>
+        <v>6981244</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2571,10 +2571,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132617593</v>
+        <v>132623302</v>
       </c>
       <c r="B19" t="n">
-        <v>91872</v>
+        <v>101326</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,37 +2582,45 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672724</v>
+        <v>672746</v>
       </c>
       <c r="R19" t="n">
-        <v>6981448</v>
+        <v>6981560</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2641,7 +2649,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2651,7 +2659,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2660,28 +2668,29 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132617588</v>
+        <v>132617600</v>
       </c>
       <c r="B20" t="n">
-        <v>91872</v>
+        <v>101326</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2689,21 +2698,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2713,13 +2722,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>672671</v>
+        <v>672651</v>
       </c>
       <c r="R20" t="n">
-        <v>6981418</v>
+        <v>6981546</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2748,7 +2757,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2758,7 +2767,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2785,10 +2794,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132617548</v>
+        <v>132623268</v>
       </c>
       <c r="B21" t="n">
-        <v>91872</v>
+        <v>101326</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,37 +2805,45 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>672935</v>
+        <v>672837</v>
       </c>
       <c r="R21" t="n">
-        <v>6981231</v>
+        <v>6981360</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2855,7 +2872,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2865,7 +2882,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2874,28 +2891,29 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132623302</v>
+        <v>132617593</v>
       </c>
       <c r="B22" t="n">
-        <v>101326</v>
+        <v>91872</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2903,45 +2921,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>672746</v>
+        <v>672724</v>
       </c>
       <c r="R22" t="n">
-        <v>6981560</v>
+        <v>6981448</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2970,7 +2980,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2980,7 +2990,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2989,29 +2999,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132617600</v>
+        <v>132617588</v>
       </c>
       <c r="B23" t="n">
-        <v>101326</v>
+        <v>91872</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3019,21 +3028,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3043,13 +3052,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672651</v>
+        <v>672671</v>
       </c>
       <c r="R23" t="n">
-        <v>6981546</v>
+        <v>6981418</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3078,7 +3087,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3088,7 +3097,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3115,10 +3124,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132623268</v>
+        <v>132617548</v>
       </c>
       <c r="B24" t="n">
-        <v>101326</v>
+        <v>91872</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3126,45 +3135,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>672837</v>
+        <v>672935</v>
       </c>
       <c r="R24" t="n">
-        <v>6981360</v>
+        <v>6981231</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3193,7 +3194,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3203,7 +3204,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3212,19 +3213,18 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -5275,56 +5275,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132623256</v>
+        <v>132617558</v>
       </c>
       <c r="B43" t="n">
-        <v>101326</v>
+        <v>80305</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>392</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672930</v>
+        <v>672873</v>
       </c>
       <c r="R43" t="n">
-        <v>6981133</v>
+        <v>6981339</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5353,7 +5345,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5363,7 +5355,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5372,29 +5364,28 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132617592</v>
+        <v>132623256</v>
       </c>
       <c r="B44" t="n">
-        <v>80392</v>
+        <v>101326</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5402,37 +5393,45 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672709</v>
+        <v>672930</v>
       </c>
       <c r="R44" t="n">
-        <v>6981488</v>
+        <v>6981133</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5461,7 +5460,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5471,7 +5470,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5480,50 +5479,51 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132617558</v>
+        <v>132617592</v>
       </c>
       <c r="B45" t="n">
-        <v>80305</v>
+        <v>80392</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>392</v>
+        <v>229497</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5533,13 +5533,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672873</v>
+        <v>672709</v>
       </c>
       <c r="R45" t="n">
-        <v>6981339</v>
+        <v>6981488</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5605,37 +5605,42 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132617567</v>
+        <v>132623254</v>
       </c>
       <c r="B46" t="n">
-        <v>80432</v>
+        <v>101326</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5643,13 +5648,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>672776</v>
+        <v>672976</v>
       </c>
       <c r="R46" t="n">
-        <v>6981332</v>
+        <v>6981122</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5678,7 +5683,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5688,7 +5693,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5701,72 +5706,57 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132617576</v>
+        <v>132623294</v>
       </c>
       <c r="B47" t="n">
-        <v>57953</v>
+        <v>101326</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5774,13 +5764,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>672684</v>
+        <v>672601</v>
       </c>
       <c r="R47" t="n">
-        <v>6981289</v>
+        <v>6981439</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5809,7 +5799,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5819,12 +5809,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5833,25 +5818,26 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132623254</v>
+        <v>132623300</v>
       </c>
       <c r="B48" t="n">
         <v>101326</v>
@@ -5894,13 +5880,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>672976</v>
+        <v>672758</v>
       </c>
       <c r="R48" t="n">
-        <v>6981122</v>
+        <v>6981513</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5929,7 +5915,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5939,7 +5925,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5967,7 +5953,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132623294</v>
+        <v>132617546</v>
       </c>
       <c r="B49" t="n">
         <v>101326</v>
@@ -5996,27 +5982,19 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672601</v>
+        <v>672949</v>
       </c>
       <c r="R49" t="n">
-        <v>6981439</v>
+        <v>6981130</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6045,7 +6023,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6055,7 +6033,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6064,61 +6042,55 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132623300</v>
+        <v>132617567</v>
       </c>
       <c r="B50" t="n">
-        <v>101326</v>
+        <v>80432</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6126,13 +6098,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>672758</v>
+        <v>672776</v>
       </c>
       <c r="R50" t="n">
-        <v>6981513</v>
+        <v>6981332</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6161,7 +6133,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6171,7 +6143,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6184,60 +6156,83 @@
       <c r="AG50" t="b">
         <v>0</v>
       </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132617546</v>
+        <v>132617576</v>
       </c>
       <c r="B51" t="n">
-        <v>101326</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672949</v>
+        <v>672684</v>
       </c>
       <c r="R51" t="n">
-        <v>6981130</v>
+        <v>6981289</v>
       </c>
       <c r="S51" t="n">
         <v>3</v>
@@ -6269,7 +6264,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6279,7 +6274,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6306,56 +6306,68 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132623292</v>
+        <v>132617603</v>
       </c>
       <c r="B52" t="n">
-        <v>101326</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672655</v>
+        <v>672617</v>
       </c>
       <c r="R52" t="n">
-        <v>6981418</v>
+        <v>6981488</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6384,7 +6396,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6394,7 +6406,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6403,19 +6415,18 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6537,65 +6548,57 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132617603</v>
+        <v>132617589</v>
       </c>
       <c r="B54" t="n">
-        <v>57953</v>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672617</v>
+        <v>672627</v>
       </c>
       <c r="R54" t="n">
-        <v>6981488</v>
+        <v>6981425</v>
       </c>
       <c r="S54" t="n">
         <v>2</v>
@@ -6627,7 +6630,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6637,7 +6640,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6646,6 +6649,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6664,45 +6668,41 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132617589</v>
+        <v>132623292</v>
       </c>
       <c r="B55" t="n">
-        <v>99118</v>
+        <v>101326</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672627</v>
+        <v>672655</v>
       </c>
       <c r="R55" t="n">
-        <v>6981425</v>
+        <v>6981418</v>
       </c>
       <c r="S55" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6772,12 +6772,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6910,48 +6910,56 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132617555</v>
+        <v>132623265</v>
       </c>
       <c r="B57" t="n">
-        <v>79327</v>
+        <v>101326</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>672921</v>
+        <v>672872</v>
       </c>
       <c r="R57" t="n">
-        <v>6981328</v>
+        <v>6981332</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6980,7 +6988,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6990,7 +6998,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6999,55 +7007,61 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132617549</v>
+        <v>132623280</v>
       </c>
       <c r="B58" t="n">
-        <v>80432</v>
+        <v>101326</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7055,13 +7069,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>672932</v>
+        <v>672636</v>
       </c>
       <c r="R58" t="n">
-        <v>6981224</v>
+        <v>6981290</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7090,7 +7104,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7100,7 +7114,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7113,81 +7127,63 @@
       <c r="AG58" t="b">
         <v>0</v>
       </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132623271</v>
+        <v>132617606</v>
       </c>
       <c r="B59" t="n">
-        <v>80432</v>
+        <v>101326</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>672780</v>
+        <v>672733</v>
       </c>
       <c r="R59" t="n">
-        <v>6981331</v>
+        <v>6981160</v>
       </c>
       <c r="S59" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7216,7 +7212,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7226,7 +7222,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7235,44 +7231,28 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132623303</v>
+        <v>132617555</v>
       </c>
       <c r="B60" t="n">
-        <v>56522</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7280,49 +7260,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672560</v>
+        <v>672921</v>
       </c>
       <c r="R60" t="n">
-        <v>6981577</v>
+        <v>6981328</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7351,7 +7319,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7361,7 +7329,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7376,54 +7344,49 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132623265</v>
+        <v>132617549</v>
       </c>
       <c r="B61" t="n">
-        <v>101326</v>
+        <v>80432</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7431,13 +7394,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672872</v>
+        <v>672932</v>
       </c>
       <c r="R61" t="n">
-        <v>6981332</v>
+        <v>6981224</v>
       </c>
       <c r="S61" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7466,7 +7429,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7476,7 +7439,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7489,57 +7452,67 @@
       <c r="AG61" t="b">
         <v>0</v>
       </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132623280</v>
+        <v>132623271</v>
       </c>
       <c r="B62" t="n">
-        <v>101326</v>
+        <v>80432</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7547,13 +7520,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>672636</v>
+        <v>672780</v>
       </c>
       <c r="R62" t="n">
-        <v>6981290</v>
+        <v>6981331</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7582,7 +7555,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7592,7 +7565,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7605,6 +7578,21 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
@@ -7613,55 +7601,67 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132617606</v>
+        <v>132623303</v>
       </c>
       <c r="B63" t="n">
-        <v>101326</v>
+        <v>56522</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>206004</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672733</v>
+        <v>672560</v>
       </c>
       <c r="R63" t="n">
-        <v>6981160</v>
+        <v>6981577</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7700,7 +7700,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7715,12 +7715,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -8542,32 +8542,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132617584</v>
+        <v>132617556</v>
       </c>
       <c r="B71" t="n">
-        <v>91872</v>
+        <v>91909</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8577,10 +8577,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672639</v>
+        <v>672881</v>
       </c>
       <c r="R71" t="n">
-        <v>6981355</v>
+        <v>6981314</v>
       </c>
       <c r="S71" t="n">
         <v>3</v>
@@ -8612,7 +8612,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8622,7 +8622,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På stående död gran</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8649,10 +8654,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132617598</v>
+        <v>132617561</v>
       </c>
       <c r="B72" t="n">
-        <v>92329</v>
+        <v>91909</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8660,21 +8665,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6040186</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8684,13 +8689,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>672763</v>
+        <v>672878</v>
       </c>
       <c r="R72" t="n">
-        <v>6981545</v>
+        <v>6981375</v>
       </c>
       <c r="S72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8719,7 +8724,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8729,7 +8734,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8738,24 +8743,8 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8772,10 +8761,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132617556</v>
+        <v>132617598</v>
       </c>
       <c r="B73" t="n">
-        <v>91909</v>
+        <v>92329</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8783,21 +8772,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6040186</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8807,13 +8796,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>672881</v>
+        <v>672763</v>
       </c>
       <c r="R73" t="n">
-        <v>6981314</v>
+        <v>6981545</v>
       </c>
       <c r="S73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8842,7 +8831,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8852,12 +8841,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:25</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På stående död gran</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8866,8 +8850,24 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8884,32 +8884,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132617561</v>
+        <v>132617584</v>
       </c>
       <c r="B74" t="n">
-        <v>91909</v>
+        <v>91872</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8919,10 +8919,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>672878</v>
+        <v>672639</v>
       </c>
       <c r="R74" t="n">
-        <v>6981375</v>
+        <v>6981355</v>
       </c>
       <c r="S74" t="n">
         <v>3</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8964,7 +8964,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10049,37 +10049,42 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132617594</v>
+        <v>132623255</v>
       </c>
       <c r="B84" t="n">
-        <v>91909</v>
+        <v>101326</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -10087,13 +10092,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>672755</v>
+        <v>672955</v>
       </c>
       <c r="R84" t="n">
-        <v>6981496</v>
+        <v>6981134</v>
       </c>
       <c r="S84" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10122,7 +10127,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10132,7 +10137,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10148,22 +10153,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132623255</v>
+        <v>132617587</v>
       </c>
       <c r="B85" t="n">
-        <v>101326</v>
+        <v>80392</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10171,31 +10176,26 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -10203,13 +10203,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>672955</v>
+        <v>672655</v>
       </c>
       <c r="R85" t="n">
-        <v>6981134</v>
+        <v>6981378</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10261,47 +10261,62 @@
       <c r="AG85" t="b">
         <v>0</v>
       </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132617587</v>
+        <v>132617594</v>
       </c>
       <c r="B86" t="n">
-        <v>80392</v>
+        <v>91909</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10314,10 +10329,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>672655</v>
+        <v>672755</v>
       </c>
       <c r="R86" t="n">
-        <v>6981378</v>
+        <v>6981496</v>
       </c>
       <c r="S86" t="n">
         <v>3</v>
@@ -10349,7 +10364,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10359,7 +10374,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10371,21 +10386,6 @@
       <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -10518,10 +10518,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132617577</v>
+        <v>132617565</v>
       </c>
       <c r="B88" t="n">
-        <v>91909</v>
+        <v>80432</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10529,34 +10529,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>672687</v>
+        <v>672833</v>
       </c>
       <c r="R88" t="n">
-        <v>6981287</v>
+        <v>6981355</v>
       </c>
       <c r="S88" t="n">
         <v>3</v>
@@ -10588,7 +10591,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10598,12 +10601,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>Växandes på björk.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10612,8 +10615,24 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -10630,42 +10649,37 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132623291</v>
+        <v>132623270</v>
       </c>
       <c r="B89" t="n">
-        <v>101326</v>
+        <v>79327</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10673,10 +10687,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>672630</v>
+        <v>672831</v>
       </c>
       <c r="R89" t="n">
-        <v>6981380</v>
+        <v>6981355</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10708,7 +10722,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10718,7 +10732,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10730,6 +10744,21 @@
       <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -10746,56 +10775,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132623304</v>
+        <v>132617583</v>
       </c>
       <c r="B90" t="n">
-        <v>101326</v>
+        <v>79327</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>672732</v>
+        <v>672577</v>
       </c>
       <c r="R90" t="n">
-        <v>6981161</v>
+        <v>6981292</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10824,7 +10845,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10834,7 +10855,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10843,29 +10864,28 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132617565</v>
+        <v>132617577</v>
       </c>
       <c r="B91" t="n">
-        <v>80432</v>
+        <v>91909</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10873,37 +10893,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>672833</v>
+        <v>672687</v>
       </c>
       <c r="R91" t="n">
-        <v>6981355</v>
+        <v>6981287</v>
       </c>
       <c r="S91" t="n">
         <v>3</v>
@@ -10935,7 +10952,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10945,12 +10962,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Växandes på björk.</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10959,24 +10976,8 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
@@ -10993,37 +10994,42 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132623270</v>
+        <v>132623291</v>
       </c>
       <c r="B92" t="n">
-        <v>79327</v>
+        <v>101326</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -11031,10 +11037,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>672831</v>
+        <v>672630</v>
       </c>
       <c r="R92" t="n">
-        <v>6981355</v>
+        <v>6981380</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -11066,7 +11072,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11076,7 +11082,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11088,21 +11094,6 @@
       <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -11119,48 +11110,56 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132617583</v>
+        <v>132623304</v>
       </c>
       <c r="B93" t="n">
-        <v>79327</v>
+        <v>101326</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>672577</v>
+        <v>672732</v>
       </c>
       <c r="R93" t="n">
-        <v>6981292</v>
+        <v>6981161</v>
       </c>
       <c r="S93" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11189,7 +11188,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11199,7 +11198,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11208,18 +11207,19 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>

--- a/artfynd/A 13423-2026 artfynd.xlsx
+++ b/artfynd/A 13423-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132617547</v>
+        <v>132617578</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>91910</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672932</v>
+        <v>672651</v>
       </c>
       <c r="R2" t="n">
-        <v>6981174</v>
+        <v>6981280</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +785,7 @@
         <v>132617597</v>
       </c>
       <c r="B3" t="n">
-        <v>91872</v>
+        <v>91873</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132617578</v>
+        <v>132617547</v>
       </c>
       <c r="B4" t="n">
-        <v>91909</v>
+        <v>79328</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672651</v>
+        <v>672932</v>
       </c>
       <c r="R4" t="n">
-        <v>6981280</v>
+        <v>6981174</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132617551</v>
+        <v>132617572</v>
       </c>
       <c r="B5" t="n">
-        <v>91909</v>
+        <v>57951</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,34 +1007,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>672976</v>
+        <v>672701</v>
       </c>
       <c r="R5" t="n">
-        <v>6981217</v>
+        <v>6981350</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1066,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1084,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132617572</v>
+        <v>132617551</v>
       </c>
       <c r="B6" t="n">
-        <v>57950</v>
+        <v>91910</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,42 +1122,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>672701</v>
+        <v>672976</v>
       </c>
       <c r="R6" t="n">
-        <v>6981350</v>
+        <v>6981217</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,7 +1221,7 @@
         <v>132623293</v>
       </c>
       <c r="B7" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>132623296</v>
       </c>
       <c r="B8" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>132623279</v>
       </c>
       <c r="B9" t="n">
-        <v>97983</v>
+        <v>97984</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,45 +1557,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132617579</v>
+        <v>132617550</v>
       </c>
       <c r="B10" t="n">
-        <v>91872</v>
+        <v>57951</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672651</v>
+        <v>672983</v>
       </c>
       <c r="R10" t="n">
-        <v>6981280</v>
+        <v>6981247</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1627,7 +1635,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1637,7 +1645,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,61 +1672,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132617605</v>
+        <v>132617579</v>
       </c>
       <c r="B11" t="n">
-        <v>57953</v>
+        <v>91873</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672801</v>
+        <v>672651</v>
       </c>
       <c r="R11" t="n">
-        <v>6981249</v>
+        <v>6981280</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1750,7 +1742,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1760,12 +1752,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Två födosökande individer varav en hona</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1792,10 +1779,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132617571</v>
+        <v>132617605</v>
       </c>
       <c r="B12" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,28 +1807,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672713</v>
+        <v>672801</v>
       </c>
       <c r="R12" t="n">
-        <v>6981357</v>
+        <v>6981249</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,12 +1875,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Två födosökande individer varav en hona</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132617554</v>
+        <v>132617571</v>
       </c>
       <c r="B13" t="n">
-        <v>91909</v>
+        <v>57954</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,37 +1918,45 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672912</v>
+        <v>672713</v>
       </c>
       <c r="R13" t="n">
-        <v>6981315</v>
+        <v>6981357</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1982,7 +1985,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1995,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2027,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132617550</v>
+        <v>132617554</v>
       </c>
       <c r="B14" t="n">
-        <v>57950</v>
+        <v>91910</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,42 +2038,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672983</v>
+        <v>672912</v>
       </c>
       <c r="R14" t="n">
-        <v>6981247</v>
+        <v>6981315</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2134,10 +2134,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132623282</v>
+        <v>132623301</v>
       </c>
       <c r="B15" t="n">
-        <v>101326</v>
+        <v>97984</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,42 +2145,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672633</v>
+        <v>672767</v>
       </c>
       <c r="R15" t="n">
-        <v>6981324</v>
+        <v>6981492</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2212,7 +2204,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2222,7 +2214,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,7 +2223,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2250,10 +2241,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132623301</v>
+        <v>132623282</v>
       </c>
       <c r="B16" t="n">
-        <v>97983</v>
+        <v>101327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,34 +2252,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672767</v>
+        <v>672633</v>
       </c>
       <c r="R16" t="n">
-        <v>6981492</v>
+        <v>6981324</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2320,7 +2319,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2330,7 +2329,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2339,6 +2338,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2360,7 +2360,7 @@
         <v>132617590</v>
       </c>
       <c r="B17" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>132617581</v>
       </c>
       <c r="B18" t="n">
-        <v>91872</v>
+        <v>91873</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2571,10 +2571,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132623302</v>
+        <v>132617601</v>
       </c>
       <c r="B19" t="n">
-        <v>101326</v>
+        <v>80393</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,31 +2582,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2614,13 +2609,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672746</v>
+        <v>672548</v>
       </c>
       <c r="R19" t="n">
-        <v>6981560</v>
+        <v>6981599</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2649,7 +2644,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2659,7 +2654,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2672,25 +2667,40 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132617600</v>
+        <v>132617593</v>
       </c>
       <c r="B20" t="n">
-        <v>101326</v>
+        <v>91873</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2698,21 +2708,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2722,13 +2732,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>672651</v>
+        <v>672724</v>
       </c>
       <c r="R20" t="n">
-        <v>6981546</v>
+        <v>6981448</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2757,7 +2767,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2767,7 +2777,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2794,10 +2804,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132623268</v>
+        <v>132617588</v>
       </c>
       <c r="B21" t="n">
-        <v>101326</v>
+        <v>91873</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2805,45 +2815,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>672837</v>
+        <v>672671</v>
       </c>
       <c r="R21" t="n">
-        <v>6981360</v>
+        <v>6981418</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2872,7 +2874,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2882,7 +2884,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2891,29 +2893,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132617593</v>
+        <v>132617548</v>
       </c>
       <c r="B22" t="n">
-        <v>91872</v>
+        <v>91873</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,13 +2946,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>672724</v>
+        <v>672935</v>
       </c>
       <c r="R22" t="n">
-        <v>6981448</v>
+        <v>6981231</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2980,7 +2981,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2990,7 +2991,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3017,10 +3018,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132617588</v>
+        <v>132623302</v>
       </c>
       <c r="B23" t="n">
-        <v>91872</v>
+        <v>101327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3028,37 +3029,45 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672671</v>
+        <v>672746</v>
       </c>
       <c r="R23" t="n">
-        <v>6981418</v>
+        <v>6981560</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3087,7 +3096,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3097,7 +3106,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3106,28 +3115,29 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132617548</v>
+        <v>132617600</v>
       </c>
       <c r="B24" t="n">
-        <v>91872</v>
+        <v>101327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3135,21 +3145,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3159,10 +3169,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>672935</v>
+        <v>672651</v>
       </c>
       <c r="R24" t="n">
-        <v>6981231</v>
+        <v>6981546</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3194,7 +3204,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3204,7 +3214,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3231,10 +3241,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132617601</v>
+        <v>132623268</v>
       </c>
       <c r="B25" t="n">
-        <v>80392</v>
+        <v>101327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3242,26 +3252,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3269,13 +3284,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>672548</v>
+        <v>672837</v>
       </c>
       <c r="R25" t="n">
-        <v>6981599</v>
+        <v>6981360</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3304,7 +3319,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3314,7 +3329,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3327,40 +3342,25 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132617604</v>
+        <v>132617580</v>
       </c>
       <c r="B26" t="n">
-        <v>57953</v>
+        <v>91910</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3368,54 +3368,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>672698</v>
+        <v>672623</v>
       </c>
       <c r="R26" t="n">
-        <v>6981511</v>
+        <v>6981252</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3447,7 +3427,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3457,7 +3437,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3484,45 +3464,65 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132617568</v>
+        <v>132617604</v>
       </c>
       <c r="B27" t="n">
-        <v>97983</v>
+        <v>57954</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>672748</v>
+        <v>672698</v>
       </c>
       <c r="R27" t="n">
-        <v>6981368</v>
+        <v>6981511</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3591,10 +3591,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132623266</v>
+        <v>132623295</v>
       </c>
       <c r="B28" t="n">
-        <v>97977</v>
+        <v>101327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3602,33 +3602,45 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221944</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>672878</v>
+        <v>672594</v>
       </c>
       <c r="R28" t="n">
-        <v>6981334</v>
+        <v>6981486</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3657,7 +3669,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3667,7 +3679,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3688,55 +3700,63 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132617580</v>
+        <v>132623272</v>
       </c>
       <c r="B29" t="n">
-        <v>91909</v>
+        <v>101327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672623</v>
+        <v>672787</v>
       </c>
       <c r="R29" t="n">
-        <v>6981252</v>
+        <v>6981316</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3765,7 +3785,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3775,7 +3795,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3784,28 +3804,29 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132623295</v>
+        <v>132617568</v>
       </c>
       <c r="B30" t="n">
-        <v>101326</v>
+        <v>97984</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3813,45 +3834,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672594</v>
+        <v>672748</v>
       </c>
       <c r="R30" t="n">
-        <v>6981486</v>
+        <v>6981368</v>
       </c>
       <c r="S30" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3880,7 +3893,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3890,7 +3903,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3899,29 +3912,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132623272</v>
+        <v>132623266</v>
       </c>
       <c r="B31" t="n">
-        <v>101326</v>
+        <v>97978</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3929,45 +3941,33 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>221944</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>672787</v>
+        <v>672878</v>
       </c>
       <c r="R31" t="n">
-        <v>6981316</v>
+        <v>6981334</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4037,7 +4037,7 @@
         <v>132623278</v>
       </c>
       <c r="B32" t="n">
-        <v>97983</v>
+        <v>97984</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4141,42 +4141,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132623274</v>
+        <v>132617582</v>
       </c>
       <c r="B33" t="n">
-        <v>101326</v>
+        <v>57951</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4184,13 +4184,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>672744</v>
+        <v>672612</v>
       </c>
       <c r="R33" t="n">
-        <v>6981271</v>
+        <v>6981238</v>
       </c>
       <c r="S33" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4238,19 +4238,18 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4260,7 +4259,7 @@
         <v>132617586</v>
       </c>
       <c r="B34" t="n">
-        <v>91872</v>
+        <v>91873</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4364,53 +4363,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132617582</v>
+        <v>132617596</v>
       </c>
       <c r="B35" t="n">
-        <v>57950</v>
+        <v>97984</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>672612</v>
+        <v>672810</v>
       </c>
       <c r="R35" t="n">
-        <v>6981238</v>
+        <v>6981546</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -4442,7 +4433,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4452,7 +4443,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4479,10 +4470,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132617596</v>
+        <v>132623274</v>
       </c>
       <c r="B36" t="n">
-        <v>97983</v>
+        <v>101327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4490,37 +4481,45 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>672810</v>
+        <v>672744</v>
       </c>
       <c r="R36" t="n">
-        <v>6981546</v>
+        <v>6981271</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4549,7 +4548,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4559,7 +4558,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4568,28 +4567,29 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132617564</v>
+        <v>132617599</v>
       </c>
       <c r="B37" t="n">
-        <v>80432</v>
+        <v>79328</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4597,21 +4597,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4621,10 +4621,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>672831</v>
+        <v>672664</v>
       </c>
       <c r="R37" t="n">
-        <v>6981363</v>
+        <v>6981552</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4693,32 +4693,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132617599</v>
+        <v>132623290</v>
       </c>
       <c r="B38" t="n">
-        <v>79327</v>
+        <v>97984</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4728,13 +4728,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672664</v>
+        <v>672621</v>
       </c>
       <c r="R38" t="n">
-        <v>6981552</v>
+        <v>6981383</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4788,12 +4788,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4803,7 +4803,7 @@
         <v>132623285</v>
       </c>
       <c r="B39" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4916,48 +4916,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132617557</v>
+        <v>132617564</v>
       </c>
       <c r="B40" t="n">
-        <v>80392</v>
+        <v>80433</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672878</v>
+        <v>672831</v>
       </c>
       <c r="R40" t="n">
-        <v>6981324</v>
+        <v>6981363</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -4989,7 +4986,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4999,7 +4996,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5008,24 +5005,8 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5042,10 +5023,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132623290</v>
+        <v>132617557</v>
       </c>
       <c r="B41" t="n">
-        <v>97983</v>
+        <v>80393</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5053,37 +5034,40 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>229497</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>672621</v>
+        <v>672878</v>
       </c>
       <c r="R41" t="n">
-        <v>6981383</v>
+        <v>6981324</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5112,7 +5096,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5122,7 +5106,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5131,55 +5115,76 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132617607</v>
+        <v>132623256</v>
       </c>
       <c r="B42" t="n">
-        <v>79327</v>
+        <v>101327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5187,13 +5192,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>672712</v>
+        <v>672930</v>
       </c>
       <c r="R42" t="n">
-        <v>6981164</v>
+        <v>6981133</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5222,7 +5227,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5232,7 +5237,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5245,62 +5250,47 @@
       <c r="AG42" t="b">
         <v>0</v>
       </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132617558</v>
+        <v>132617592</v>
       </c>
       <c r="B43" t="n">
-        <v>80305</v>
+        <v>80393</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>392</v>
+        <v>229497</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5310,13 +5300,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672873</v>
+        <v>672709</v>
       </c>
       <c r="R43" t="n">
-        <v>6981339</v>
+        <v>6981488</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5345,7 +5335,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5355,7 +5345,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5382,56 +5372,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132623256</v>
+        <v>132617558</v>
       </c>
       <c r="B44" t="n">
-        <v>101326</v>
+        <v>80306</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>392</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672930</v>
+        <v>672873</v>
       </c>
       <c r="R44" t="n">
-        <v>6981133</v>
+        <v>6981339</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5460,7 +5442,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5470,7 +5452,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5479,64 +5461,66 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132617592</v>
+        <v>132617607</v>
       </c>
       <c r="B45" t="n">
-        <v>80392</v>
+        <v>79328</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672709</v>
+        <v>672712</v>
       </c>
       <c r="R45" t="n">
-        <v>6981488</v>
+        <v>6981164</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -5568,7 +5552,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5578,7 +5562,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5587,8 +5571,24 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5605,42 +5605,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132623254</v>
+        <v>132617567</v>
       </c>
       <c r="B46" t="n">
-        <v>101326</v>
+        <v>80433</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5648,13 +5643,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>672976</v>
+        <v>672776</v>
       </c>
       <c r="R46" t="n">
-        <v>6981122</v>
+        <v>6981332</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5683,7 +5678,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5693,7 +5688,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5706,57 +5701,72 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132623294</v>
+        <v>132617576</v>
       </c>
       <c r="B47" t="n">
-        <v>101326</v>
+        <v>57954</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5764,13 +5774,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>672601</v>
+        <v>672684</v>
       </c>
       <c r="R47" t="n">
-        <v>6981439</v>
+        <v>6981289</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5799,7 +5809,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5809,7 +5819,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5818,29 +5833,28 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132623300</v>
+        <v>132623254</v>
       </c>
       <c r="B48" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5880,13 +5894,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>672758</v>
+        <v>672976</v>
       </c>
       <c r="R48" t="n">
-        <v>6981513</v>
+        <v>6981122</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5915,7 +5929,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5925,7 +5939,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5953,10 +5967,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132617546</v>
+        <v>132623294</v>
       </c>
       <c r="B49" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5982,19 +5996,27 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672949</v>
+        <v>672601</v>
       </c>
       <c r="R49" t="n">
-        <v>6981130</v>
+        <v>6981439</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6023,7 +6045,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6033,7 +6055,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6042,55 +6064,61 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132617567</v>
+        <v>132623300</v>
       </c>
       <c r="B50" t="n">
-        <v>80432</v>
+        <v>101327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6098,13 +6126,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>672776</v>
+        <v>672758</v>
       </c>
       <c r="R50" t="n">
-        <v>6981332</v>
+        <v>6981513</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6133,7 +6161,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6143,7 +6171,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6156,83 +6184,60 @@
       <c r="AG50" t="b">
         <v>0</v>
       </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132617576</v>
+        <v>132617546</v>
       </c>
       <c r="B51" t="n">
-        <v>57953</v>
+        <v>101327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672684</v>
+        <v>672949</v>
       </c>
       <c r="R51" t="n">
-        <v>6981289</v>
+        <v>6981130</v>
       </c>
       <c r="S51" t="n">
         <v>3</v>
@@ -6264,7 +6269,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6274,12 +6279,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6306,68 +6306,56 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132617603</v>
+        <v>132623292</v>
       </c>
       <c r="B52" t="n">
-        <v>57953</v>
+        <v>101327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672617</v>
+        <v>672655</v>
       </c>
       <c r="R52" t="n">
-        <v>6981488</v>
+        <v>6981418</v>
       </c>
       <c r="S52" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6396,7 +6384,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6406,7 +6394,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6415,18 +6403,19 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6436,7 +6425,7 @@
         <v>132617595</v>
       </c>
       <c r="B53" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6548,57 +6537,65 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132617589</v>
+        <v>132617603</v>
       </c>
       <c r="B54" t="n">
-        <v>99118</v>
+        <v>57954</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672627</v>
+        <v>672617</v>
       </c>
       <c r="R54" t="n">
-        <v>6981425</v>
+        <v>6981488</v>
       </c>
       <c r="S54" t="n">
         <v>2</v>
@@ -6630,7 +6627,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6640,7 +6637,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6649,7 +6646,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6668,41 +6664,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132623292</v>
+        <v>132617589</v>
       </c>
       <c r="B55" t="n">
-        <v>101326</v>
+        <v>99119</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672655</v>
+        <v>672627</v>
       </c>
       <c r="R55" t="n">
-        <v>6981418</v>
+        <v>6981425</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6772,12 +6772,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6787,7 +6787,7 @@
         <v>132617566</v>
       </c>
       <c r="B56" t="n">
-        <v>80392</v>
+        <v>80393</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6910,56 +6910,60 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132623265</v>
+        <v>132623303</v>
       </c>
       <c r="B57" t="n">
-        <v>101326</v>
+        <v>56522</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>206004</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>672872</v>
+        <v>672560</v>
       </c>
       <c r="R57" t="n">
-        <v>6981332</v>
+        <v>6981577</v>
       </c>
       <c r="S57" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6988,7 +6992,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6998,7 +7002,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7007,7 +7011,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7026,10 +7029,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132623280</v>
+        <v>132617602</v>
       </c>
       <c r="B58" t="n">
-        <v>101326</v>
+        <v>97984</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7037,45 +7040,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>672636</v>
+        <v>672593</v>
       </c>
       <c r="R58" t="n">
-        <v>6981290</v>
+        <v>6981519</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7104,7 +7099,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7114,7 +7109,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7123,29 +7118,28 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132617606</v>
+        <v>132623265</v>
       </c>
       <c r="B59" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7171,19 +7165,27 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>672733</v>
+        <v>672872</v>
       </c>
       <c r="R59" t="n">
-        <v>6981160</v>
+        <v>6981332</v>
       </c>
       <c r="S59" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7212,7 +7214,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7222,7 +7224,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7231,66 +7233,75 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132617555</v>
+        <v>132623280</v>
       </c>
       <c r="B60" t="n">
-        <v>79327</v>
+        <v>101327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672921</v>
+        <v>672636</v>
       </c>
       <c r="R60" t="n">
-        <v>6981328</v>
+        <v>6981290</v>
       </c>
       <c r="S60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7319,7 +7330,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7329,7 +7340,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7338,66 +7349,64 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132617549</v>
+        <v>132617606</v>
       </c>
       <c r="B61" t="n">
-        <v>80432</v>
+        <v>101327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672932</v>
+        <v>672733</v>
       </c>
       <c r="R61" t="n">
-        <v>6981224</v>
+        <v>6981160</v>
       </c>
       <c r="S61" t="n">
         <v>3</v>
@@ -7429,7 +7438,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7439,7 +7448,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7448,24 +7457,8 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7485,7 +7478,7 @@
         <v>132623271</v>
       </c>
       <c r="B62" t="n">
-        <v>80432</v>
+        <v>80433</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7608,10 +7601,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132623303</v>
+        <v>132617549</v>
       </c>
       <c r="B63" t="n">
-        <v>56522</v>
+        <v>80433</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7619,49 +7612,40 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672560</v>
+        <v>672932</v>
       </c>
       <c r="R63" t="n">
-        <v>6981577</v>
+        <v>6981224</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7690,7 +7674,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7700,7 +7684,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7709,50 +7693,66 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132617602</v>
+        <v>132617555</v>
       </c>
       <c r="B64" t="n">
-        <v>97983</v>
+        <v>79328</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7762,10 +7762,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>672593</v>
+        <v>672921</v>
       </c>
       <c r="R64" t="n">
-        <v>6981519</v>
+        <v>6981328</v>
       </c>
       <c r="S64" t="n">
         <v>3</v>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7837,7 +7837,7 @@
         <v>132617591</v>
       </c>
       <c r="B65" t="n">
-        <v>80432</v>
+        <v>80433</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>132617574</v>
       </c>
       <c r="B66" t="n">
-        <v>91872</v>
+        <v>91873</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8076,10 +8076,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132617553</v>
+        <v>132617560</v>
       </c>
       <c r="B67" t="n">
-        <v>101326</v>
+        <v>97984</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8087,21 +8087,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8111,13 +8111,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>672931</v>
+        <v>672883</v>
       </c>
       <c r="R67" t="n">
-        <v>6981286</v>
+        <v>6981346</v>
       </c>
       <c r="S67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8183,10 +8183,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132617560</v>
+        <v>132617553</v>
       </c>
       <c r="B68" t="n">
-        <v>97983</v>
+        <v>101327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8194,21 +8194,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8218,13 +8218,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>672883</v>
+        <v>672931</v>
       </c>
       <c r="R68" t="n">
-        <v>6981346</v>
+        <v>6981286</v>
       </c>
       <c r="S68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8290,10 +8290,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132623263</v>
+        <v>132617556</v>
       </c>
       <c r="B69" t="n">
-        <v>79327</v>
+        <v>91910</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8301,40 +8301,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>672878</v>
+        <v>672881</v>
       </c>
       <c r="R69" t="n">
-        <v>6981321</v>
+        <v>6981314</v>
       </c>
       <c r="S69" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8363,7 +8360,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8373,7 +8370,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På stående död gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8382,44 +8384,28 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132623267</v>
+        <v>132617561</v>
       </c>
       <c r="B70" t="n">
-        <v>79327</v>
+        <v>91910</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8427,40 +8413,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>672869</v>
+        <v>672878</v>
       </c>
       <c r="R70" t="n">
-        <v>6981357</v>
+        <v>6981375</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8489,7 +8472,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8499,7 +8482,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8508,66 +8491,50 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132617556</v>
+        <v>132617584</v>
       </c>
       <c r="B71" t="n">
-        <v>91909</v>
+        <v>91873</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8577,10 +8544,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672881</v>
+        <v>672639</v>
       </c>
       <c r="R71" t="n">
-        <v>6981314</v>
+        <v>6981355</v>
       </c>
       <c r="S71" t="n">
         <v>3</v>
@@ -8612,7 +8579,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8622,12 +8589,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:25</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På stående död gran</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8654,10 +8616,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132617561</v>
+        <v>132623267</v>
       </c>
       <c r="B72" t="n">
-        <v>91909</v>
+        <v>79328</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8665,37 +8627,40 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>672878</v>
+        <v>672869</v>
       </c>
       <c r="R72" t="n">
-        <v>6981375</v>
+        <v>6981357</v>
       </c>
       <c r="S72" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8724,7 +8689,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8734,7 +8699,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8743,28 +8708,44 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132617598</v>
+        <v>132623263</v>
       </c>
       <c r="B73" t="n">
-        <v>92329</v>
+        <v>79328</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8772,37 +8753,40 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>672763</v>
+        <v>672878</v>
       </c>
       <c r="R73" t="n">
-        <v>6981545</v>
+        <v>6981321</v>
       </c>
       <c r="S73" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8831,7 +8815,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8841,7 +8825,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8872,22 +8856,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132617584</v>
+        <v>132623305</v>
       </c>
       <c r="B74" t="n">
-        <v>91872</v>
+        <v>101327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8895,37 +8879,45 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>672639</v>
+        <v>672911</v>
       </c>
       <c r="R74" t="n">
-        <v>6981355</v>
+        <v>6981136</v>
       </c>
       <c r="S74" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8954,7 +8946,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8964,7 +8956,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8973,28 +8965,29 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132623305</v>
+        <v>132623253</v>
       </c>
       <c r="B75" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9034,10 +9027,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672911</v>
+        <v>672918</v>
       </c>
       <c r="R75" t="n">
-        <v>6981136</v>
+        <v>6980944</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9069,7 +9062,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9079,7 +9072,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9107,56 +9100,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132623253</v>
+        <v>132617598</v>
       </c>
       <c r="B76" t="n">
-        <v>101326</v>
+        <v>92330</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222498</v>
+        <v>6040186</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>672918</v>
+        <v>672763</v>
       </c>
       <c r="R76" t="n">
-        <v>6980944</v>
+        <v>6981545</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9185,7 +9170,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9195,7 +9180,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9208,15 +9193,30 @@
       <c r="AG76" t="b">
         <v>0</v>
       </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -9226,7 +9226,7 @@
         <v>132617559</v>
       </c>
       <c r="B77" t="n">
-        <v>80432</v>
+        <v>80433</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9349,32 +9349,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132617552</v>
+        <v>132617575</v>
       </c>
       <c r="B78" t="n">
-        <v>57950</v>
+        <v>57946</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>100110</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9382,7 +9382,7 @@
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -9392,13 +9392,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>672968</v>
+        <v>672681</v>
       </c>
       <c r="R78" t="n">
-        <v>6981202</v>
+        <v>6981300</v>
       </c>
       <c r="S78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9437,7 +9437,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Sång i över en minut.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9464,10 +9469,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132617585</v>
+        <v>132623275</v>
       </c>
       <c r="B79" t="n">
-        <v>80392</v>
+        <v>101327</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9475,26 +9480,31 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -9502,13 +9512,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>672635</v>
+        <v>672670</v>
       </c>
       <c r="R79" t="n">
-        <v>6981376</v>
+        <v>6981289</v>
       </c>
       <c r="S79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9537,7 +9547,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9547,7 +9557,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9560,40 +9570,25 @@
       <c r="AG79" t="b">
         <v>0</v>
       </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132623284</v>
+        <v>132623257</v>
       </c>
       <c r="B80" t="n">
-        <v>97983</v>
+        <v>101327</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9601,37 +9596,45 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>672622</v>
+        <v>672951</v>
       </c>
       <c r="R80" t="n">
-        <v>6981351</v>
+        <v>6981191</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9660,7 +9663,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9670,7 +9673,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9679,6 +9682,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9697,32 +9701,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132617575</v>
+        <v>132617552</v>
       </c>
       <c r="B81" t="n">
-        <v>57945</v>
+        <v>57951</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100110</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9730,7 +9734,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -9740,13 +9744,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>672681</v>
+        <v>672968</v>
       </c>
       <c r="R81" t="n">
-        <v>6981300</v>
+        <v>6981202</v>
       </c>
       <c r="S81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9775,7 +9779,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9785,12 +9789,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Sång i över en minut.</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9817,10 +9816,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132623275</v>
+        <v>132623284</v>
       </c>
       <c r="B82" t="n">
-        <v>101326</v>
+        <v>97984</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9828,45 +9827,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>672670</v>
+        <v>672622</v>
       </c>
       <c r="R82" t="n">
-        <v>6981289</v>
+        <v>6981351</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9895,7 +9886,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9905,7 +9896,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9914,7 +9905,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9933,10 +9923,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132623257</v>
+        <v>132617585</v>
       </c>
       <c r="B83" t="n">
-        <v>101326</v>
+        <v>80393</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9944,31 +9934,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9976,13 +9961,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>672951</v>
+        <v>672635</v>
       </c>
       <c r="R83" t="n">
-        <v>6981191</v>
+        <v>6981376</v>
       </c>
       <c r="S83" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10011,7 +9996,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10021,7 +10006,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10034,57 +10019,67 @@
       <c r="AG83" t="b">
         <v>0</v>
       </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132623255</v>
+        <v>132617594</v>
       </c>
       <c r="B84" t="n">
-        <v>101326</v>
+        <v>91910</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -10092,13 +10087,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>672955</v>
+        <v>672755</v>
       </c>
       <c r="R84" t="n">
-        <v>6981134</v>
+        <v>6981496</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10127,7 +10122,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10137,7 +10132,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10153,22 +10148,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132617587</v>
+        <v>132623255</v>
       </c>
       <c r="B85" t="n">
-        <v>80392</v>
+        <v>101327</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10176,26 +10171,31 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -10203,13 +10203,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>672655</v>
+        <v>672955</v>
       </c>
       <c r="R85" t="n">
-        <v>6981378</v>
+        <v>6981134</v>
       </c>
       <c r="S85" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10261,62 +10261,47 @@
       <c r="AG85" t="b">
         <v>0</v>
       </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132617594</v>
+        <v>132617587</v>
       </c>
       <c r="B86" t="n">
-        <v>91909</v>
+        <v>80393</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10329,10 +10314,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>672755</v>
+        <v>672655</v>
       </c>
       <c r="R86" t="n">
-        <v>6981496</v>
+        <v>6981378</v>
       </c>
       <c r="S86" t="n">
         <v>3</v>
@@ -10364,7 +10349,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10374,7 +10359,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10386,6 +10371,21 @@
       <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -10405,7 +10405,7 @@
         <v>132623277</v>
       </c>
       <c r="B87" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10518,10 +10518,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132617565</v>
+        <v>132617577</v>
       </c>
       <c r="B88" t="n">
-        <v>80432</v>
+        <v>91910</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10529,37 +10529,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>672833</v>
+        <v>672687</v>
       </c>
       <c r="R88" t="n">
-        <v>6981355</v>
+        <v>6981287</v>
       </c>
       <c r="S88" t="n">
         <v>3</v>
@@ -10591,7 +10588,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10601,12 +10598,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Växandes på björk.</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10615,24 +10612,8 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -10649,10 +10630,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132623270</v>
+        <v>132617565</v>
       </c>
       <c r="B89" t="n">
-        <v>79327</v>
+        <v>80433</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10660,21 +10641,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10687,13 +10668,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>672831</v>
+        <v>672833</v>
       </c>
       <c r="R89" t="n">
         <v>6981355</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10722,7 +10703,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10732,7 +10713,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Växandes på björk.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10747,76 +10733,84 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132617583</v>
+        <v>132623291</v>
       </c>
       <c r="B90" t="n">
-        <v>79327</v>
+        <v>101327</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>672577</v>
+        <v>672630</v>
       </c>
       <c r="R90" t="n">
-        <v>6981292</v>
+        <v>6981380</v>
       </c>
       <c r="S90" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10845,7 +10839,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10855,7 +10849,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10864,66 +10858,75 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132617577</v>
+        <v>132623304</v>
       </c>
       <c r="B91" t="n">
-        <v>91909</v>
+        <v>101327</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>672687</v>
+        <v>672732</v>
       </c>
       <c r="R91" t="n">
-        <v>6981287</v>
+        <v>6981161</v>
       </c>
       <c r="S91" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10952,7 +10955,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10962,12 +10965,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>På död stående gran</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10976,28 +10974,29 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132623291</v>
+        <v>132617562</v>
       </c>
       <c r="B92" t="n">
-        <v>101326</v>
+        <v>91873</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11005,45 +11004,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>672630</v>
+        <v>672869</v>
       </c>
       <c r="R92" t="n">
-        <v>6981380</v>
+        <v>6981366</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11072,7 +11063,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11082,7 +11073,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11091,75 +11082,66 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132623304</v>
+        <v>132617583</v>
       </c>
       <c r="B93" t="n">
-        <v>101326</v>
+        <v>79328</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>672732</v>
+        <v>672577</v>
       </c>
       <c r="R93" t="n">
-        <v>6981161</v>
+        <v>6981292</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11188,7 +11170,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11198,7 +11180,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11207,67 +11189,69 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132617562</v>
+        <v>132623270</v>
       </c>
       <c r="B94" t="n">
-        <v>91872</v>
+        <v>79328</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>672869</v>
+        <v>672831</v>
       </c>
       <c r="R94" t="n">
-        <v>6981366</v>
+        <v>6981355</v>
       </c>
       <c r="S94" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11296,7 +11280,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11306,7 +11290,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11315,28 +11299,44 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132623258</v>
+        <v>132617563</v>
       </c>
       <c r="B95" t="n">
-        <v>101326</v>
+        <v>97984</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11344,45 +11344,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>672971</v>
+        <v>672858</v>
       </c>
       <c r="R95" t="n">
-        <v>6981202</v>
+        <v>6981365</v>
       </c>
       <c r="S95" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11411,7 +11403,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11421,7 +11413,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11430,29 +11422,28 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132623273</v>
+        <v>132617570</v>
       </c>
       <c r="B96" t="n">
-        <v>101326</v>
+        <v>97984</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11460,45 +11451,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>672774</v>
+        <v>672723</v>
       </c>
       <c r="R96" t="n">
-        <v>6981240</v>
+        <v>6981408</v>
       </c>
       <c r="S96" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11527,7 +11510,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11537,7 +11520,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11546,29 +11529,28 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132617563</v>
+        <v>132623299</v>
       </c>
       <c r="B97" t="n">
-        <v>97983</v>
+        <v>97984</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11600,13 +11582,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>672858</v>
+        <v>672709</v>
       </c>
       <c r="R97" t="n">
-        <v>6981365</v>
+        <v>6981494</v>
       </c>
       <c r="S97" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11635,7 +11617,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11645,7 +11627,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11660,22 +11642,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132617570</v>
+        <v>132623258</v>
       </c>
       <c r="B98" t="n">
-        <v>97983</v>
+        <v>101327</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11683,37 +11665,45 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>672723</v>
+        <v>672971</v>
       </c>
       <c r="R98" t="n">
-        <v>6981408</v>
+        <v>6981202</v>
       </c>
       <c r="S98" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11742,7 +11732,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11752,7 +11742,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11761,28 +11751,29 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132623299</v>
+        <v>132623273</v>
       </c>
       <c r="B99" t="n">
-        <v>97983</v>
+        <v>101327</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11790,37 +11781,45 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>672709</v>
+        <v>672774</v>
       </c>
       <c r="R99" t="n">
-        <v>6981494</v>
+        <v>6981240</v>
       </c>
       <c r="S99" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11849,7 +11848,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11859,7 +11858,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11868,6 +11867,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13423-2026 artfynd.xlsx
+++ b/artfynd/A 13423-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132617578</v>
+        <v>132617597</v>
       </c>
       <c r="B2" t="n">
-        <v>91910</v>
+        <v>91875</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672651</v>
+        <v>672762</v>
       </c>
       <c r="R2" t="n">
-        <v>6981280</v>
+        <v>6981535</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132617597</v>
+        <v>132617547</v>
       </c>
       <c r="B3" t="n">
-        <v>91873</v>
+        <v>79328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672762</v>
+        <v>672932</v>
       </c>
       <c r="R3" t="n">
-        <v>6981535</v>
+        <v>6981174</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132617547</v>
+        <v>132617578</v>
       </c>
       <c r="B4" t="n">
-        <v>79328</v>
+        <v>91912</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672932</v>
+        <v>672651</v>
       </c>
       <c r="R4" t="n">
-        <v>6981174</v>
+        <v>6981280</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,42 +996,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132617572</v>
+        <v>132623293</v>
       </c>
       <c r="B5" t="n">
-        <v>57951</v>
+        <v>101329</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1039,13 +1039,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>672701</v>
+        <v>672629</v>
       </c>
       <c r="R5" t="n">
-        <v>6981350</v>
+        <v>6981435</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,66 +1093,75 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132617551</v>
+        <v>132623296</v>
       </c>
       <c r="B6" t="n">
-        <v>91910</v>
+        <v>101329</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>672976</v>
+        <v>672649</v>
       </c>
       <c r="R6" t="n">
-        <v>6981217</v>
+        <v>6981516</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1181,7 +1190,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1191,7 +1200,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,60 +1209,61 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132623293</v>
+        <v>132617572</v>
       </c>
       <c r="B7" t="n">
-        <v>101327</v>
+        <v>57951</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1261,13 +1271,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>672629</v>
+        <v>672701</v>
       </c>
       <c r="R7" t="n">
-        <v>6981435</v>
+        <v>6981350</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1296,7 +1306,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1306,7 +1316,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,75 +1325,66 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132623296</v>
+        <v>132617551</v>
       </c>
       <c r="B8" t="n">
-        <v>101327</v>
+        <v>91912</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>672649</v>
+        <v>672976</v>
       </c>
       <c r="R8" t="n">
-        <v>6981516</v>
+        <v>6981217</v>
       </c>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1412,7 +1413,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1422,7 +1423,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1431,19 +1432,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1453,7 +1453,7 @@
         <v>132623279</v>
       </c>
       <c r="B9" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132617550</v>
+        <v>132617554</v>
       </c>
       <c r="B10" t="n">
-        <v>57951</v>
+        <v>91912</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,42 +1568,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672983</v>
+        <v>672912</v>
       </c>
       <c r="R10" t="n">
-        <v>6981247</v>
+        <v>6981315</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1635,7 +1627,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1645,7 +1637,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132617579</v>
+        <v>132623301</v>
       </c>
       <c r="B11" t="n">
-        <v>91873</v>
+        <v>97986</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1683,21 +1675,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1707,13 +1699,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672651</v>
+        <v>672767</v>
       </c>
       <c r="R11" t="n">
-        <v>6981280</v>
+        <v>6981492</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1742,7 +1734,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1752,7 +1744,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,73 +1759,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132617605</v>
+        <v>132617579</v>
       </c>
       <c r="B12" t="n">
-        <v>57954</v>
+        <v>91875</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672801</v>
+        <v>672651</v>
       </c>
       <c r="R12" t="n">
-        <v>6981249</v>
+        <v>6981280</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1865,7 +1841,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,12 +1851,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Två födosökande individer varav en hona</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1878,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132617571</v>
+        <v>132617550</v>
       </c>
       <c r="B13" t="n">
-        <v>57954</v>
+        <v>57951</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,16 +1889,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1940,7 +1911,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1950,13 +1921,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672713</v>
+        <v>672983</v>
       </c>
       <c r="R13" t="n">
-        <v>6981357</v>
+        <v>6981247</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1985,7 +1956,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1995,12 +1966,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2027,10 +1993,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132617554</v>
+        <v>132617605</v>
       </c>
       <c r="B14" t="n">
-        <v>91910</v>
+        <v>57954</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2038,34 +2004,50 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672912</v>
+        <v>672801</v>
       </c>
       <c r="R14" t="n">
-        <v>6981315</v>
+        <v>6981249</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2097,7 +2079,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2107,7 +2089,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Två födosökande individer varav en hona</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2134,48 +2121,56 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132623301</v>
+        <v>132617571</v>
       </c>
       <c r="B15" t="n">
-        <v>97984</v>
+        <v>57954</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672767</v>
+        <v>672713</v>
       </c>
       <c r="R15" t="n">
-        <v>6981492</v>
+        <v>6981357</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2204,7 +2199,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2214,7 +2209,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2229,12 +2229,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2244,7 +2244,7 @@
         <v>132623282</v>
       </c>
       <c r="B16" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,32 +2357,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132617590</v>
+        <v>132617581</v>
       </c>
       <c r="B17" t="n">
-        <v>91910</v>
+        <v>91875</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672706</v>
+        <v>672612</v>
       </c>
       <c r="R17" t="n">
-        <v>6981525</v>
+        <v>6981244</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2464,32 +2464,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132617581</v>
+        <v>132617590</v>
       </c>
       <c r="B18" t="n">
-        <v>91873</v>
+        <v>91912</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672612</v>
+        <v>672706</v>
       </c>
       <c r="R18" t="n">
-        <v>6981244</v>
+        <v>6981525</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2571,10 +2571,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132617601</v>
+        <v>132617593</v>
       </c>
       <c r="B19" t="n">
-        <v>80393</v>
+        <v>91875</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,40 +2582,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672548</v>
+        <v>672724</v>
       </c>
       <c r="R19" t="n">
-        <v>6981599</v>
+        <v>6981448</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2644,7 +2641,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2654,7 +2651,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2663,24 +2660,8 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2697,10 +2678,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132617593</v>
+        <v>132617588</v>
       </c>
       <c r="B20" t="n">
-        <v>91873</v>
+        <v>91875</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2732,10 +2713,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>672724</v>
+        <v>672671</v>
       </c>
       <c r="R20" t="n">
-        <v>6981448</v>
+        <v>6981418</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2767,7 +2748,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2777,7 +2758,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2804,10 +2785,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132617588</v>
+        <v>132617548</v>
       </c>
       <c r="B21" t="n">
-        <v>91873</v>
+        <v>91875</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2839,13 +2820,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>672671</v>
+        <v>672935</v>
       </c>
       <c r="R21" t="n">
-        <v>6981418</v>
+        <v>6981231</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2874,7 +2855,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2884,7 +2865,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2911,10 +2892,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132617548</v>
+        <v>132623302</v>
       </c>
       <c r="B22" t="n">
-        <v>91873</v>
+        <v>101329</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2922,37 +2903,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>672935</v>
+        <v>672746</v>
       </c>
       <c r="R22" t="n">
-        <v>6981231</v>
+        <v>6981560</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2981,7 +2970,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2991,7 +2980,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3000,28 +2989,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132623302</v>
+        <v>132617600</v>
       </c>
       <c r="B23" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3047,27 +3037,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672746</v>
+        <v>672651</v>
       </c>
       <c r="R23" t="n">
-        <v>6981560</v>
+        <v>6981546</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3096,7 +3078,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3106,7 +3088,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3115,29 +3097,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132617600</v>
+        <v>132623268</v>
       </c>
       <c r="B24" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3163,19 +3144,27 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>672651</v>
+        <v>672837</v>
       </c>
       <c r="R24" t="n">
-        <v>6981546</v>
+        <v>6981360</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3204,7 +3193,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3214,7 +3203,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3223,28 +3212,29 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132623268</v>
+        <v>132617601</v>
       </c>
       <c r="B25" t="n">
-        <v>101327</v>
+        <v>80393</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3252,31 +3242,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3284,13 +3269,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>672837</v>
+        <v>672548</v>
       </c>
       <c r="R25" t="n">
-        <v>6981360</v>
+        <v>6981599</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3319,7 +3304,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3329,7 +3314,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3342,15 +3327,30 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3360,7 +3360,7 @@
         <v>132617580</v>
       </c>
       <c r="B26" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3591,10 +3591,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132623295</v>
+        <v>132617568</v>
       </c>
       <c r="B28" t="n">
-        <v>101327</v>
+        <v>97986</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3602,45 +3602,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>672594</v>
+        <v>672748</v>
       </c>
       <c r="R28" t="n">
-        <v>6981486</v>
+        <v>6981368</v>
       </c>
       <c r="S28" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3669,7 +3661,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3679,7 +3671,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3688,29 +3680,28 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132623272</v>
+        <v>132623266</v>
       </c>
       <c r="B29" t="n">
-        <v>101327</v>
+        <v>97980</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3718,45 +3709,33 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>221944</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672787</v>
+        <v>672878</v>
       </c>
       <c r="R29" t="n">
-        <v>6981316</v>
+        <v>6981334</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3785,7 +3764,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3795,7 +3774,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3816,17 +3795,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132617568</v>
+        <v>132623295</v>
       </c>
       <c r="B30" t="n">
-        <v>97984</v>
+        <v>101329</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3834,37 +3813,45 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672748</v>
+        <v>672594</v>
       </c>
       <c r="R30" t="n">
-        <v>6981368</v>
+        <v>6981486</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3893,7 +3880,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3903,7 +3890,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3912,28 +3899,29 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132623266</v>
+        <v>132623272</v>
       </c>
       <c r="B31" t="n">
-        <v>97978</v>
+        <v>101329</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3941,33 +3929,45 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221944</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>672878</v>
+        <v>672787</v>
       </c>
       <c r="R31" t="n">
-        <v>6981334</v>
+        <v>6981316</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4037,7 +4037,7 @@
         <v>132623278</v>
       </c>
       <c r="B32" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4141,53 +4141,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132617582</v>
+        <v>132617586</v>
       </c>
       <c r="B33" t="n">
-        <v>57951</v>
+        <v>91875</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>672612</v>
+        <v>672660</v>
       </c>
       <c r="R33" t="n">
-        <v>6981238</v>
+        <v>6981395</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -4219,7 +4211,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4229,7 +4221,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4256,45 +4248,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132617586</v>
+        <v>132617582</v>
       </c>
       <c r="B34" t="n">
-        <v>91873</v>
+        <v>57951</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>672660</v>
+        <v>672612</v>
       </c>
       <c r="R34" t="n">
-        <v>6981395</v>
+        <v>6981238</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4366,7 +4366,7 @@
         <v>132617596</v>
       </c>
       <c r="B35" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>132623274</v>
       </c>
       <c r="B36" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4693,32 +4693,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132623290</v>
+        <v>132617564</v>
       </c>
       <c r="B38" t="n">
-        <v>97984</v>
+        <v>80433</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4728,13 +4728,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672621</v>
+        <v>672831</v>
       </c>
       <c r="R38" t="n">
-        <v>6981383</v>
+        <v>6981363</v>
       </c>
       <c r="S38" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4788,22 +4788,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132623285</v>
+        <v>132623290</v>
       </c>
       <c r="B39" t="n">
-        <v>101327</v>
+        <v>97986</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4811,45 +4811,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>672638</v>
+        <v>672621</v>
       </c>
       <c r="R39" t="n">
-        <v>6981364</v>
+        <v>6981383</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4878,7 +4870,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4888,7 +4880,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4897,7 +4889,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4916,45 +4907,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132617564</v>
+        <v>132617557</v>
       </c>
       <c r="B40" t="n">
-        <v>80433</v>
+        <v>80393</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672831</v>
+        <v>672878</v>
       </c>
       <c r="R40" t="n">
-        <v>6981363</v>
+        <v>6981324</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -4986,7 +4980,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4996,7 +4990,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5005,8 +4999,24 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5023,10 +5033,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132617557</v>
+        <v>132623285</v>
       </c>
       <c r="B41" t="n">
-        <v>80393</v>
+        <v>101329</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5034,26 +5044,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5061,13 +5076,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>672878</v>
+        <v>672638</v>
       </c>
       <c r="R41" t="n">
-        <v>6981324</v>
+        <v>6981364</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5096,7 +5111,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5106,7 +5121,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5119,40 +5134,25 @@
       <c r="AG41" t="b">
         <v>0</v>
       </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132623256</v>
+        <v>132617592</v>
       </c>
       <c r="B42" t="n">
-        <v>101327</v>
+        <v>80393</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5160,45 +5160,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>672930</v>
+        <v>672709</v>
       </c>
       <c r="R42" t="n">
-        <v>6981133</v>
+        <v>6981488</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5227,7 +5219,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5237,7 +5229,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5246,51 +5238,50 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132617592</v>
+        <v>132617558</v>
       </c>
       <c r="B43" t="n">
-        <v>80393</v>
+        <v>80306</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229497</v>
+        <v>392</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5300,13 +5291,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672709</v>
+        <v>672873</v>
       </c>
       <c r="R43" t="n">
-        <v>6981488</v>
+        <v>6981339</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5335,7 +5326,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5345,7 +5336,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5372,48 +5363,51 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132617558</v>
+        <v>132617607</v>
       </c>
       <c r="B44" t="n">
-        <v>80306</v>
+        <v>79328</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672873</v>
+        <v>672712</v>
       </c>
       <c r="R44" t="n">
-        <v>6981339</v>
+        <v>6981164</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5442,7 +5436,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5452,7 +5446,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5461,8 +5455,24 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5479,37 +5489,42 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132617607</v>
+        <v>132623256</v>
       </c>
       <c r="B45" t="n">
-        <v>79328</v>
+        <v>101329</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5517,13 +5532,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672712</v>
+        <v>672930</v>
       </c>
       <c r="R45" t="n">
-        <v>6981164</v>
+        <v>6981133</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5552,7 +5567,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5562,7 +5577,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5575,67 +5590,57 @@
       <c r="AG45" t="b">
         <v>0</v>
       </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132617567</v>
+        <v>132623254</v>
       </c>
       <c r="B46" t="n">
-        <v>80433</v>
+        <v>101329</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5643,13 +5648,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>672776</v>
+        <v>672976</v>
       </c>
       <c r="R46" t="n">
-        <v>6981332</v>
+        <v>6981122</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5678,7 +5683,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5688,7 +5693,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5701,72 +5706,57 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132617576</v>
+        <v>132623294</v>
       </c>
       <c r="B47" t="n">
-        <v>57954</v>
+        <v>101329</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5774,13 +5764,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>672684</v>
+        <v>672601</v>
       </c>
       <c r="R47" t="n">
-        <v>6981289</v>
+        <v>6981439</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5809,7 +5799,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5819,12 +5809,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5833,28 +5818,29 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132623254</v>
+        <v>132623300</v>
       </c>
       <c r="B48" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5894,13 +5880,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>672976</v>
+        <v>672758</v>
       </c>
       <c r="R48" t="n">
-        <v>6981122</v>
+        <v>6981513</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5929,7 +5915,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5939,7 +5925,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5967,10 +5953,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132623294</v>
+        <v>132617546</v>
       </c>
       <c r="B49" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5996,27 +5982,19 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672601</v>
+        <v>672949</v>
       </c>
       <c r="R49" t="n">
-        <v>6981439</v>
+        <v>6981130</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6045,7 +6023,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6055,7 +6033,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6064,61 +6042,55 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132623300</v>
+        <v>132617567</v>
       </c>
       <c r="B50" t="n">
-        <v>101327</v>
+        <v>80433</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6126,13 +6098,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>672758</v>
+        <v>672776</v>
       </c>
       <c r="R50" t="n">
-        <v>6981513</v>
+        <v>6981332</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6161,7 +6133,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6171,7 +6143,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6184,60 +6156,83 @@
       <c r="AG50" t="b">
         <v>0</v>
       </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132617546</v>
+        <v>132617576</v>
       </c>
       <c r="B51" t="n">
-        <v>101327</v>
+        <v>57954</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672949</v>
+        <v>672684</v>
       </c>
       <c r="R51" t="n">
-        <v>6981130</v>
+        <v>6981289</v>
       </c>
       <c r="S51" t="n">
         <v>3</v>
@@ -6269,7 +6264,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6279,7 +6274,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6306,41 +6306,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132623292</v>
+        <v>132617589</v>
       </c>
       <c r="B52" t="n">
-        <v>101327</v>
+        <v>99121</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
@@ -6349,13 +6353,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672655</v>
+        <v>672627</v>
       </c>
       <c r="R52" t="n">
-        <v>6981418</v>
+        <v>6981425</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6384,7 +6388,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6394,7 +6398,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6410,53 +6414,49 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132617595</v>
+        <v>132617566</v>
       </c>
       <c r="B53" t="n">
-        <v>79328</v>
+        <v>80393</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6464,13 +6464,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>672745</v>
+        <v>672774</v>
       </c>
       <c r="R53" t="n">
-        <v>6981544</v>
+        <v>6981334</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6521,6 +6521,21 @@
       <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6537,10 +6552,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132617603</v>
+        <v>132617595</v>
       </c>
       <c r="B54" t="n">
-        <v>57954</v>
+        <v>79328</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6548,57 +6563,44 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672617</v>
+        <v>672745</v>
       </c>
       <c r="R54" t="n">
-        <v>6981488</v>
+        <v>6981544</v>
       </c>
       <c r="S54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6627,7 +6629,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6637,7 +6639,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6646,6 +6648,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6664,57 +6667,65 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132617589</v>
+        <v>132617603</v>
       </c>
       <c r="B55" t="n">
-        <v>99119</v>
+        <v>57954</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672627</v>
+        <v>672617</v>
       </c>
       <c r="R55" t="n">
-        <v>6981425</v>
+        <v>6981488</v>
       </c>
       <c r="S55" t="n">
         <v>2</v>
@@ -6746,7 +6757,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6756,7 +6767,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6765,7 +6776,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6784,10 +6794,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132617566</v>
+        <v>132623292</v>
       </c>
       <c r="B56" t="n">
-        <v>80393</v>
+        <v>101329</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6795,26 +6805,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6822,13 +6837,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>672774</v>
+        <v>672655</v>
       </c>
       <c r="R56" t="n">
-        <v>6981334</v>
+        <v>6981418</v>
       </c>
       <c r="S56" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6857,7 +6872,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6867,7 +6882,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6880,90 +6895,63 @@
       <c r="AG56" t="b">
         <v>0</v>
       </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132623303</v>
+        <v>132617602</v>
       </c>
       <c r="B57" t="n">
-        <v>56522</v>
+        <v>97986</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>206004</v>
+        <v>221945</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>672560</v>
+        <v>672593</v>
       </c>
       <c r="R57" t="n">
-        <v>6981577</v>
+        <v>6981519</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6992,7 +6980,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7002,7 +6990,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7017,60 +7005,63 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132617602</v>
+        <v>132623271</v>
       </c>
       <c r="B58" t="n">
-        <v>97984</v>
+        <v>80433</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>672593</v>
+        <v>672780</v>
       </c>
       <c r="R58" t="n">
-        <v>6981519</v>
+        <v>6981331</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7099,7 +7090,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7109,7 +7100,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7118,74 +7109,82 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132623265</v>
+        <v>132617555</v>
       </c>
       <c r="B59" t="n">
-        <v>101327</v>
+        <v>79328</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>672872</v>
+        <v>672921</v>
       </c>
       <c r="R59" t="n">
-        <v>6981332</v>
+        <v>6981328</v>
       </c>
       <c r="S59" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7214,7 +7213,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7224,7 +7223,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7233,61 +7232,55 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132623280</v>
+        <v>132617549</v>
       </c>
       <c r="B60" t="n">
-        <v>101327</v>
+        <v>80433</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7295,13 +7288,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672636</v>
+        <v>672932</v>
       </c>
       <c r="R60" t="n">
-        <v>6981290</v>
+        <v>6981224</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7330,7 +7323,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7340,7 +7333,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7353,63 +7346,90 @@
       <c r="AG60" t="b">
         <v>0</v>
       </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132617606</v>
+        <v>132623303</v>
       </c>
       <c r="B61" t="n">
-        <v>101327</v>
+        <v>56522</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>206004</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672733</v>
+        <v>672560</v>
       </c>
       <c r="R61" t="n">
-        <v>6981160</v>
+        <v>6981577</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7438,7 +7458,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7448,7 +7468,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7463,49 +7483,54 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132623271</v>
+        <v>132623265</v>
       </c>
       <c r="B62" t="n">
-        <v>80433</v>
+        <v>101329</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7513,13 +7538,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>672780</v>
+        <v>672872</v>
       </c>
       <c r="R62" t="n">
-        <v>6981331</v>
+        <v>6981332</v>
       </c>
       <c r="S62" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7548,7 +7573,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7558,7 +7583,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7571,21 +7596,6 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
@@ -7594,44 +7604,49 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132617549</v>
+        <v>132623280</v>
       </c>
       <c r="B63" t="n">
-        <v>80433</v>
+        <v>101329</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7639,13 +7654,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672932</v>
+        <v>672636</v>
       </c>
       <c r="R63" t="n">
-        <v>6981224</v>
+        <v>6981290</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7674,7 +7689,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7684,7 +7699,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7697,62 +7712,47 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132617555</v>
+        <v>132617606</v>
       </c>
       <c r="B64" t="n">
-        <v>79328</v>
+        <v>101329</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7762,10 +7762,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>672921</v>
+        <v>672733</v>
       </c>
       <c r="R64" t="n">
-        <v>6981328</v>
+        <v>6981160</v>
       </c>
       <c r="S64" t="n">
         <v>3</v>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7834,52 +7834,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132617591</v>
+        <v>132617574</v>
       </c>
       <c r="B65" t="n">
-        <v>80433</v>
+        <v>91875</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>672709</v>
+        <v>672695</v>
       </c>
       <c r="R65" t="n">
-        <v>6981489</v>
+        <v>6981312</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -7911,7 +7904,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7921,12 +7914,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Växandes på fyra närliggande aspträd</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7935,24 +7923,8 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -7969,45 +7941,52 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132617574</v>
+        <v>132617591</v>
       </c>
       <c r="B66" t="n">
-        <v>91873</v>
+        <v>80433</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>672695</v>
+        <v>672709</v>
       </c>
       <c r="R66" t="n">
-        <v>6981312</v>
+        <v>6981489</v>
       </c>
       <c r="S66" t="n">
         <v>3</v>
@@ -8039,7 +8018,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8049,7 +8028,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Växandes på fyra närliggande aspträd</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8058,8 +8042,24 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8079,7 +8079,7 @@
         <v>132617560</v>
       </c>
       <c r="B67" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>132617553</v>
       </c>
       <c r="B68" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8290,32 +8290,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132617556</v>
+        <v>132617584</v>
       </c>
       <c r="B69" t="n">
-        <v>91910</v>
+        <v>91875</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>672881</v>
+        <v>672639</v>
       </c>
       <c r="R69" t="n">
-        <v>6981314</v>
+        <v>6981355</v>
       </c>
       <c r="S69" t="n">
         <v>3</v>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8370,12 +8370,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:25</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På stående död gran</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8402,10 +8397,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132617561</v>
+        <v>132623267</v>
       </c>
       <c r="B70" t="n">
-        <v>91910</v>
+        <v>79328</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8413,37 +8408,40 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>672878</v>
+        <v>672869</v>
       </c>
       <c r="R70" t="n">
-        <v>6981375</v>
+        <v>6981357</v>
       </c>
       <c r="S70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8472,7 +8470,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8482,7 +8480,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8491,66 +8489,85 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132617584</v>
+        <v>132623263</v>
       </c>
       <c r="B71" t="n">
-        <v>91873</v>
+        <v>79328</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672639</v>
+        <v>672878</v>
       </c>
       <c r="R71" t="n">
-        <v>6981355</v>
+        <v>6981321</v>
       </c>
       <c r="S71" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8579,7 +8596,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8589,7 +8606,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8598,28 +8615,44 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132623267</v>
+        <v>132617561</v>
       </c>
       <c r="B72" t="n">
-        <v>79328</v>
+        <v>91912</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8627,40 +8660,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>672869</v>
+        <v>672878</v>
       </c>
       <c r="R72" t="n">
-        <v>6981357</v>
+        <v>6981375</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8689,7 +8719,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8699,7 +8729,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8708,44 +8738,28 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132623263</v>
+        <v>132617598</v>
       </c>
       <c r="B73" t="n">
-        <v>79328</v>
+        <v>92332</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8753,40 +8767,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>672878</v>
+        <v>672763</v>
       </c>
       <c r="R73" t="n">
-        <v>6981321</v>
+        <v>6981545</v>
       </c>
       <c r="S73" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8815,7 +8826,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8825,7 +8836,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8856,68 +8867,60 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132623305</v>
+        <v>132617556</v>
       </c>
       <c r="B74" t="n">
-        <v>101327</v>
+        <v>91912</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>672911</v>
+        <v>672881</v>
       </c>
       <c r="R74" t="n">
-        <v>6981136</v>
+        <v>6981314</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8946,7 +8949,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8956,7 +8959,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På stående död gran</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8965,29 +8973,28 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132623253</v>
+        <v>132623305</v>
       </c>
       <c r="B75" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9027,10 +9034,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672918</v>
+        <v>672911</v>
       </c>
       <c r="R75" t="n">
-        <v>6980944</v>
+        <v>6981136</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9062,7 +9069,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9072,7 +9079,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9100,48 +9107,56 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132617598</v>
+        <v>132623253</v>
       </c>
       <c r="B76" t="n">
-        <v>92330</v>
+        <v>101329</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6040186</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>672763</v>
+        <v>672918</v>
       </c>
       <c r="R76" t="n">
-        <v>6981545</v>
+        <v>6980944</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9170,7 +9185,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9180,7 +9195,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9193,40 +9208,25 @@
       <c r="AG76" t="b">
         <v>0</v>
       </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132617559</v>
+        <v>132617552</v>
       </c>
       <c r="B77" t="n">
-        <v>80433</v>
+        <v>57951</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9234,26 +9234,31 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9261,10 +9266,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>672887</v>
+        <v>672968</v>
       </c>
       <c r="R77" t="n">
-        <v>6981335</v>
+        <v>6981202</v>
       </c>
       <c r="S77" t="n">
         <v>1</v>
@@ -9296,7 +9301,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9306,7 +9311,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9315,24 +9320,8 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9349,42 +9338,37 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132617575</v>
+        <v>132617559</v>
       </c>
       <c r="B78" t="n">
-        <v>57946</v>
+        <v>80433</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100110</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -9392,13 +9376,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>672681</v>
+        <v>672887</v>
       </c>
       <c r="R78" t="n">
-        <v>6981300</v>
+        <v>6981335</v>
       </c>
       <c r="S78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9427,7 +9411,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9437,12 +9421,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Sång i över en minut.</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9451,8 +9430,24 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9469,10 +9464,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132623275</v>
+        <v>132617575</v>
       </c>
       <c r="B79" t="n">
-        <v>101327</v>
+        <v>57946</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9480,31 +9475,31 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222498</v>
+        <v>100110</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -9512,13 +9507,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>672670</v>
+        <v>672681</v>
       </c>
       <c r="R79" t="n">
-        <v>6981289</v>
+        <v>6981300</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9547,7 +9542,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9557,7 +9552,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Sång i över en minut.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9566,29 +9566,28 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132623257</v>
+        <v>132623275</v>
       </c>
       <c r="B80" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9628,13 +9627,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>672951</v>
+        <v>672670</v>
       </c>
       <c r="R80" t="n">
-        <v>6981191</v>
+        <v>6981289</v>
       </c>
       <c r="S80" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9663,7 +9662,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9673,7 +9672,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9701,42 +9700,42 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132617552</v>
+        <v>132623257</v>
       </c>
       <c r="B81" t="n">
-        <v>57951</v>
+        <v>101329</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -9744,13 +9743,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>672968</v>
+        <v>672951</v>
       </c>
       <c r="R81" t="n">
-        <v>6981202</v>
+        <v>6981191</v>
       </c>
       <c r="S81" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9779,7 +9778,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9789,7 +9788,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9798,28 +9797,29 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132623284</v>
+        <v>132617585</v>
       </c>
       <c r="B82" t="n">
-        <v>97984</v>
+        <v>80393</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9827,37 +9827,40 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221945</v>
+        <v>229497</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>672622</v>
+        <v>672635</v>
       </c>
       <c r="R82" t="n">
-        <v>6981351</v>
+        <v>6981376</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9886,7 +9889,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9896,7 +9899,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9905,28 +9908,44 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132617585</v>
+        <v>132623284</v>
       </c>
       <c r="B83" t="n">
-        <v>80393</v>
+        <v>97986</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9934,40 +9953,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229497</v>
+        <v>221945</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>672635</v>
+        <v>672622</v>
       </c>
       <c r="R83" t="n">
-        <v>6981376</v>
+        <v>6981351</v>
       </c>
       <c r="S83" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9996,7 +10012,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10006,7 +10022,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10015,34 +10031,18 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -10052,7 +10052,7 @@
         <v>132617594</v>
       </c>
       <c r="B84" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         <v>132623255</v>
       </c>
       <c r="B85" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>132623277</v>
       </c>
       <c r="B87" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>132617577</v>
       </c>
       <c r="B88" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10630,37 +10630,42 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132617565</v>
+        <v>132623291</v>
       </c>
       <c r="B89" t="n">
-        <v>80433</v>
+        <v>101329</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10668,13 +10673,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>672833</v>
+        <v>672630</v>
       </c>
       <c r="R89" t="n">
-        <v>6981355</v>
+        <v>6981380</v>
       </c>
       <c r="S89" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10703,7 +10708,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10713,12 +10718,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:09</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Växandes på björk.</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10731,40 +10731,25 @@
       <c r="AG89" t="b">
         <v>0</v>
       </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132623291</v>
+        <v>132623304</v>
       </c>
       <c r="B90" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10804,13 +10789,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>672630</v>
+        <v>672732</v>
       </c>
       <c r="R90" t="n">
-        <v>6981380</v>
+        <v>6981161</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10839,7 +10824,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10849,7 +10834,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10877,10 +10862,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132623304</v>
+        <v>132617562</v>
       </c>
       <c r="B91" t="n">
-        <v>101327</v>
+        <v>91875</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10888,45 +10873,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>672732</v>
+        <v>672869</v>
       </c>
       <c r="R91" t="n">
-        <v>6981161</v>
+        <v>6981366</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10955,7 +10932,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10965,7 +10942,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10974,51 +10951,50 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132617562</v>
+        <v>132617583</v>
       </c>
       <c r="B92" t="n">
-        <v>91873</v>
+        <v>79328</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11028,10 +11004,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>672869</v>
+        <v>672577</v>
       </c>
       <c r="R92" t="n">
-        <v>6981366</v>
+        <v>6981292</v>
       </c>
       <c r="S92" t="n">
         <v>3</v>
@@ -11063,7 +11039,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11073,7 +11049,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11100,7 +11076,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132617583</v>
+        <v>132623270</v>
       </c>
       <c r="B93" t="n">
         <v>79328</v>
@@ -11129,19 +11105,22 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>672577</v>
+        <v>672831</v>
       </c>
       <c r="R93" t="n">
-        <v>6981292</v>
+        <v>6981355</v>
       </c>
       <c r="S93" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11170,7 +11149,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11180,7 +11159,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11189,28 +11168,44 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132623270</v>
+        <v>132617565</v>
       </c>
       <c r="B94" t="n">
-        <v>79328</v>
+        <v>80433</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11218,21 +11213,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11245,13 +11240,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>672831</v>
+        <v>672833</v>
       </c>
       <c r="R94" t="n">
         <v>6981355</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11280,7 +11275,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11290,7 +11285,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Växandes på björk.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11305,28 +11305,28 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -11336,7 +11336,7 @@
         <v>132617563</v>
       </c>
       <c r="B95" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>132617570</v>
       </c>
       <c r="B96" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>132623299</v>
       </c>
       <c r="B97" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>132623258</v>
       </c>
       <c r="B98" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>132623273</v>
       </c>
       <c r="B99" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 13423-2026 artfynd.xlsx
+++ b/artfynd/A 13423-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132617597</v>
+        <v>132617547</v>
       </c>
       <c r="B2" t="n">
-        <v>91875</v>
+        <v>79329</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672762</v>
+        <v>672932</v>
       </c>
       <c r="R2" t="n">
-        <v>6981535</v>
+        <v>6981174</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132617547</v>
+        <v>132617578</v>
       </c>
       <c r="B3" t="n">
-        <v>79328</v>
+        <v>91913</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672932</v>
+        <v>672651</v>
       </c>
       <c r="R3" t="n">
-        <v>6981174</v>
+        <v>6981280</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132617578</v>
+        <v>132617597</v>
       </c>
       <c r="B4" t="n">
-        <v>91912</v>
+        <v>91876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672651</v>
+        <v>672762</v>
       </c>
       <c r="R4" t="n">
-        <v>6981280</v>
+        <v>6981535</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,56 +996,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132623293</v>
+        <v>132617551</v>
       </c>
       <c r="B5" t="n">
-        <v>101329</v>
+        <v>91913</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>672629</v>
+        <v>672976</v>
       </c>
       <c r="R5" t="n">
-        <v>6981435</v>
+        <v>6981217</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,61 +1085,60 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132623296</v>
+        <v>132617572</v>
       </c>
       <c r="B6" t="n">
-        <v>101329</v>
+        <v>57951</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1155,13 +1146,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>672649</v>
+        <v>672701</v>
       </c>
       <c r="R6" t="n">
-        <v>6981516</v>
+        <v>6981350</v>
       </c>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,7 +1181,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1200,7 +1191,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,61 +1200,60 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132617572</v>
+        <v>132623293</v>
       </c>
       <c r="B7" t="n">
-        <v>57951</v>
+        <v>101330</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1271,13 +1261,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>672701</v>
+        <v>672629</v>
       </c>
       <c r="R7" t="n">
-        <v>6981350</v>
+        <v>6981435</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1306,7 +1296,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1316,7 +1306,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,66 +1315,75 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132617551</v>
+        <v>132623296</v>
       </c>
       <c r="B8" t="n">
-        <v>91912</v>
+        <v>101330</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>672976</v>
+        <v>672649</v>
       </c>
       <c r="R8" t="n">
-        <v>6981217</v>
+        <v>6981516</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1423,7 +1422,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,18 +1431,19 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1453,7 +1453,7 @@
         <v>132623279</v>
       </c>
       <c r="B9" t="n">
-        <v>97986</v>
+        <v>97987</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132617554</v>
+        <v>132617605</v>
       </c>
       <c r="B10" t="n">
-        <v>91912</v>
+        <v>57954</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,34 +1568,50 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672912</v>
+        <v>672801</v>
       </c>
       <c r="R10" t="n">
-        <v>6981315</v>
+        <v>6981249</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1627,7 +1643,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1637,7 +1653,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Två födosökande individer varav en hona</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,48 +1685,56 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132623301</v>
+        <v>132617571</v>
       </c>
       <c r="B11" t="n">
-        <v>97986</v>
+        <v>57954</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672767</v>
+        <v>672713</v>
       </c>
       <c r="R11" t="n">
-        <v>6981492</v>
+        <v>6981357</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1734,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1744,7 +1773,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,44 +1793,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132617579</v>
+        <v>132617554</v>
       </c>
       <c r="B12" t="n">
-        <v>91875</v>
+        <v>91913</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1806,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672651</v>
+        <v>672912</v>
       </c>
       <c r="R12" t="n">
-        <v>6981280</v>
+        <v>6981315</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1841,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1851,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1878,53 +1912,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132617550</v>
+        <v>132617579</v>
       </c>
       <c r="B13" t="n">
-        <v>57951</v>
+        <v>91876</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672983</v>
+        <v>672651</v>
       </c>
       <c r="R13" t="n">
-        <v>6981247</v>
+        <v>6981280</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -1956,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1966,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1993,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132617605</v>
+        <v>132617550</v>
       </c>
       <c r="B14" t="n">
-        <v>57954</v>
+        <v>57951</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,16 +2030,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2021,33 +2047,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672801</v>
+        <v>672983</v>
       </c>
       <c r="R14" t="n">
-        <v>6981249</v>
+        <v>6981247</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2079,7 +2097,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2089,12 +2107,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Två födosökande individer varav en hona</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2121,42 +2134,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132617571</v>
+        <v>132623282</v>
       </c>
       <c r="B15" t="n">
-        <v>57954</v>
+        <v>101330</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2164,13 +2177,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672713</v>
+        <v>672633</v>
       </c>
       <c r="R15" t="n">
-        <v>6981357</v>
+        <v>6981324</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2199,7 +2212,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2209,12 +2222,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2223,28 +2231,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132623282</v>
+        <v>132623301</v>
       </c>
       <c r="B16" t="n">
-        <v>101329</v>
+        <v>97987</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,42 +2261,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672633</v>
+        <v>672767</v>
       </c>
       <c r="R16" t="n">
-        <v>6981324</v>
+        <v>6981492</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2319,7 +2320,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2329,7 +2330,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,7 +2339,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2357,32 +2357,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132617581</v>
+        <v>132617590</v>
       </c>
       <c r="B17" t="n">
-        <v>91875</v>
+        <v>91913</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672612</v>
+        <v>672706</v>
       </c>
       <c r="R17" t="n">
-        <v>6981244</v>
+        <v>6981525</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2464,32 +2464,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132617590</v>
+        <v>132617581</v>
       </c>
       <c r="B18" t="n">
-        <v>91912</v>
+        <v>91876</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672706</v>
+        <v>672612</v>
       </c>
       <c r="R18" t="n">
-        <v>6981525</v>
+        <v>6981244</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2574,7 +2574,7 @@
         <v>132617593</v>
       </c>
       <c r="B19" t="n">
-        <v>91875</v>
+        <v>91876</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>132617588</v>
       </c>
       <c r="B20" t="n">
-        <v>91875</v>
+        <v>91876</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>132617548</v>
       </c>
       <c r="B21" t="n">
-        <v>91875</v>
+        <v>91876</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>132623302</v>
       </c>
       <c r="B22" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>132617600</v>
       </c>
       <c r="B23" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>132623268</v>
       </c>
       <c r="B24" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>132617601</v>
       </c>
       <c r="B25" t="n">
-        <v>80393</v>
+        <v>80394</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>132617580</v>
       </c>
       <c r="B26" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3591,10 +3591,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132617568</v>
+        <v>132623295</v>
       </c>
       <c r="B28" t="n">
-        <v>97986</v>
+        <v>101330</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3602,37 +3602,45 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>672748</v>
+        <v>672594</v>
       </c>
       <c r="R28" t="n">
-        <v>6981368</v>
+        <v>6981486</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3661,7 +3669,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3671,7 +3679,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3680,28 +3688,29 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132623266</v>
+        <v>132623272</v>
       </c>
       <c r="B29" t="n">
-        <v>97980</v>
+        <v>101330</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3709,33 +3718,45 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221944</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672878</v>
+        <v>672787</v>
       </c>
       <c r="R29" t="n">
-        <v>6981334</v>
+        <v>6981316</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3764,7 +3785,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3774,7 +3795,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3795,17 +3816,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132623295</v>
+        <v>132617568</v>
       </c>
       <c r="B30" t="n">
-        <v>101329</v>
+        <v>97987</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3813,45 +3834,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672594</v>
+        <v>672748</v>
       </c>
       <c r="R30" t="n">
-        <v>6981486</v>
+        <v>6981368</v>
       </c>
       <c r="S30" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3880,7 +3893,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3890,7 +3903,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3899,29 +3912,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132623272</v>
+        <v>132623266</v>
       </c>
       <c r="B31" t="n">
-        <v>101329</v>
+        <v>97981</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3929,45 +3941,33 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>221944</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>672787</v>
+        <v>672878</v>
       </c>
       <c r="R31" t="n">
-        <v>6981316</v>
+        <v>6981334</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4037,7 +4037,7 @@
         <v>132623278</v>
       </c>
       <c r="B32" t="n">
-        <v>97986</v>
+        <v>97987</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>132617586</v>
       </c>
       <c r="B33" t="n">
-        <v>91875</v>
+        <v>91876</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4363,10 +4363,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132617596</v>
+        <v>132623274</v>
       </c>
       <c r="B35" t="n">
-        <v>97986</v>
+        <v>101330</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4374,37 +4374,45 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>672810</v>
+        <v>672744</v>
       </c>
       <c r="R35" t="n">
-        <v>6981546</v>
+        <v>6981271</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4433,7 +4441,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4443,7 +4451,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4452,28 +4460,29 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132623274</v>
+        <v>132617596</v>
       </c>
       <c r="B36" t="n">
-        <v>101329</v>
+        <v>97987</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4481,45 +4490,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>672744</v>
+        <v>672810</v>
       </c>
       <c r="R36" t="n">
-        <v>6981271</v>
+        <v>6981546</v>
       </c>
       <c r="S36" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4548,7 +4549,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4558,7 +4559,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4567,64 +4568,66 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132617599</v>
+        <v>132617557</v>
       </c>
       <c r="B37" t="n">
-        <v>79328</v>
+        <v>80394</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>672664</v>
+        <v>672878</v>
       </c>
       <c r="R37" t="n">
-        <v>6981552</v>
+        <v>6981324</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4656,7 +4659,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4666,7 +4669,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4675,8 +4678,24 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4693,48 +4712,56 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132617564</v>
+        <v>132623285</v>
       </c>
       <c r="B38" t="n">
-        <v>80433</v>
+        <v>101330</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672831</v>
+        <v>672638</v>
       </c>
       <c r="R38" t="n">
-        <v>6981363</v>
+        <v>6981364</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4763,7 +4790,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4773,7 +4800,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4782,18 +4809,19 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4803,7 +4831,7 @@
         <v>132623290</v>
       </c>
       <c r="B39" t="n">
-        <v>97986</v>
+        <v>97987</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4907,48 +4935,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132617557</v>
+        <v>132617599</v>
       </c>
       <c r="B40" t="n">
-        <v>80393</v>
+        <v>79329</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672878</v>
+        <v>672664</v>
       </c>
       <c r="R40" t="n">
-        <v>6981324</v>
+        <v>6981552</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -4980,7 +5005,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4990,7 +5015,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4999,24 +5024,8 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5033,56 +5042,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132623285</v>
+        <v>132617564</v>
       </c>
       <c r="B41" t="n">
-        <v>101329</v>
+        <v>80434</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>672638</v>
+        <v>672831</v>
       </c>
       <c r="R41" t="n">
-        <v>6981364</v>
+        <v>6981363</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5111,7 +5112,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5121,7 +5122,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5130,64 +5131,66 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132617592</v>
+        <v>132617607</v>
       </c>
       <c r="B42" t="n">
-        <v>80393</v>
+        <v>79329</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>672709</v>
+        <v>672712</v>
       </c>
       <c r="R42" t="n">
-        <v>6981488</v>
+        <v>6981164</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -5219,7 +5222,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5229,7 +5232,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5238,8 +5241,24 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5256,48 +5275,56 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132617558</v>
+        <v>132623256</v>
       </c>
       <c r="B43" t="n">
-        <v>80306</v>
+        <v>101330</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>392</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672873</v>
+        <v>672930</v>
       </c>
       <c r="R43" t="n">
-        <v>6981339</v>
+        <v>6981133</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5326,7 +5353,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5336,7 +5363,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5345,69 +5372,67 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132617607</v>
+        <v>132617558</v>
       </c>
       <c r="B44" t="n">
-        <v>79328</v>
+        <v>80307</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672712</v>
+        <v>672873</v>
       </c>
       <c r="R44" t="n">
-        <v>6981164</v>
+        <v>6981339</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5436,7 +5461,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5446,7 +5471,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5455,24 +5480,8 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5489,10 +5498,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132623256</v>
+        <v>132617592</v>
       </c>
       <c r="B45" t="n">
-        <v>101329</v>
+        <v>80394</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5500,45 +5509,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672930</v>
+        <v>672709</v>
       </c>
       <c r="R45" t="n">
-        <v>6981133</v>
+        <v>6981488</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5567,7 +5568,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5577,7 +5578,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5586,61 +5587,55 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132623254</v>
+        <v>132617567</v>
       </c>
       <c r="B46" t="n">
-        <v>101329</v>
+        <v>80434</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5648,13 +5643,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>672976</v>
+        <v>672776</v>
       </c>
       <c r="R46" t="n">
-        <v>6981122</v>
+        <v>6981332</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5683,7 +5678,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5693,7 +5688,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5706,25 +5701,40 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132623294</v>
+        <v>132623254</v>
       </c>
       <c r="B47" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5764,10 +5774,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>672601</v>
+        <v>672976</v>
       </c>
       <c r="R47" t="n">
-        <v>6981439</v>
+        <v>6981122</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5799,7 +5809,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5809,7 +5819,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5837,10 +5847,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132623300</v>
+        <v>132623294</v>
       </c>
       <c r="B48" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5880,13 +5890,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>672758</v>
+        <v>672601</v>
       </c>
       <c r="R48" t="n">
-        <v>6981513</v>
+        <v>6981439</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5915,7 +5925,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5925,7 +5935,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5953,10 +5963,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132617546</v>
+        <v>132623300</v>
       </c>
       <c r="B49" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5982,19 +5992,27 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672949</v>
+        <v>672758</v>
       </c>
       <c r="R49" t="n">
-        <v>6981130</v>
+        <v>6981513</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6023,7 +6041,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6033,7 +6051,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6042,69 +6060,67 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132617567</v>
+        <v>132617546</v>
       </c>
       <c r="B50" t="n">
-        <v>80433</v>
+        <v>101330</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>672776</v>
+        <v>672949</v>
       </c>
       <c r="R50" t="n">
-        <v>6981332</v>
+        <v>6981130</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6133,7 +6149,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6143,7 +6159,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6152,24 +6168,8 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6306,46 +6306,41 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132617589</v>
+        <v>132617595</v>
       </c>
       <c r="B52" t="n">
-        <v>99121</v>
+        <v>79329</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6353,13 +6348,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672627</v>
+        <v>672745</v>
       </c>
       <c r="R52" t="n">
-        <v>6981425</v>
+        <v>6981544</v>
       </c>
       <c r="S52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6388,7 +6383,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6398,7 +6393,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6426,48 +6421,65 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132617566</v>
+        <v>132617603</v>
       </c>
       <c r="B53" t="n">
-        <v>80393</v>
+        <v>57954</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>672774</v>
+        <v>672617</v>
       </c>
       <c r="R53" t="n">
-        <v>6981334</v>
+        <v>6981488</v>
       </c>
       <c r="S53" t="n">
         <v>2</v>
@@ -6499,7 +6511,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6509,7 +6521,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6518,24 +6530,8 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6552,41 +6548,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132617595</v>
+        <v>132623292</v>
       </c>
       <c r="B54" t="n">
-        <v>79328</v>
+        <v>101330</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6594,13 +6591,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672745</v>
+        <v>672655</v>
       </c>
       <c r="R54" t="n">
-        <v>6981544</v>
+        <v>6981418</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6629,7 +6626,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6639,7 +6636,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6655,77 +6652,69 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132617603</v>
+        <v>132617589</v>
       </c>
       <c r="B55" t="n">
-        <v>57954</v>
+        <v>99122</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672617</v>
+        <v>672627</v>
       </c>
       <c r="R55" t="n">
-        <v>6981488</v>
+        <v>6981425</v>
       </c>
       <c r="S55" t="n">
         <v>2</v>
@@ -6757,7 +6746,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6767,7 +6756,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6776,6 +6765,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6794,10 +6784,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132623292</v>
+        <v>132617566</v>
       </c>
       <c r="B56" t="n">
-        <v>101329</v>
+        <v>80394</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6805,31 +6795,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6837,13 +6822,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>672655</v>
+        <v>672774</v>
       </c>
       <c r="R56" t="n">
-        <v>6981418</v>
+        <v>6981334</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6872,7 +6857,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6882,7 +6867,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6895,63 +6880,81 @@
       <c r="AG56" t="b">
         <v>0</v>
       </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132617602</v>
+        <v>132623271</v>
       </c>
       <c r="B57" t="n">
-        <v>97986</v>
+        <v>80434</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>672593</v>
+        <v>672780</v>
       </c>
       <c r="R57" t="n">
-        <v>6981519</v>
+        <v>6981331</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6980,7 +6983,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6990,7 +6993,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6999,28 +7002,44 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132623271</v>
+        <v>132617549</v>
       </c>
       <c r="B58" t="n">
-        <v>80433</v>
+        <v>80434</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7055,13 +7074,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>672780</v>
+        <v>672932</v>
       </c>
       <c r="R58" t="n">
-        <v>6981331</v>
+        <v>6981224</v>
       </c>
       <c r="S58" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7090,7 +7109,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7100,7 +7119,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7131,12 +7150,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7146,7 +7165,7 @@
         <v>132617555</v>
       </c>
       <c r="B59" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7250,48 +7269,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132617549</v>
+        <v>132617602</v>
       </c>
       <c r="B60" t="n">
-        <v>80433</v>
+        <v>97987</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672932</v>
+        <v>672593</v>
       </c>
       <c r="R60" t="n">
-        <v>6981224</v>
+        <v>6981519</v>
       </c>
       <c r="S60" t="n">
         <v>3</v>
@@ -7323,7 +7339,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7333,7 +7349,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7342,24 +7358,8 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7498,7 +7498,7 @@
         <v>132623265</v>
       </c>
       <c r="B62" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>132623280</v>
       </c>
       <c r="B63" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>132617606</v>
       </c>
       <c r="B64" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7834,45 +7834,52 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132617574</v>
+        <v>132617591</v>
       </c>
       <c r="B65" t="n">
-        <v>91875</v>
+        <v>80434</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>672695</v>
+        <v>672709</v>
       </c>
       <c r="R65" t="n">
-        <v>6981312</v>
+        <v>6981489</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -7904,7 +7911,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7914,7 +7921,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Växandes på fyra närliggande aspträd</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7923,8 +7935,24 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -7941,52 +7969,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132617591</v>
+        <v>132617574</v>
       </c>
       <c r="B66" t="n">
-        <v>80433</v>
+        <v>91876</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>672709</v>
+        <v>672695</v>
       </c>
       <c r="R66" t="n">
-        <v>6981489</v>
+        <v>6981312</v>
       </c>
       <c r="S66" t="n">
         <v>3</v>
@@ -8018,7 +8039,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8028,12 +8049,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Växandes på fyra närliggande aspträd</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8042,24 +8058,8 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8079,7 +8079,7 @@
         <v>132617560</v>
       </c>
       <c r="B67" t="n">
-        <v>97986</v>
+        <v>97987</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>132617553</v>
       </c>
       <c r="B68" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8290,32 +8290,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132617584</v>
+        <v>132617598</v>
       </c>
       <c r="B69" t="n">
-        <v>91875</v>
+        <v>92333</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>6040186</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8325,13 +8325,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>672639</v>
+        <v>672763</v>
       </c>
       <c r="R69" t="n">
-        <v>6981355</v>
+        <v>6981545</v>
       </c>
       <c r="S69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8379,8 +8379,24 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8397,37 +8413,42 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132623267</v>
+        <v>132623305</v>
       </c>
       <c r="B70" t="n">
-        <v>79328</v>
+        <v>101330</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8435,10 +8456,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>672869</v>
+        <v>672911</v>
       </c>
       <c r="R70" t="n">
-        <v>6981357</v>
+        <v>6981136</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8470,7 +8491,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8480,7 +8501,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8492,21 +8513,6 @@
       <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8523,37 +8529,42 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132623263</v>
+        <v>132623253</v>
       </c>
       <c r="B71" t="n">
-        <v>79328</v>
+        <v>101330</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -8561,13 +8572,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672878</v>
+        <v>672918</v>
       </c>
       <c r="R71" t="n">
-        <v>6981321</v>
+        <v>6980944</v>
       </c>
       <c r="S71" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8596,7 +8607,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8606,7 +8617,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8618,21 +8629,6 @@
       <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8649,10 +8645,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132617561</v>
+        <v>132617556</v>
       </c>
       <c r="B72" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8684,10 +8680,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>672878</v>
+        <v>672881</v>
       </c>
       <c r="R72" t="n">
-        <v>6981375</v>
+        <v>6981314</v>
       </c>
       <c r="S72" t="n">
         <v>3</v>
@@ -8719,7 +8715,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8729,7 +8725,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På stående död gran</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8756,10 +8757,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132617598</v>
+        <v>132617561</v>
       </c>
       <c r="B73" t="n">
-        <v>92332</v>
+        <v>91913</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8767,21 +8768,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6040186</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8791,13 +8792,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>672763</v>
+        <v>672878</v>
       </c>
       <c r="R73" t="n">
-        <v>6981545</v>
+        <v>6981375</v>
       </c>
       <c r="S73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8826,7 +8827,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8836,7 +8837,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8845,24 +8846,8 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8879,10 +8864,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132617556</v>
+        <v>132623267</v>
       </c>
       <c r="B74" t="n">
-        <v>91912</v>
+        <v>79329</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8890,37 +8875,40 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>672881</v>
+        <v>672869</v>
       </c>
       <c r="R74" t="n">
-        <v>6981314</v>
+        <v>6981357</v>
       </c>
       <c r="S74" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8949,7 +8937,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8959,12 +8947,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:25</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På stående död gran</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8973,28 +8956,44 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132623305</v>
+        <v>132617584</v>
       </c>
       <c r="B75" t="n">
-        <v>101329</v>
+        <v>91876</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9002,45 +9001,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672911</v>
+        <v>672639</v>
       </c>
       <c r="R75" t="n">
-        <v>6981136</v>
+        <v>6981355</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9069,7 +9060,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9079,7 +9070,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9088,61 +9079,55 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132623253</v>
+        <v>132623263</v>
       </c>
       <c r="B76" t="n">
-        <v>101329</v>
+        <v>79329</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9150,13 +9135,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>672918</v>
+        <v>672878</v>
       </c>
       <c r="R76" t="n">
-        <v>6980944</v>
+        <v>6981321</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9185,7 +9170,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9195,7 +9180,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9207,6 +9192,21 @@
       <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9338,37 +9338,42 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132617559</v>
+        <v>132617575</v>
       </c>
       <c r="B78" t="n">
-        <v>80433</v>
+        <v>57946</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>100110</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -9376,13 +9381,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>672887</v>
+        <v>672681</v>
       </c>
       <c r="R78" t="n">
-        <v>6981335</v>
+        <v>6981300</v>
       </c>
       <c r="S78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9411,7 +9416,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9421,7 +9426,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Sång i över en minut.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9430,24 +9440,8 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9464,42 +9458,37 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132617575</v>
+        <v>132617559</v>
       </c>
       <c r="B79" t="n">
-        <v>57946</v>
+        <v>80434</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100110</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -9507,13 +9496,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>672681</v>
+        <v>672887</v>
       </c>
       <c r="R79" t="n">
-        <v>6981300</v>
+        <v>6981335</v>
       </c>
       <c r="S79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9542,7 +9531,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9552,12 +9541,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Sång i över en minut.</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9566,8 +9550,24 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9584,10 +9584,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132623275</v>
+        <v>132623284</v>
       </c>
       <c r="B80" t="n">
-        <v>101329</v>
+        <v>97987</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9595,45 +9595,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>672670</v>
+        <v>672622</v>
       </c>
       <c r="R80" t="n">
-        <v>6981289</v>
+        <v>6981351</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9662,7 +9654,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9672,7 +9664,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9681,7 +9673,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9700,10 +9691,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132623257</v>
+        <v>132617585</v>
       </c>
       <c r="B81" t="n">
-        <v>101329</v>
+        <v>80394</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9711,31 +9702,26 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -9743,13 +9729,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>672951</v>
+        <v>672635</v>
       </c>
       <c r="R81" t="n">
-        <v>6981191</v>
+        <v>6981376</v>
       </c>
       <c r="S81" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9778,7 +9764,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9788,7 +9774,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9801,25 +9787,40 @@
       <c r="AG81" t="b">
         <v>0</v>
       </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132617585</v>
+        <v>132623275</v>
       </c>
       <c r="B82" t="n">
-        <v>80393</v>
+        <v>101330</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9827,26 +9828,31 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9854,13 +9860,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>672635</v>
+        <v>672670</v>
       </c>
       <c r="R82" t="n">
-        <v>6981376</v>
+        <v>6981289</v>
       </c>
       <c r="S82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9889,7 +9895,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9899,7 +9905,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9912,40 +9918,25 @@
       <c r="AG82" t="b">
         <v>0</v>
       </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132623284</v>
+        <v>132623257</v>
       </c>
       <c r="B83" t="n">
-        <v>97986</v>
+        <v>101330</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9953,37 +9944,45 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>672622</v>
+        <v>672951</v>
       </c>
       <c r="R83" t="n">
-        <v>6981351</v>
+        <v>6981191</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10012,7 +10011,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10022,7 +10021,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10031,6 +10030,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -10049,37 +10049,42 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132617594</v>
+        <v>132623255</v>
       </c>
       <c r="B84" t="n">
-        <v>91912</v>
+        <v>101330</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -10087,13 +10092,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>672755</v>
+        <v>672955</v>
       </c>
       <c r="R84" t="n">
-        <v>6981496</v>
+        <v>6981134</v>
       </c>
       <c r="S84" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10122,7 +10127,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10132,7 +10137,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10148,54 +10153,49 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132623255</v>
+        <v>132617594</v>
       </c>
       <c r="B85" t="n">
-        <v>101329</v>
+        <v>91913</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -10203,13 +10203,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>672955</v>
+        <v>672755</v>
       </c>
       <c r="R85" t="n">
-        <v>6981134</v>
+        <v>6981496</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10264,12 +10264,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10279,7 +10279,7 @@
         <v>132617587</v>
       </c>
       <c r="B86" t="n">
-        <v>80393</v>
+        <v>80394</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>132623277</v>
       </c>
       <c r="B87" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>132617577</v>
       </c>
       <c r="B88" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10630,10 +10630,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132623291</v>
+        <v>132617562</v>
       </c>
       <c r="B89" t="n">
-        <v>101329</v>
+        <v>91876</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10641,45 +10641,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>672630</v>
+        <v>672869</v>
       </c>
       <c r="R89" t="n">
-        <v>6981380</v>
+        <v>6981366</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10708,7 +10700,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10718,7 +10710,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10727,75 +10719,66 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132623304</v>
+        <v>132617583</v>
       </c>
       <c r="B90" t="n">
-        <v>101329</v>
+        <v>79329</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>672732</v>
+        <v>672577</v>
       </c>
       <c r="R90" t="n">
-        <v>6981161</v>
+        <v>6981292</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10824,7 +10807,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10834,7 +10817,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10843,67 +10826,69 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132617562</v>
+        <v>132623270</v>
       </c>
       <c r="B91" t="n">
-        <v>91875</v>
+        <v>79329</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>672869</v>
+        <v>672831</v>
       </c>
       <c r="R91" t="n">
-        <v>6981366</v>
+        <v>6981355</v>
       </c>
       <c r="S91" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10932,7 +10917,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10942,7 +10927,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10951,28 +10936,44 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132617583</v>
+        <v>132617565</v>
       </c>
       <c r="B92" t="n">
-        <v>79328</v>
+        <v>80434</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10980,34 +10981,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>672577</v>
+        <v>672833</v>
       </c>
       <c r="R92" t="n">
-        <v>6981292</v>
+        <v>6981355</v>
       </c>
       <c r="S92" t="n">
         <v>3</v>
@@ -11039,7 +11043,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11049,7 +11053,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Växandes på björk.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11058,8 +11067,24 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -11076,37 +11101,42 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132623270</v>
+        <v>132623291</v>
       </c>
       <c r="B93" t="n">
-        <v>79328</v>
+        <v>101330</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -11114,10 +11144,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>672831</v>
+        <v>672630</v>
       </c>
       <c r="R93" t="n">
-        <v>6981355</v>
+        <v>6981380</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11149,7 +11179,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11159,7 +11189,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11171,21 +11201,6 @@
       <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11202,37 +11217,42 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132617565</v>
+        <v>132623304</v>
       </c>
       <c r="B94" t="n">
-        <v>80433</v>
+        <v>101330</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11240,13 +11260,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>672833</v>
+        <v>672732</v>
       </c>
       <c r="R94" t="n">
-        <v>6981355</v>
+        <v>6981161</v>
       </c>
       <c r="S94" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11275,7 +11295,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11285,12 +11305,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:09</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Växandes på björk.</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11303,40 +11318,25 @@
       <c r="AG94" t="b">
         <v>0</v>
       </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132617563</v>
+        <v>132623258</v>
       </c>
       <c r="B95" t="n">
-        <v>97986</v>
+        <v>101330</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11344,37 +11344,45 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>672858</v>
+        <v>672971</v>
       </c>
       <c r="R95" t="n">
-        <v>6981365</v>
+        <v>6981202</v>
       </c>
       <c r="S95" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11403,7 +11411,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11413,7 +11421,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11422,28 +11430,29 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132617570</v>
+        <v>132623273</v>
       </c>
       <c r="B96" t="n">
-        <v>97986</v>
+        <v>101330</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11451,37 +11460,45 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>672723</v>
+        <v>672774</v>
       </c>
       <c r="R96" t="n">
-        <v>6981408</v>
+        <v>6981240</v>
       </c>
       <c r="S96" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11510,7 +11527,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11520,7 +11537,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11529,28 +11546,29 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132623299</v>
+        <v>132617563</v>
       </c>
       <c r="B97" t="n">
-        <v>97986</v>
+        <v>97987</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11582,13 +11600,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>672709</v>
+        <v>672858</v>
       </c>
       <c r="R97" t="n">
-        <v>6981494</v>
+        <v>6981365</v>
       </c>
       <c r="S97" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11617,7 +11635,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11627,7 +11645,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11642,22 +11660,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132623258</v>
+        <v>132617570</v>
       </c>
       <c r="B98" t="n">
-        <v>101329</v>
+        <v>97987</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11665,45 +11683,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>672971</v>
+        <v>672723</v>
       </c>
       <c r="R98" t="n">
-        <v>6981202</v>
+        <v>6981408</v>
       </c>
       <c r="S98" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11732,7 +11742,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11742,7 +11752,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11751,29 +11761,28 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132623273</v>
+        <v>132623299</v>
       </c>
       <c r="B99" t="n">
-        <v>101329</v>
+        <v>97987</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11781,45 +11790,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>672774</v>
+        <v>672709</v>
       </c>
       <c r="R99" t="n">
-        <v>6981240</v>
+        <v>6981494</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11848,7 +11849,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11858,7 +11859,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11867,7 +11868,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13423-2026 artfynd.xlsx
+++ b/artfynd/A 13423-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132617547</v>
+        <v>132617578</v>
       </c>
       <c r="B2" t="n">
-        <v>79329</v>
+        <v>91913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672932</v>
+        <v>672651</v>
       </c>
       <c r="R2" t="n">
-        <v>6981174</v>
+        <v>6981280</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132617578</v>
+        <v>132617547</v>
       </c>
       <c r="B3" t="n">
-        <v>91913</v>
+        <v>79329</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672651</v>
+        <v>672932</v>
       </c>
       <c r="R3" t="n">
-        <v>6981280</v>
+        <v>6981174</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -996,48 +996,56 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132617551</v>
+        <v>132623293</v>
       </c>
       <c r="B5" t="n">
-        <v>91913</v>
+        <v>101330</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>672976</v>
+        <v>672629</v>
       </c>
       <c r="R5" t="n">
-        <v>6981217</v>
+        <v>6981435</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1084,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,60 +1093,61 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132617572</v>
+        <v>132623296</v>
       </c>
       <c r="B6" t="n">
-        <v>57951</v>
+        <v>101330</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1146,13 +1155,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>672701</v>
+        <v>672649</v>
       </c>
       <c r="R6" t="n">
-        <v>6981350</v>
+        <v>6981516</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1181,7 +1190,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1191,7 +1200,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,28 +1209,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132623293</v>
+        <v>132623279</v>
       </c>
       <c r="B7" t="n">
-        <v>101330</v>
+        <v>97987</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,42 +1239,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>672629</v>
+        <v>672637</v>
       </c>
       <c r="R7" t="n">
-        <v>6981435</v>
+        <v>6981289</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1296,7 +1298,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1306,7 +1308,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,7 +1317,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1334,42 +1335,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132623296</v>
+        <v>132617572</v>
       </c>
       <c r="B8" t="n">
-        <v>101330</v>
+        <v>57951</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1377,13 +1378,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>672649</v>
+        <v>672701</v>
       </c>
       <c r="R8" t="n">
-        <v>6981516</v>
+        <v>6981350</v>
       </c>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1412,7 +1413,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1422,7 +1423,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1431,51 +1432,50 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132623279</v>
+        <v>132617551</v>
       </c>
       <c r="B9" t="n">
-        <v>97987</v>
+        <v>91913</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1485,13 +1485,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>672637</v>
+        <v>672976</v>
       </c>
       <c r="R9" t="n">
-        <v>6981289</v>
+        <v>6981217</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,76 +1545,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132617605</v>
+        <v>132623301</v>
       </c>
       <c r="B10" t="n">
-        <v>57954</v>
+        <v>97987</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672801</v>
+        <v>672767</v>
       </c>
       <c r="R10" t="n">
-        <v>6981249</v>
+        <v>6981492</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1643,7 +1627,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1653,12 +1637,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Två födosökande individer varav en hona</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,54 +1652,54 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132617571</v>
+        <v>132623282</v>
       </c>
       <c r="B11" t="n">
-        <v>57954</v>
+        <v>101330</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1728,13 +1707,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672713</v>
+        <v>672633</v>
       </c>
       <c r="R11" t="n">
-        <v>6981357</v>
+        <v>6981324</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1763,7 +1742,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,12 +1752,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1787,28 +1761,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132617554</v>
+        <v>132617550</v>
       </c>
       <c r="B12" t="n">
-        <v>91913</v>
+        <v>57951</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,34 +1791,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672912</v>
+        <v>672983</v>
       </c>
       <c r="R12" t="n">
-        <v>6981315</v>
+        <v>6981247</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1875,7 +1858,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1868,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,45 +1895,61 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132617579</v>
+        <v>132617605</v>
       </c>
       <c r="B13" t="n">
-        <v>91876</v>
+        <v>57954</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672651</v>
+        <v>672801</v>
       </c>
       <c r="R13" t="n">
-        <v>6981280</v>
+        <v>6981249</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -1982,7 +1981,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1991,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Två födosökande individer varav en hona</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132617550</v>
+        <v>132617571</v>
       </c>
       <c r="B14" t="n">
-        <v>57951</v>
+        <v>57954</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,16 +2034,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2052,7 +2056,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2062,13 +2066,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672983</v>
+        <v>672713</v>
       </c>
       <c r="R14" t="n">
-        <v>6981247</v>
+        <v>6981357</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2097,7 +2101,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2107,7 +2111,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2134,56 +2143,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132623282</v>
+        <v>132617554</v>
       </c>
       <c r="B15" t="n">
-        <v>101330</v>
+        <v>91913</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672633</v>
+        <v>672912</v>
       </c>
       <c r="R15" t="n">
-        <v>6981324</v>
+        <v>6981315</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2212,7 +2213,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2222,7 +2223,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,29 +2232,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132623301</v>
+        <v>132617579</v>
       </c>
       <c r="B16" t="n">
-        <v>97987</v>
+        <v>91876</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,21 +2261,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2285,13 +2285,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672767</v>
+        <v>672651</v>
       </c>
       <c r="R16" t="n">
-        <v>6981492</v>
+        <v>6981280</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2345,12 +2345,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -4586,48 +4586,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132617557</v>
+        <v>132617599</v>
       </c>
       <c r="B37" t="n">
-        <v>80394</v>
+        <v>79329</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>672878</v>
+        <v>672664</v>
       </c>
       <c r="R37" t="n">
-        <v>6981324</v>
+        <v>6981552</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4659,7 +4656,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4669,7 +4666,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4678,24 +4675,8 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4712,56 +4693,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132623285</v>
+        <v>132617564</v>
       </c>
       <c r="B38" t="n">
-        <v>101330</v>
+        <v>80434</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672638</v>
+        <v>672831</v>
       </c>
       <c r="R38" t="n">
-        <v>6981364</v>
+        <v>6981363</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4790,7 +4763,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4800,7 +4773,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4809,29 +4782,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132623290</v>
+        <v>132623285</v>
       </c>
       <c r="B39" t="n">
-        <v>97987</v>
+        <v>101330</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4839,37 +4811,45 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>672621</v>
+        <v>672638</v>
       </c>
       <c r="R39" t="n">
-        <v>6981383</v>
+        <v>6981364</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4898,7 +4878,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4908,7 +4888,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4917,6 +4897,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4935,45 +4916,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132617599</v>
+        <v>132617557</v>
       </c>
       <c r="B40" t="n">
-        <v>79329</v>
+        <v>80394</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672664</v>
+        <v>672878</v>
       </c>
       <c r="R40" t="n">
-        <v>6981552</v>
+        <v>6981324</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -5005,7 +4989,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5015,7 +4999,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5024,8 +5008,24 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5042,32 +5042,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132617564</v>
+        <v>132623290</v>
       </c>
       <c r="B41" t="n">
-        <v>80434</v>
+        <v>97987</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5077,13 +5077,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>672831</v>
+        <v>672621</v>
       </c>
       <c r="R41" t="n">
-        <v>6981363</v>
+        <v>6981383</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5137,12 +5137,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -6306,41 +6306,42 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132617595</v>
+        <v>132623292</v>
       </c>
       <c r="B52" t="n">
-        <v>79329</v>
+        <v>101330</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6348,13 +6349,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672745</v>
+        <v>672655</v>
       </c>
       <c r="R52" t="n">
-        <v>6981544</v>
+        <v>6981418</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6383,7 +6384,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6393,7 +6394,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6409,77 +6410,69 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132617603</v>
+        <v>132617589</v>
       </c>
       <c r="B53" t="n">
-        <v>57954</v>
+        <v>99122</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>672617</v>
+        <v>672627</v>
       </c>
       <c r="R53" t="n">
-        <v>6981488</v>
+        <v>6981425</v>
       </c>
       <c r="S53" t="n">
         <v>2</v>
@@ -6511,7 +6504,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6521,7 +6514,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6530,6 +6523,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6548,10 +6542,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132623292</v>
+        <v>132617566</v>
       </c>
       <c r="B54" t="n">
-        <v>101330</v>
+        <v>80394</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6559,31 +6553,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6591,13 +6580,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672655</v>
+        <v>672774</v>
       </c>
       <c r="R54" t="n">
-        <v>6981418</v>
+        <v>6981334</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6626,7 +6615,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6636,7 +6625,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6649,72 +6638,95 @@
       <c r="AG54" t="b">
         <v>0</v>
       </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132617589</v>
+        <v>132617603</v>
       </c>
       <c r="B55" t="n">
-        <v>99122</v>
+        <v>57954</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672627</v>
+        <v>672617</v>
       </c>
       <c r="R55" t="n">
-        <v>6981425</v>
+        <v>6981488</v>
       </c>
       <c r="S55" t="n">
         <v>2</v>
@@ -6746,7 +6758,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6756,7 +6768,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6765,7 +6777,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6784,37 +6795,41 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132617566</v>
+        <v>132617595</v>
       </c>
       <c r="B56" t="n">
-        <v>80394</v>
+        <v>79329</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6822,13 +6837,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>672774</v>
+        <v>672745</v>
       </c>
       <c r="R56" t="n">
-        <v>6981334</v>
+        <v>6981544</v>
       </c>
       <c r="S56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6857,7 +6872,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6867,7 +6882,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6879,21 +6894,6 @@
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7834,52 +7834,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132617591</v>
+        <v>132617553</v>
       </c>
       <c r="B65" t="n">
-        <v>80434</v>
+        <v>101330</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>672709</v>
+        <v>672931</v>
       </c>
       <c r="R65" t="n">
-        <v>6981489</v>
+        <v>6981286</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -7911,7 +7904,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7921,12 +7914,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Växandes på fyra närliggande aspträd</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7935,24 +7923,8 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -7969,45 +7941,52 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132617574</v>
+        <v>132617591</v>
       </c>
       <c r="B66" t="n">
-        <v>91876</v>
+        <v>80434</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>672695</v>
+        <v>672709</v>
       </c>
       <c r="R66" t="n">
-        <v>6981312</v>
+        <v>6981489</v>
       </c>
       <c r="S66" t="n">
         <v>3</v>
@@ -8039,7 +8018,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8049,7 +8028,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Växandes på fyra närliggande aspträd</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8058,8 +8042,24 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8076,10 +8076,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132617560</v>
+        <v>132617574</v>
       </c>
       <c r="B67" t="n">
-        <v>97987</v>
+        <v>91876</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8087,21 +8087,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8111,13 +8111,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>672883</v>
+        <v>672695</v>
       </c>
       <c r="R67" t="n">
-        <v>6981346</v>
+        <v>6981312</v>
       </c>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8183,10 +8183,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132617553</v>
+        <v>132617560</v>
       </c>
       <c r="B68" t="n">
-        <v>101330</v>
+        <v>97987</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8194,21 +8194,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8218,13 +8218,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>672931</v>
+        <v>672883</v>
       </c>
       <c r="R68" t="n">
-        <v>6981286</v>
+        <v>6981346</v>
       </c>
       <c r="S68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8290,10 +8290,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132617598</v>
+        <v>132617556</v>
       </c>
       <c r="B69" t="n">
-        <v>92333</v>
+        <v>91913</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8301,21 +8301,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6040186</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8325,13 +8325,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>672763</v>
+        <v>672881</v>
       </c>
       <c r="R69" t="n">
-        <v>6981545</v>
+        <v>6981314</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8370,7 +8370,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På stående död gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8379,24 +8384,8 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8413,56 +8402,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132623305</v>
+        <v>132617561</v>
       </c>
       <c r="B70" t="n">
-        <v>101330</v>
+        <v>91913</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>672911</v>
+        <v>672878</v>
       </c>
       <c r="R70" t="n">
-        <v>6981136</v>
+        <v>6981375</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8491,7 +8472,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8501,7 +8482,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8510,75 +8491,66 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132623253</v>
+        <v>132617598</v>
       </c>
       <c r="B71" t="n">
-        <v>101330</v>
+        <v>92333</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222498</v>
+        <v>6040186</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672918</v>
+        <v>672763</v>
       </c>
       <c r="R71" t="n">
-        <v>6980944</v>
+        <v>6981545</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8607,7 +8579,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8617,7 +8589,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8630,63 +8602,86 @@
       <c r="AG71" t="b">
         <v>0</v>
       </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132617556</v>
+        <v>132623253</v>
       </c>
       <c r="B72" t="n">
-        <v>91913</v>
+        <v>101330</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>672881</v>
+        <v>672918</v>
       </c>
       <c r="R72" t="n">
-        <v>6981314</v>
+        <v>6980944</v>
       </c>
       <c r="S72" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8715,7 +8710,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8725,12 +8720,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:25</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På stående död gran</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8739,66 +8729,75 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132617561</v>
+        <v>132623305</v>
       </c>
       <c r="B73" t="n">
-        <v>91913</v>
+        <v>101330</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>672878</v>
+        <v>672911</v>
       </c>
       <c r="R73" t="n">
-        <v>6981375</v>
+        <v>6981136</v>
       </c>
       <c r="S73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8827,7 +8826,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8837,7 +8836,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8846,18 +8845,19 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -9223,10 +9223,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132617552</v>
+        <v>132617559</v>
       </c>
       <c r="B77" t="n">
-        <v>57951</v>
+        <v>80434</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9234,31 +9234,26 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9266,10 +9261,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>672968</v>
+        <v>672887</v>
       </c>
       <c r="R77" t="n">
-        <v>6981202</v>
+        <v>6981335</v>
       </c>
       <c r="S77" t="n">
         <v>1</v>
@@ -9301,7 +9296,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9311,7 +9306,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9320,8 +9315,24 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9338,32 +9349,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132617575</v>
+        <v>132617552</v>
       </c>
       <c r="B78" t="n">
-        <v>57946</v>
+        <v>57951</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100110</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9371,7 +9382,7 @@
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -9381,13 +9392,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>672681</v>
+        <v>672968</v>
       </c>
       <c r="R78" t="n">
-        <v>6981300</v>
+        <v>6981202</v>
       </c>
       <c r="S78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9416,7 +9427,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9426,12 +9437,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Sång i över en minut.</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9458,37 +9464,42 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132617559</v>
+        <v>132617575</v>
       </c>
       <c r="B79" t="n">
-        <v>80434</v>
+        <v>57946</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>100110</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -9496,13 +9507,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>672887</v>
+        <v>672681</v>
       </c>
       <c r="R79" t="n">
-        <v>6981335</v>
+        <v>6981300</v>
       </c>
       <c r="S79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9531,7 +9542,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9541,7 +9552,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Sång i över en minut.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9550,24 +9566,8 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -10844,37 +10844,42 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132623270</v>
+        <v>132623291</v>
       </c>
       <c r="B91" t="n">
-        <v>79329</v>
+        <v>101330</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -10882,10 +10887,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>672831</v>
+        <v>672630</v>
       </c>
       <c r="R91" t="n">
-        <v>6981355</v>
+        <v>6981380</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10917,7 +10922,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10927,7 +10932,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10939,21 +10944,6 @@
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
@@ -10970,37 +10960,42 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132617565</v>
+        <v>132623304</v>
       </c>
       <c r="B92" t="n">
-        <v>80434</v>
+        <v>101330</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -11008,13 +11003,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>672833</v>
+        <v>672732</v>
       </c>
       <c r="R92" t="n">
-        <v>6981355</v>
+        <v>6981161</v>
       </c>
       <c r="S92" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11043,7 +11038,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11053,12 +11048,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:09</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Växandes på björk.</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11071,72 +11061,52 @@
       <c r="AG92" t="b">
         <v>0</v>
       </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132623291</v>
+        <v>132623270</v>
       </c>
       <c r="B93" t="n">
-        <v>101330</v>
+        <v>79329</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -11144,10 +11114,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>672630</v>
+        <v>672831</v>
       </c>
       <c r="R93" t="n">
-        <v>6981380</v>
+        <v>6981355</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11179,7 +11149,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11189,7 +11159,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11201,6 +11171,21 @@
       <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11217,42 +11202,37 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132623304</v>
+        <v>132617565</v>
       </c>
       <c r="B94" t="n">
-        <v>101330</v>
+        <v>80434</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11260,13 +11240,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>672732</v>
+        <v>672833</v>
       </c>
       <c r="R94" t="n">
-        <v>6981161</v>
+        <v>6981355</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11295,7 +11275,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11305,7 +11285,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Växandes på björk.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11318,15 +11303,30 @@
       <c r="AG94" t="b">
         <v>0</v>
       </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>

--- a/artfynd/A 13423-2026 artfynd.xlsx
+++ b/artfynd/A 13423-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132617547</v>
+        <v>132617578</v>
       </c>
       <c r="B2" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672932</v>
+        <v>672651</v>
       </c>
       <c r="R2" t="n">
-        <v>6981174</v>
+        <v>6981280</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132617578</v>
+        <v>132617597</v>
       </c>
       <c r="B3" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672651</v>
+        <v>672762</v>
       </c>
       <c r="R3" t="n">
-        <v>6981280</v>
+        <v>6981535</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132617597</v>
+        <v>132617547</v>
       </c>
       <c r="B4" t="n">
-        <v>91881</v>
+        <v>79333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672762</v>
+        <v>672932</v>
       </c>
       <c r="R4" t="n">
-        <v>6981535</v>
+        <v>6981174</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1557,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132617554</v>
+        <v>132617550</v>
       </c>
       <c r="B10" t="n">
-        <v>91918</v>
+        <v>57955</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,34 +1568,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672912</v>
+        <v>672983</v>
       </c>
       <c r="R10" t="n">
-        <v>6981315</v>
+        <v>6981247</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1627,7 +1635,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1637,7 +1645,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,10 +1672,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132617550</v>
+        <v>132617554</v>
       </c>
       <c r="B11" t="n">
-        <v>57955</v>
+        <v>91918</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,42 +1683,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672983</v>
+        <v>672912</v>
       </c>
       <c r="R11" t="n">
-        <v>6981247</v>
+        <v>6981315</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1779,10 +1779,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132623282</v>
+        <v>132617579</v>
       </c>
       <c r="B12" t="n">
-        <v>101338</v>
+        <v>91881</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,45 +1790,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672633</v>
+        <v>672651</v>
       </c>
       <c r="R12" t="n">
-        <v>6981324</v>
+        <v>6981280</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1857,7 +1849,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1867,7 +1859,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1876,64 +1868,79 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132617579</v>
+        <v>132617605</v>
       </c>
       <c r="B13" t="n">
-        <v>91881</v>
+        <v>57958</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672651</v>
+        <v>672801</v>
       </c>
       <c r="R13" t="n">
-        <v>6981280</v>
+        <v>6981249</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -1965,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1975,7 +1982,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Två födosökande individer varav en hona</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2002,7 +2014,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132617605</v>
+        <v>132617571</v>
       </c>
       <c r="B14" t="n">
         <v>57958</v>
@@ -2030,36 +2042,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672801</v>
+        <v>672713</v>
       </c>
       <c r="R14" t="n">
-        <v>6981249</v>
+        <v>6981357</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2088,7 +2092,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2098,12 +2102,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Två födosökande individer varav en hona</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,42 +2134,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132617571</v>
+        <v>132623282</v>
       </c>
       <c r="B15" t="n">
-        <v>57958</v>
+        <v>101338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2173,13 +2177,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672713</v>
+        <v>672633</v>
       </c>
       <c r="R15" t="n">
-        <v>6981357</v>
+        <v>6981324</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2208,7 +2212,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2218,12 +2222,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2232,18 +2231,19 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2678,10 +2678,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132617600</v>
+        <v>132617588</v>
       </c>
       <c r="B20" t="n">
-        <v>101338</v>
+        <v>91881</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2713,13 +2713,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>672651</v>
+        <v>672671</v>
       </c>
       <c r="R20" t="n">
-        <v>6981546</v>
+        <v>6981418</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2785,10 +2785,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132617601</v>
+        <v>132617548</v>
       </c>
       <c r="B21" t="n">
-        <v>80398</v>
+        <v>91881</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,37 +2796,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229497</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>672548</v>
+        <v>672935</v>
       </c>
       <c r="R21" t="n">
-        <v>6981599</v>
+        <v>6981231</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2858,7 +2855,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2868,7 +2865,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2877,24 +2874,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2911,10 +2892,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132617588</v>
+        <v>132623302</v>
       </c>
       <c r="B22" t="n">
-        <v>91881</v>
+        <v>101338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2922,37 +2903,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>672671</v>
+        <v>672746</v>
       </c>
       <c r="R22" t="n">
-        <v>6981418</v>
+        <v>6981560</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2981,7 +2970,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2991,7 +2980,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3000,28 +2989,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132617548</v>
+        <v>132617600</v>
       </c>
       <c r="B23" t="n">
-        <v>91881</v>
+        <v>101338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3029,21 +3019,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3053,10 +3043,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672935</v>
+        <v>672651</v>
       </c>
       <c r="R23" t="n">
-        <v>6981231</v>
+        <v>6981546</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -3088,7 +3078,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3098,7 +3088,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3125,7 +3115,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132623302</v>
+        <v>132623268</v>
       </c>
       <c r="B24" t="n">
         <v>101338</v>
@@ -3168,13 +3158,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>672746</v>
+        <v>672837</v>
       </c>
       <c r="R24" t="n">
-        <v>6981560</v>
+        <v>6981360</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3203,7 +3193,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3213,7 +3203,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3241,10 +3231,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132623268</v>
+        <v>132617601</v>
       </c>
       <c r="B25" t="n">
-        <v>101338</v>
+        <v>80398</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3252,31 +3242,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3284,13 +3269,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>672837</v>
+        <v>672548</v>
       </c>
       <c r="R25" t="n">
-        <v>6981360</v>
+        <v>6981599</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3319,7 +3304,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3329,7 +3314,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3342,15 +3327,30 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3591,10 +3591,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132623272</v>
+        <v>132617568</v>
       </c>
       <c r="B28" t="n">
-        <v>101338</v>
+        <v>97995</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3602,45 +3602,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>672787</v>
+        <v>672748</v>
       </c>
       <c r="R28" t="n">
-        <v>6981316</v>
+        <v>6981368</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3669,7 +3661,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3679,7 +3671,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3688,29 +3680,28 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132623295</v>
+        <v>132623266</v>
       </c>
       <c r="B29" t="n">
-        <v>101338</v>
+        <v>97989</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3718,45 +3709,33 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>221944</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672594</v>
+        <v>672878</v>
       </c>
       <c r="R29" t="n">
-        <v>6981486</v>
+        <v>6981334</v>
       </c>
       <c r="S29" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3785,7 +3764,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3795,7 +3774,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3816,17 +3795,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132617568</v>
+        <v>132623295</v>
       </c>
       <c r="B30" t="n">
-        <v>97995</v>
+        <v>101338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3834,37 +3813,45 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672748</v>
+        <v>672594</v>
       </c>
       <c r="R30" t="n">
-        <v>6981368</v>
+        <v>6981486</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3893,7 +3880,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3903,7 +3890,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3912,28 +3899,29 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132623266</v>
+        <v>132623272</v>
       </c>
       <c r="B31" t="n">
-        <v>97989</v>
+        <v>101338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3941,33 +3929,45 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221944</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>672878</v>
+        <v>672787</v>
       </c>
       <c r="R31" t="n">
-        <v>6981334</v>
+        <v>6981316</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4141,53 +4141,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132617582</v>
+        <v>132617586</v>
       </c>
       <c r="B33" t="n">
-        <v>57955</v>
+        <v>91881</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>672612</v>
+        <v>672660</v>
       </c>
       <c r="R33" t="n">
-        <v>6981238</v>
+        <v>6981395</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -4219,7 +4211,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4229,7 +4221,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4256,45 +4248,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132617586</v>
+        <v>132617582</v>
       </c>
       <c r="B34" t="n">
-        <v>91881</v>
+        <v>57955</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>672660</v>
+        <v>672612</v>
       </c>
       <c r="R34" t="n">
-        <v>6981395</v>
+        <v>6981238</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4693,56 +4693,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132623285</v>
+        <v>132617564</v>
       </c>
       <c r="B38" t="n">
-        <v>101338</v>
+        <v>80438</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672638</v>
+        <v>672831</v>
       </c>
       <c r="R38" t="n">
-        <v>6981364</v>
+        <v>6981363</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4771,7 +4763,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4781,7 +4773,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4790,29 +4782,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132623290</v>
+        <v>132623285</v>
       </c>
       <c r="B39" t="n">
-        <v>97995</v>
+        <v>101338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4820,37 +4811,45 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>672621</v>
+        <v>672638</v>
       </c>
       <c r="R39" t="n">
-        <v>6981383</v>
+        <v>6981364</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4879,7 +4878,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4889,7 +4888,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4898,6 +4897,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4916,32 +4916,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132617564</v>
+        <v>132623290</v>
       </c>
       <c r="B40" t="n">
-        <v>80438</v>
+        <v>97995</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4951,13 +4951,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672831</v>
+        <v>672621</v>
       </c>
       <c r="R40" t="n">
-        <v>6981363</v>
+        <v>6981383</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5011,12 +5011,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5149,51 +5149,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132617607</v>
+        <v>132617558</v>
       </c>
       <c r="B42" t="n">
-        <v>79333</v>
+        <v>80311</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>672712</v>
+        <v>672873</v>
       </c>
       <c r="R42" t="n">
-        <v>6981164</v>
+        <v>6981339</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5222,7 +5219,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5232,7 +5229,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5241,24 +5238,8 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5382,48 +5363,56 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132617558</v>
+        <v>132623256</v>
       </c>
       <c r="B44" t="n">
-        <v>80311</v>
+        <v>101338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>392</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672873</v>
+        <v>672930</v>
       </c>
       <c r="R44" t="n">
-        <v>6981339</v>
+        <v>6981133</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5452,7 +5441,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5462,7 +5451,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5471,60 +5460,56 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132623256</v>
+        <v>132617607</v>
       </c>
       <c r="B45" t="n">
-        <v>101338</v>
+        <v>79333</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5532,13 +5517,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672930</v>
+        <v>672712</v>
       </c>
       <c r="R45" t="n">
-        <v>6981133</v>
+        <v>6981164</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5567,7 +5552,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5577,7 +5562,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5590,25 +5575,40 @@
       <c r="AG45" t="b">
         <v>0</v>
       </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132617567</v>
+        <v>132617576</v>
       </c>
       <c r="B46" t="n">
-        <v>80438</v>
+        <v>57958</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5616,26 +5616,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5643,13 +5648,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>672776</v>
+        <v>672684</v>
       </c>
       <c r="R46" t="n">
-        <v>6981332</v>
+        <v>6981289</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5678,7 +5683,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5688,7 +5693,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5697,24 +5707,8 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5731,42 +5725,42 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132617576</v>
+        <v>132623254</v>
       </c>
       <c r="B47" t="n">
-        <v>57958</v>
+        <v>101338</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5774,13 +5768,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>672684</v>
+        <v>672976</v>
       </c>
       <c r="R47" t="n">
-        <v>6981289</v>
+        <v>6981122</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5809,7 +5803,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5819,12 +5813,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5833,25 +5822,26 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132623254</v>
+        <v>132623294</v>
       </c>
       <c r="B48" t="n">
         <v>101338</v>
@@ -5894,10 +5884,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>672976</v>
+        <v>672601</v>
       </c>
       <c r="R48" t="n">
-        <v>6981122</v>
+        <v>6981439</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5929,7 +5919,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5939,7 +5929,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5967,7 +5957,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132623294</v>
+        <v>132623300</v>
       </c>
       <c r="B49" t="n">
         <v>101338</v>
@@ -6010,13 +6000,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672601</v>
+        <v>672758</v>
       </c>
       <c r="R49" t="n">
-        <v>6981439</v>
+        <v>6981513</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6045,7 +6035,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6055,7 +6045,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6083,7 +6073,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132623300</v>
+        <v>132617546</v>
       </c>
       <c r="B50" t="n">
         <v>101338</v>
@@ -6112,27 +6102,19 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>672758</v>
+        <v>672949</v>
       </c>
       <c r="R50" t="n">
-        <v>6981513</v>
+        <v>6981130</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6161,7 +6143,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6171,7 +6153,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6180,67 +6162,69 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132617546</v>
+        <v>132617567</v>
       </c>
       <c r="B51" t="n">
-        <v>101338</v>
+        <v>80438</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672949</v>
+        <v>672776</v>
       </c>
       <c r="R51" t="n">
-        <v>6981130</v>
+        <v>6981332</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6269,7 +6253,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6279,7 +6263,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6288,8 +6272,24 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6306,45 +6306,41 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132617589</v>
+        <v>132623292</v>
       </c>
       <c r="B52" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
@@ -6353,13 +6349,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672627</v>
+        <v>672655</v>
       </c>
       <c r="R52" t="n">
-        <v>6981425</v>
+        <v>6981418</v>
       </c>
       <c r="S52" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6388,7 +6384,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6398,7 +6394,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6414,22 +6410,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132623292</v>
+        <v>132617566</v>
       </c>
       <c r="B53" t="n">
-        <v>101338</v>
+        <v>80398</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6437,31 +6433,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6469,13 +6460,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>672655</v>
+        <v>672774</v>
       </c>
       <c r="R53" t="n">
-        <v>6981418</v>
+        <v>6981334</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6504,7 +6495,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6514,7 +6505,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6527,52 +6518,76 @@
       <c r="AG53" t="b">
         <v>0</v>
       </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132617566</v>
+        <v>132617589</v>
       </c>
       <c r="B54" t="n">
-        <v>80398</v>
+        <v>99130</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6580,10 +6595,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672774</v>
+        <v>672627</v>
       </c>
       <c r="R54" t="n">
-        <v>6981334</v>
+        <v>6981425</v>
       </c>
       <c r="S54" t="n">
         <v>2</v>
@@ -6615,7 +6630,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6625,7 +6640,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6637,21 +6652,6 @@
       <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7026,10 +7026,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132617602</v>
+        <v>132623280</v>
       </c>
       <c r="B58" t="n">
-        <v>97995</v>
+        <v>101338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7037,37 +7037,45 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>672593</v>
+        <v>672636</v>
       </c>
       <c r="R58" t="n">
-        <v>6981519</v>
+        <v>6981290</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7096,7 +7104,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7106,7 +7114,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7115,78 +7123,67 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132623303</v>
+        <v>132617606</v>
       </c>
       <c r="B59" t="n">
-        <v>56522</v>
+        <v>101338</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>206004</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>672560</v>
+        <v>672733</v>
       </c>
       <c r="R59" t="n">
-        <v>6981577</v>
+        <v>6981160</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7215,7 +7212,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7225,7 +7222,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7240,65 +7237,69 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132623280</v>
+        <v>132623303</v>
       </c>
       <c r="B60" t="n">
-        <v>101338</v>
+        <v>56522</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>206004</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672636</v>
+        <v>672560</v>
       </c>
       <c r="R60" t="n">
-        <v>6981290</v>
+        <v>6981577</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7330,7 +7331,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7340,7 +7341,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7349,7 +7350,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7368,10 +7368,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132617606</v>
+        <v>132617602</v>
       </c>
       <c r="B61" t="n">
-        <v>101338</v>
+        <v>97995</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7379,21 +7379,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7403,10 +7403,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672733</v>
+        <v>672593</v>
       </c>
       <c r="R61" t="n">
-        <v>6981160</v>
+        <v>6981519</v>
       </c>
       <c r="S61" t="n">
         <v>3</v>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7475,10 +7475,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132617555</v>
+        <v>132623271</v>
       </c>
       <c r="B62" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7486,37 +7486,40 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>672921</v>
+        <v>672780</v>
       </c>
       <c r="R62" t="n">
-        <v>6981328</v>
+        <v>6981331</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7545,7 +7548,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7555,7 +7558,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7564,28 +7567,44 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132623271</v>
+        <v>132617555</v>
       </c>
       <c r="B63" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7593,40 +7612,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672780</v>
+        <v>672921</v>
       </c>
       <c r="R63" t="n">
-        <v>6981331</v>
+        <v>6981328</v>
       </c>
       <c r="S63" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7655,7 +7671,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7665,7 +7681,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7674,34 +7690,18 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7834,10 +7834,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132617553</v>
+        <v>132617574</v>
       </c>
       <c r="B65" t="n">
-        <v>101338</v>
+        <v>91881</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7845,21 +7845,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7869,10 +7869,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>672931</v>
+        <v>672695</v>
       </c>
       <c r="R65" t="n">
-        <v>6981286</v>
+        <v>6981312</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7941,48 +7941,55 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132617560</v>
+        <v>132617591</v>
       </c>
       <c r="B66" t="n">
-        <v>97995</v>
+        <v>80438</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>672883</v>
+        <v>672709</v>
       </c>
       <c r="R66" t="n">
-        <v>6981346</v>
+        <v>6981489</v>
       </c>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8011,7 +8018,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8021,7 +8028,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Växandes på fyra närliggande aspträd</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8030,8 +8042,24 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8048,10 +8076,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132617574</v>
+        <v>132617560</v>
       </c>
       <c r="B67" t="n">
-        <v>91881</v>
+        <v>97995</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8059,21 +8087,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8083,13 +8111,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>672695</v>
+        <v>672883</v>
       </c>
       <c r="R67" t="n">
-        <v>6981312</v>
+        <v>6981346</v>
       </c>
       <c r="S67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8118,7 +8146,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8128,7 +8156,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8155,52 +8183,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132617591</v>
+        <v>132617553</v>
       </c>
       <c r="B68" t="n">
-        <v>80438</v>
+        <v>101338</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>672709</v>
+        <v>672931</v>
       </c>
       <c r="R68" t="n">
-        <v>6981489</v>
+        <v>6981286</v>
       </c>
       <c r="S68" t="n">
         <v>3</v>
@@ -8232,7 +8253,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8242,12 +8263,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Växandes på fyra närliggande aspträd</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8256,24 +8272,8 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8290,32 +8290,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132617556</v>
+        <v>132617584</v>
       </c>
       <c r="B69" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>672881</v>
+        <v>672639</v>
       </c>
       <c r="R69" t="n">
-        <v>6981314</v>
+        <v>6981355</v>
       </c>
       <c r="S69" t="n">
         <v>3</v>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8370,12 +8370,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:25</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På stående död gran</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8402,10 +8397,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132617561</v>
+        <v>132623267</v>
       </c>
       <c r="B70" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8413,37 +8408,40 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>672878</v>
+        <v>672869</v>
       </c>
       <c r="R70" t="n">
-        <v>6981375</v>
+        <v>6981357</v>
       </c>
       <c r="S70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8472,7 +8470,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8482,7 +8480,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8491,66 +8489,85 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132617584</v>
+        <v>132623263</v>
       </c>
       <c r="B71" t="n">
-        <v>91881</v>
+        <v>79333</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672639</v>
+        <v>672878</v>
       </c>
       <c r="R71" t="n">
-        <v>6981355</v>
+        <v>6981321</v>
       </c>
       <c r="S71" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8579,7 +8596,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8589,7 +8606,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8598,74 +8615,82 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132623305</v>
+        <v>132617598</v>
       </c>
       <c r="B72" t="n">
-        <v>101338</v>
+        <v>92338</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>6040186</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>672911</v>
+        <v>672763</v>
       </c>
       <c r="R72" t="n">
-        <v>6981136</v>
+        <v>6981545</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8694,7 +8719,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8704,7 +8729,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8717,22 +8742,37 @@
       <c r="AG72" t="b">
         <v>0</v>
       </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132623253</v>
+        <v>132623305</v>
       </c>
       <c r="B73" t="n">
         <v>101338</v>
@@ -8775,10 +8815,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>672918</v>
+        <v>672911</v>
       </c>
       <c r="R73" t="n">
-        <v>6980944</v>
+        <v>6981136</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8810,7 +8850,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8820,7 +8860,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8848,37 +8888,42 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132623267</v>
+        <v>132623253</v>
       </c>
       <c r="B74" t="n">
-        <v>79333</v>
+        <v>101338</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8886,10 +8931,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>672869</v>
+        <v>672918</v>
       </c>
       <c r="R74" t="n">
-        <v>6981357</v>
+        <v>6980944</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8921,7 +8966,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8931,7 +8976,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8943,21 +8988,6 @@
       <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8974,10 +9004,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132623263</v>
+        <v>132617556</v>
       </c>
       <c r="B75" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8985,40 +9015,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672878</v>
+        <v>672881</v>
       </c>
       <c r="R75" t="n">
-        <v>6981321</v>
+        <v>6981314</v>
       </c>
       <c r="S75" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9047,7 +9074,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9057,7 +9084,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På stående död gran</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9066,44 +9098,28 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132617598</v>
+        <v>132617561</v>
       </c>
       <c r="B76" t="n">
-        <v>92338</v>
+        <v>91918</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9111,21 +9127,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6040186</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9135,13 +9151,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>672763</v>
+        <v>672878</v>
       </c>
       <c r="R76" t="n">
-        <v>6981545</v>
+        <v>6981375</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9170,7 +9186,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9180,7 +9196,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9189,24 +9205,8 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9223,10 +9223,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132617575</v>
+        <v>132623275</v>
       </c>
       <c r="B77" t="n">
-        <v>57950</v>
+        <v>101338</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9234,31 +9234,31 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100110</v>
+        <v>222498</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9266,13 +9266,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>672681</v>
+        <v>672670</v>
       </c>
       <c r="R77" t="n">
-        <v>6981300</v>
+        <v>6981289</v>
       </c>
       <c r="S77" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9311,12 +9311,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Sång i över en minut.</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9325,28 +9320,29 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132623284</v>
+        <v>132623257</v>
       </c>
       <c r="B78" t="n">
-        <v>97995</v>
+        <v>101338</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9354,37 +9350,45 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>672622</v>
+        <v>672951</v>
       </c>
       <c r="R78" t="n">
-        <v>6981351</v>
+        <v>6981191</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9413,7 +9417,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9423,7 +9427,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9432,6 +9436,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -9450,10 +9455,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132617585</v>
+        <v>132617575</v>
       </c>
       <c r="B79" t="n">
-        <v>80398</v>
+        <v>57950</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9461,26 +9466,31 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229497</v>
+        <v>100110</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -9488,10 +9498,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>672635</v>
+        <v>672681</v>
       </c>
       <c r="R79" t="n">
-        <v>6981376</v>
+        <v>6981300</v>
       </c>
       <c r="S79" t="n">
         <v>3</v>
@@ -9523,7 +9533,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9533,7 +9543,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Sång i över en minut.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9542,24 +9557,8 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9576,42 +9575,37 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132617552</v>
+        <v>132617585</v>
       </c>
       <c r="B80" t="n">
-        <v>57955</v>
+        <v>80398</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -9619,13 +9613,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>672968</v>
+        <v>672635</v>
       </c>
       <c r="R80" t="n">
-        <v>6981202</v>
+        <v>6981376</v>
       </c>
       <c r="S80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9654,7 +9648,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9664,7 +9658,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9673,8 +9667,24 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9691,51 +9701,48 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132617559</v>
+        <v>132623284</v>
       </c>
       <c r="B81" t="n">
-        <v>80438</v>
+        <v>97995</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>672887</v>
+        <v>672622</v>
       </c>
       <c r="R81" t="n">
-        <v>6981335</v>
+        <v>6981351</v>
       </c>
       <c r="S81" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9764,7 +9771,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9774,7 +9781,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9783,76 +9790,55 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132623275</v>
+        <v>132617559</v>
       </c>
       <c r="B82" t="n">
-        <v>101338</v>
+        <v>80438</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9860,13 +9846,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>672670</v>
+        <v>672887</v>
       </c>
       <c r="R82" t="n">
-        <v>6981289</v>
+        <v>6981335</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9895,7 +9881,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9905,7 +9891,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9918,57 +9904,72 @@
       <c r="AG82" t="b">
         <v>0</v>
       </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132623257</v>
+        <v>132617552</v>
       </c>
       <c r="B83" t="n">
-        <v>101338</v>
+        <v>57955</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9976,13 +9977,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>672951</v>
+        <v>672968</v>
       </c>
       <c r="R83" t="n">
-        <v>6981191</v>
+        <v>6981202</v>
       </c>
       <c r="S83" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10011,7 +10012,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10021,7 +10022,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10030,19 +10031,18 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -10175,42 +10175,37 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132623255</v>
+        <v>132617594</v>
       </c>
       <c r="B85" t="n">
-        <v>101338</v>
+        <v>91918</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -10218,13 +10213,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>672955</v>
+        <v>672755</v>
       </c>
       <c r="R85" t="n">
-        <v>6981134</v>
+        <v>6981496</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10253,7 +10248,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10263,7 +10258,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10279,49 +10274,54 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132617594</v>
+        <v>132623255</v>
       </c>
       <c r="B86" t="n">
-        <v>91918</v>
+        <v>101338</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -10329,13 +10329,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>672755</v>
+        <v>672955</v>
       </c>
       <c r="R86" t="n">
-        <v>6981496</v>
+        <v>6981134</v>
       </c>
       <c r="S86" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10390,12 +10390,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -10518,56 +10518,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132623291</v>
+        <v>132617577</v>
       </c>
       <c r="B88" t="n">
-        <v>101338</v>
+        <v>91918</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>672630</v>
+        <v>672687</v>
       </c>
       <c r="R88" t="n">
-        <v>6981380</v>
+        <v>6981287</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10596,7 +10588,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10606,7 +10598,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10615,51 +10612,50 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132617583</v>
+        <v>132617562</v>
       </c>
       <c r="B89" t="n">
-        <v>79333</v>
+        <v>91881</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10669,10 +10665,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>672577</v>
+        <v>672869</v>
       </c>
       <c r="R89" t="n">
-        <v>6981292</v>
+        <v>6981366</v>
       </c>
       <c r="S89" t="n">
         <v>3</v>
@@ -10704,7 +10700,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10714,7 +10710,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10741,7 +10737,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132623270</v>
+        <v>132617583</v>
       </c>
       <c r="B90" t="n">
         <v>79333</v>
@@ -10770,22 +10766,19 @@
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>672831</v>
+        <v>672577</v>
       </c>
       <c r="R90" t="n">
-        <v>6981355</v>
+        <v>6981292</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10814,7 +10807,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10824,7 +10817,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10833,44 +10826,28 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132617577</v>
+        <v>132623270</v>
       </c>
       <c r="B91" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10878,37 +10855,40 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>672687</v>
+        <v>672831</v>
       </c>
       <c r="R91" t="n">
-        <v>6981287</v>
+        <v>6981355</v>
       </c>
       <c r="S91" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10937,7 +10917,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10947,12 +10927,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>På död stående gran</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10961,18 +10936,34 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -11110,10 +11101,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132617562</v>
+        <v>132623291</v>
       </c>
       <c r="B93" t="n">
-        <v>91881</v>
+        <v>101338</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11121,37 +11112,45 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>672869</v>
+        <v>672630</v>
       </c>
       <c r="R93" t="n">
-        <v>6981366</v>
+        <v>6981380</v>
       </c>
       <c r="S93" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11180,7 +11179,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11190,7 +11189,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11199,18 +11198,19 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -11333,10 +11333,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132617563</v>
+        <v>132623258</v>
       </c>
       <c r="B95" t="n">
-        <v>97995</v>
+        <v>101338</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11344,37 +11344,45 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>672858</v>
+        <v>672971</v>
       </c>
       <c r="R95" t="n">
-        <v>6981365</v>
+        <v>6981202</v>
       </c>
       <c r="S95" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11403,7 +11411,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11413,7 +11421,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11422,28 +11430,29 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132617570</v>
+        <v>132623273</v>
       </c>
       <c r="B96" t="n">
-        <v>97995</v>
+        <v>101338</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11451,37 +11460,45 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>672723</v>
+        <v>672774</v>
       </c>
       <c r="R96" t="n">
-        <v>6981408</v>
+        <v>6981240</v>
       </c>
       <c r="S96" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11510,7 +11527,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11520,7 +11537,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11529,25 +11546,26 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132623299</v>
+        <v>132617563</v>
       </c>
       <c r="B97" t="n">
         <v>97995</v>
@@ -11582,13 +11600,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>672709</v>
+        <v>672858</v>
       </c>
       <c r="R97" t="n">
-        <v>6981494</v>
+        <v>6981365</v>
       </c>
       <c r="S97" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11617,7 +11635,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11627,7 +11645,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11642,22 +11660,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132623258</v>
+        <v>132617570</v>
       </c>
       <c r="B98" t="n">
-        <v>101338</v>
+        <v>97995</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11665,45 +11683,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>672971</v>
+        <v>672723</v>
       </c>
       <c r="R98" t="n">
-        <v>6981202</v>
+        <v>6981408</v>
       </c>
       <c r="S98" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11732,7 +11742,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11742,7 +11752,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11751,29 +11761,28 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132623273</v>
+        <v>132623299</v>
       </c>
       <c r="B99" t="n">
-        <v>101338</v>
+        <v>97995</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11781,45 +11790,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>672774</v>
+        <v>672709</v>
       </c>
       <c r="R99" t="n">
-        <v>6981240</v>
+        <v>6981494</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11848,7 +11849,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11858,7 +11859,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11867,7 +11868,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13423-2026 artfynd.xlsx
+++ b/artfynd/A 13423-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132617578</v>
+        <v>132617597</v>
       </c>
       <c r="B2" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672651</v>
+        <v>672762</v>
       </c>
       <c r="R2" t="n">
-        <v>6981280</v>
+        <v>6981535</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132617597</v>
+        <v>132617578</v>
       </c>
       <c r="B3" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672762</v>
+        <v>672651</v>
       </c>
       <c r="R3" t="n">
-        <v>6981535</v>
+        <v>6981280</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1228,32 +1228,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132623279</v>
+        <v>132617551</v>
       </c>
       <c r="B7" t="n">
-        <v>97995</v>
+        <v>91918</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>672637</v>
+        <v>672976</v>
       </c>
       <c r="R7" t="n">
-        <v>6981289</v>
+        <v>6981217</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1323,22 +1323,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132617551</v>
+        <v>132617572</v>
       </c>
       <c r="B8" t="n">
-        <v>91918</v>
+        <v>57955</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1346,34 +1346,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>672976</v>
+        <v>672701</v>
       </c>
       <c r="R8" t="n">
-        <v>6981217</v>
+        <v>6981350</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1405,7 +1413,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1415,7 +1423,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,56 +1450,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132617572</v>
+        <v>132623279</v>
       </c>
       <c r="B9" t="n">
-        <v>57955</v>
+        <v>97995</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>672701</v>
+        <v>672637</v>
       </c>
       <c r="R9" t="n">
-        <v>6981350</v>
+        <v>6981289</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,22 +1545,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132617550</v>
+        <v>132617554</v>
       </c>
       <c r="B10" t="n">
-        <v>57955</v>
+        <v>91918</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,42 +1568,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672983</v>
+        <v>672912</v>
       </c>
       <c r="R10" t="n">
-        <v>6981247</v>
+        <v>6981315</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1635,7 +1627,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1645,7 +1637,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132617554</v>
+        <v>132617605</v>
       </c>
       <c r="B11" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1683,34 +1675,50 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672912</v>
+        <v>672801</v>
       </c>
       <c r="R11" t="n">
-        <v>6981315</v>
+        <v>6981249</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1742,7 +1750,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1752,7 +1760,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Två födosökande individer varav en hona</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1779,48 +1792,56 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132617579</v>
+        <v>132617571</v>
       </c>
       <c r="B12" t="n">
-        <v>91881</v>
+        <v>57958</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672651</v>
+        <v>672713</v>
       </c>
       <c r="R12" t="n">
-        <v>6981280</v>
+        <v>6981357</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1849,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1859,7 +1880,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1886,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132617605</v>
+        <v>132617550</v>
       </c>
       <c r="B13" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,16 +1923,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1914,33 +1940,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672801</v>
+        <v>672983</v>
       </c>
       <c r="R13" t="n">
-        <v>6981249</v>
+        <v>6981247</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -1972,7 +1990,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,12 +2000,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Två födosökande individer varav en hona</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,56 +2027,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132617571</v>
+        <v>132623301</v>
       </c>
       <c r="B14" t="n">
-        <v>57958</v>
+        <v>97995</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672713</v>
+        <v>672767</v>
       </c>
       <c r="R14" t="n">
-        <v>6981357</v>
+        <v>6981492</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2092,7 +2097,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2102,12 +2107,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2122,12 +2122,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132623301</v>
+        <v>132617579</v>
       </c>
       <c r="B16" t="n">
-        <v>97995</v>
+        <v>91881</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,21 +2261,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2285,13 +2285,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672767</v>
+        <v>672651</v>
       </c>
       <c r="R16" t="n">
-        <v>6981492</v>
+        <v>6981280</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2345,12 +2345,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2571,10 +2571,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132617593</v>
+        <v>132617601</v>
       </c>
       <c r="B19" t="n">
-        <v>91881</v>
+        <v>80398</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,37 +2582,40 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>229497</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672724</v>
+        <v>672548</v>
       </c>
       <c r="R19" t="n">
-        <v>6981448</v>
+        <v>6981599</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2641,7 +2644,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2651,7 +2654,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2660,8 +2663,24 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2678,7 +2697,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132617588</v>
+        <v>132617593</v>
       </c>
       <c r="B20" t="n">
         <v>91881</v>
@@ -2713,10 +2732,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>672671</v>
+        <v>672724</v>
       </c>
       <c r="R20" t="n">
-        <v>6981418</v>
+        <v>6981448</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2748,7 +2767,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2758,7 +2777,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2785,7 +2804,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132617548</v>
+        <v>132617588</v>
       </c>
       <c r="B21" t="n">
         <v>91881</v>
@@ -2820,13 +2839,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>672935</v>
+        <v>672671</v>
       </c>
       <c r="R21" t="n">
-        <v>6981231</v>
+        <v>6981418</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2855,7 +2874,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2865,7 +2884,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2892,10 +2911,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132623302</v>
+        <v>132617548</v>
       </c>
       <c r="B22" t="n">
-        <v>101338</v>
+        <v>91881</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2903,45 +2922,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>672746</v>
+        <v>672935</v>
       </c>
       <c r="R22" t="n">
-        <v>6981560</v>
+        <v>6981231</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2970,7 +2981,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2980,7 +2991,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2989,26 +3000,25 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132617600</v>
+        <v>132623302</v>
       </c>
       <c r="B23" t="n">
         <v>101338</v>
@@ -3037,19 +3047,27 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672651</v>
+        <v>672746</v>
       </c>
       <c r="R23" t="n">
-        <v>6981546</v>
+        <v>6981560</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3078,7 +3096,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3088,7 +3106,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3097,25 +3115,26 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132623268</v>
+        <v>132617600</v>
       </c>
       <c r="B24" t="n">
         <v>101338</v>
@@ -3144,27 +3163,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>672837</v>
+        <v>672651</v>
       </c>
       <c r="R24" t="n">
-        <v>6981360</v>
+        <v>6981546</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3193,7 +3204,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3203,7 +3214,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3212,29 +3223,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132617601</v>
+        <v>132623268</v>
       </c>
       <c r="B25" t="n">
-        <v>80398</v>
+        <v>101338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3242,26 +3252,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3269,13 +3284,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>672548</v>
+        <v>672837</v>
       </c>
       <c r="R25" t="n">
-        <v>6981599</v>
+        <v>6981360</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3304,7 +3319,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3314,7 +3329,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3327,62 +3342,47 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132617580</v>
+        <v>132617568</v>
       </c>
       <c r="B26" t="n">
-        <v>91918</v>
+        <v>97995</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>672623</v>
+        <v>672748</v>
       </c>
       <c r="R26" t="n">
-        <v>6981252</v>
+        <v>6981368</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3427,7 +3427,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3464,68 +3464,44 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132617604</v>
+        <v>132623266</v>
       </c>
       <c r="B27" t="n">
-        <v>57958</v>
+        <v>97989</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>221944</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>672698</v>
+        <v>672878</v>
       </c>
       <c r="R27" t="n">
-        <v>6981511</v>
+        <v>6981334</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3554,7 +3530,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3564,7 +3540,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3573,50 +3549,51 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132617568</v>
+        <v>132617580</v>
       </c>
       <c r="B28" t="n">
-        <v>97995</v>
+        <v>91918</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3626,10 +3603,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>672748</v>
+        <v>672623</v>
       </c>
       <c r="R28" t="n">
-        <v>6981368</v>
+        <v>6981252</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3661,7 +3638,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3671,7 +3648,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3698,44 +3675,68 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132623266</v>
+        <v>132617604</v>
       </c>
       <c r="B29" t="n">
-        <v>97989</v>
+        <v>57958</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221944</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672878</v>
+        <v>672698</v>
       </c>
       <c r="R29" t="n">
-        <v>6981334</v>
+        <v>6981511</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3764,7 +3765,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3774,7 +3775,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3783,19 +3784,18 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4141,10 +4141,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132617586</v>
+        <v>132617596</v>
       </c>
       <c r="B33" t="n">
-        <v>91881</v>
+        <v>97995</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4152,21 +4152,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4176,10 +4176,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>672660</v>
+        <v>672810</v>
       </c>
       <c r="R33" t="n">
-        <v>6981395</v>
+        <v>6981546</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4248,42 +4248,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132617582</v>
+        <v>132623274</v>
       </c>
       <c r="B34" t="n">
-        <v>57955</v>
+        <v>101338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4291,13 +4291,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>672612</v>
+        <v>672744</v>
       </c>
       <c r="R34" t="n">
-        <v>6981238</v>
+        <v>6981271</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4345,28 +4345,29 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132623274</v>
+        <v>132617586</v>
       </c>
       <c r="B35" t="n">
-        <v>101338</v>
+        <v>91881</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4374,45 +4375,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>672744</v>
+        <v>672660</v>
       </c>
       <c r="R35" t="n">
-        <v>6981271</v>
+        <v>6981395</v>
       </c>
       <c r="S35" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4441,7 +4434,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4451,7 +4444,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4460,64 +4453,71 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132617596</v>
+        <v>132617582</v>
       </c>
       <c r="B36" t="n">
-        <v>97995</v>
+        <v>57955</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>672810</v>
+        <v>672612</v>
       </c>
       <c r="R36" t="n">
-        <v>6981546</v>
+        <v>6981238</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4586,48 +4586,56 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132617599</v>
+        <v>132623285</v>
       </c>
       <c r="B37" t="n">
-        <v>79333</v>
+        <v>101338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>672664</v>
+        <v>672638</v>
       </c>
       <c r="R37" t="n">
-        <v>6981552</v>
+        <v>6981364</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4656,7 +4664,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4666,7 +4674,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4675,18 +4683,19 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4800,56 +4809,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132623285</v>
+        <v>132617599</v>
       </c>
       <c r="B39" t="n">
-        <v>101338</v>
+        <v>79333</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>672638</v>
+        <v>672664</v>
       </c>
       <c r="R39" t="n">
-        <v>6981364</v>
+        <v>6981552</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4878,7 +4879,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4888,7 +4889,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4897,19 +4898,18 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5149,48 +5149,51 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132617558</v>
+        <v>132617607</v>
       </c>
       <c r="B42" t="n">
-        <v>80311</v>
+        <v>79333</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>672873</v>
+        <v>672712</v>
       </c>
       <c r="R42" t="n">
-        <v>6981339</v>
+        <v>6981164</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5219,7 +5222,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5229,7 +5232,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5238,8 +5241,24 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5256,10 +5275,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132617592</v>
+        <v>132623256</v>
       </c>
       <c r="B43" t="n">
-        <v>80398</v>
+        <v>101338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5267,37 +5286,45 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672709</v>
+        <v>672930</v>
       </c>
       <c r="R43" t="n">
-        <v>6981488</v>
+        <v>6981133</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5326,7 +5353,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5336,7 +5363,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5345,74 +5372,67 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132623256</v>
+        <v>132617558</v>
       </c>
       <c r="B44" t="n">
-        <v>101338</v>
+        <v>80311</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>392</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672930</v>
+        <v>672873</v>
       </c>
       <c r="R44" t="n">
-        <v>6981133</v>
+        <v>6981339</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5441,7 +5461,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5451,7 +5471,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5460,67 +5480,63 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132617607</v>
+        <v>132617592</v>
       </c>
       <c r="B45" t="n">
-        <v>79333</v>
+        <v>80398</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672712</v>
+        <v>672709</v>
       </c>
       <c r="R45" t="n">
-        <v>6981164</v>
+        <v>6981488</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -5552,7 +5568,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5562,7 +5578,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5571,24 +5587,8 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5605,42 +5605,42 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132617576</v>
+        <v>132623254</v>
       </c>
       <c r="B46" t="n">
-        <v>57958</v>
+        <v>101338</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5648,13 +5648,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>672684</v>
+        <v>672976</v>
       </c>
       <c r="R46" t="n">
-        <v>6981289</v>
+        <v>6981122</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5693,12 +5693,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5707,25 +5702,26 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132623254</v>
+        <v>132623294</v>
       </c>
       <c r="B47" t="n">
         <v>101338</v>
@@ -5768,10 +5764,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>672976</v>
+        <v>672601</v>
       </c>
       <c r="R47" t="n">
-        <v>6981122</v>
+        <v>6981439</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5803,7 +5799,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5813,7 +5809,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5841,7 +5837,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132623294</v>
+        <v>132623300</v>
       </c>
       <c r="B48" t="n">
         <v>101338</v>
@@ -5884,13 +5880,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>672601</v>
+        <v>672758</v>
       </c>
       <c r="R48" t="n">
-        <v>6981439</v>
+        <v>6981513</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5919,7 +5915,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5929,7 +5925,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5957,7 +5953,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132623300</v>
+        <v>132617546</v>
       </c>
       <c r="B49" t="n">
         <v>101338</v>
@@ -5986,27 +5982,19 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672758</v>
+        <v>672949</v>
       </c>
       <c r="R49" t="n">
-        <v>6981513</v>
+        <v>6981130</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6035,7 +6023,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6045,7 +6033,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6054,67 +6042,69 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132617546</v>
+        <v>132617567</v>
       </c>
       <c r="B50" t="n">
-        <v>101338</v>
+        <v>80438</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>672949</v>
+        <v>672776</v>
       </c>
       <c r="R50" t="n">
-        <v>6981130</v>
+        <v>6981332</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6143,7 +6133,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6153,7 +6143,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6162,8 +6152,24 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6180,10 +6186,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132617567</v>
+        <v>132617576</v>
       </c>
       <c r="B51" t="n">
-        <v>80438</v>
+        <v>57958</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6191,26 +6197,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6218,13 +6229,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672776</v>
+        <v>672684</v>
       </c>
       <c r="R51" t="n">
-        <v>6981332</v>
+        <v>6981289</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6253,7 +6264,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6263,7 +6274,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6272,24 +6288,8 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6306,41 +6306,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132623292</v>
+        <v>132617589</v>
       </c>
       <c r="B52" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
@@ -6349,13 +6353,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672655</v>
+        <v>672627</v>
       </c>
       <c r="R52" t="n">
-        <v>6981418</v>
+        <v>6981425</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6384,7 +6388,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6394,7 +6398,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6410,22 +6414,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132617566</v>
+        <v>132623292</v>
       </c>
       <c r="B53" t="n">
-        <v>80398</v>
+        <v>101338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6433,26 +6437,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6460,13 +6469,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>672774</v>
+        <v>672655</v>
       </c>
       <c r="R53" t="n">
-        <v>6981334</v>
+        <v>6981418</v>
       </c>
       <c r="S53" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6495,7 +6504,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6505,7 +6514,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6518,76 +6527,52 @@
       <c r="AG53" t="b">
         <v>0</v>
       </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132617589</v>
+        <v>132617566</v>
       </c>
       <c r="B54" t="n">
-        <v>99130</v>
+        <v>80398</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6595,10 +6580,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672627</v>
+        <v>672774</v>
       </c>
       <c r="R54" t="n">
-        <v>6981425</v>
+        <v>6981334</v>
       </c>
       <c r="S54" t="n">
         <v>2</v>
@@ -6630,7 +6615,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6640,7 +6625,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6652,6 +6637,21 @@
       <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6910,56 +6910,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132623265</v>
+        <v>132617555</v>
       </c>
       <c r="B57" t="n">
-        <v>101338</v>
+        <v>79333</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>672872</v>
+        <v>672921</v>
       </c>
       <c r="R57" t="n">
-        <v>6981332</v>
+        <v>6981328</v>
       </c>
       <c r="S57" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6988,7 +6980,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6998,7 +6990,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7007,61 +6999,55 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132623280</v>
+        <v>132617549</v>
       </c>
       <c r="B58" t="n">
-        <v>101338</v>
+        <v>80438</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7069,13 +7055,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>672636</v>
+        <v>672932</v>
       </c>
       <c r="R58" t="n">
-        <v>6981290</v>
+        <v>6981224</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7104,7 +7090,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7114,7 +7100,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7127,63 +7113,81 @@
       <c r="AG58" t="b">
         <v>0</v>
       </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132617606</v>
+        <v>132623271</v>
       </c>
       <c r="B59" t="n">
-        <v>101338</v>
+        <v>80438</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>672733</v>
+        <v>672780</v>
       </c>
       <c r="R59" t="n">
-        <v>6981160</v>
+        <v>6981331</v>
       </c>
       <c r="S59" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7212,7 +7216,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7222,7 +7226,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7231,78 +7235,82 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132623303</v>
+        <v>132617602</v>
       </c>
       <c r="B60" t="n">
-        <v>56522</v>
+        <v>97995</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>206004</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672560</v>
+        <v>672593</v>
       </c>
       <c r="R60" t="n">
-        <v>6981577</v>
+        <v>6981519</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7331,7 +7339,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7341,7 +7349,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7356,60 +7364,72 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132617602</v>
+        <v>132623303</v>
       </c>
       <c r="B61" t="n">
-        <v>97995</v>
+        <v>56522</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>206004</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672593</v>
+        <v>672560</v>
       </c>
       <c r="R61" t="n">
-        <v>6981519</v>
+        <v>6981577</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7438,7 +7458,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7448,7 +7468,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7463,49 +7483,54 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132623271</v>
+        <v>132623265</v>
       </c>
       <c r="B62" t="n">
-        <v>80438</v>
+        <v>101338</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7513,13 +7538,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>672780</v>
+        <v>672872</v>
       </c>
       <c r="R62" t="n">
-        <v>6981331</v>
+        <v>6981332</v>
       </c>
       <c r="S62" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7548,7 +7573,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7558,7 +7583,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7571,21 +7596,6 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
@@ -7594,55 +7604,63 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132617555</v>
+        <v>132623280</v>
       </c>
       <c r="B63" t="n">
-        <v>79333</v>
+        <v>101338</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672921</v>
+        <v>672636</v>
       </c>
       <c r="R63" t="n">
-        <v>6981328</v>
+        <v>6981290</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7671,7 +7689,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7681,7 +7699,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7690,66 +7708,64 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132617549</v>
+        <v>132617606</v>
       </c>
       <c r="B64" t="n">
-        <v>80438</v>
+        <v>101338</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>672932</v>
+        <v>672733</v>
       </c>
       <c r="R64" t="n">
-        <v>6981224</v>
+        <v>6981160</v>
       </c>
       <c r="S64" t="n">
         <v>3</v>
@@ -7781,7 +7797,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7791,7 +7807,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7800,24 +7816,8 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8076,10 +8076,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132617560</v>
+        <v>132617553</v>
       </c>
       <c r="B67" t="n">
-        <v>97995</v>
+        <v>101338</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8087,21 +8087,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8111,13 +8111,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>672883</v>
+        <v>672931</v>
       </c>
       <c r="R67" t="n">
-        <v>6981346</v>
+        <v>6981286</v>
       </c>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8183,10 +8183,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132617553</v>
+        <v>132617560</v>
       </c>
       <c r="B68" t="n">
-        <v>101338</v>
+        <v>97995</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8194,21 +8194,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8218,13 +8218,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>672931</v>
+        <v>672883</v>
       </c>
       <c r="R68" t="n">
-        <v>6981286</v>
+        <v>6981346</v>
       </c>
       <c r="S68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8397,10 +8397,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132623267</v>
+        <v>132617556</v>
       </c>
       <c r="B70" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8408,40 +8408,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>672869</v>
+        <v>672881</v>
       </c>
       <c r="R70" t="n">
-        <v>6981357</v>
+        <v>6981314</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8470,7 +8467,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8480,7 +8477,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På stående död gran</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8489,44 +8491,28 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132623263</v>
+        <v>132617561</v>
       </c>
       <c r="B71" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8534,27 +8520,24 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
@@ -8564,10 +8547,10 @@
         <v>672878</v>
       </c>
       <c r="R71" t="n">
-        <v>6981321</v>
+        <v>6981375</v>
       </c>
       <c r="S71" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8596,7 +8579,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8606,7 +8589,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8615,44 +8598,28 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132617598</v>
+        <v>132623263</v>
       </c>
       <c r="B72" t="n">
-        <v>92338</v>
+        <v>79333</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8660,37 +8627,40 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>672763</v>
+        <v>672878</v>
       </c>
       <c r="R72" t="n">
-        <v>6981545</v>
+        <v>6981321</v>
       </c>
       <c r="S72" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8719,7 +8689,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8729,7 +8699,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8760,54 +8730,49 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132623305</v>
+        <v>132623267</v>
       </c>
       <c r="B73" t="n">
-        <v>101338</v>
+        <v>79333</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8815,10 +8780,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>672911</v>
+        <v>672869</v>
       </c>
       <c r="R73" t="n">
-        <v>6981136</v>
+        <v>6981357</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8850,7 +8815,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8860,7 +8825,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8872,6 +8837,21 @@
       <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8888,56 +8868,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132623253</v>
+        <v>132617598</v>
       </c>
       <c r="B74" t="n">
-        <v>101338</v>
+        <v>92338</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>6040186</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>672918</v>
+        <v>672763</v>
       </c>
       <c r="R74" t="n">
-        <v>6980944</v>
+        <v>6981545</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8966,7 +8938,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8976,7 +8948,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8989,63 +8961,86 @@
       <c r="AG74" t="b">
         <v>0</v>
       </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132617556</v>
+        <v>132623305</v>
       </c>
       <c r="B75" t="n">
-        <v>91918</v>
+        <v>101338</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672881</v>
+        <v>672911</v>
       </c>
       <c r="R75" t="n">
-        <v>6981314</v>
+        <v>6981136</v>
       </c>
       <c r="S75" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9074,7 +9069,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9084,12 +9079,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>09:25</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På stående död gran</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9098,66 +9088,75 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132617561</v>
+        <v>132623253</v>
       </c>
       <c r="B76" t="n">
-        <v>91918</v>
+        <v>101338</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>672878</v>
+        <v>672918</v>
       </c>
       <c r="R76" t="n">
-        <v>6981375</v>
+        <v>6980944</v>
       </c>
       <c r="S76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9186,7 +9185,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9196,7 +9195,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9205,28 +9204,29 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132623275</v>
+        <v>132617575</v>
       </c>
       <c r="B77" t="n">
-        <v>101338</v>
+        <v>57950</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9234,31 +9234,31 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>100110</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9266,13 +9266,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>672670</v>
+        <v>672681</v>
       </c>
       <c r="R77" t="n">
-        <v>6981289</v>
+        <v>6981300</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9311,7 +9311,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Sång i över en minut.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9320,61 +9325,55 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132623257</v>
+        <v>132617559</v>
       </c>
       <c r="B78" t="n">
-        <v>101338</v>
+        <v>80438</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -9382,13 +9381,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>672951</v>
+        <v>672887</v>
       </c>
       <c r="R78" t="n">
-        <v>6981191</v>
+        <v>6981335</v>
       </c>
       <c r="S78" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9417,7 +9416,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9427,7 +9426,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9440,47 +9439,62 @@
       <c r="AG78" t="b">
         <v>0</v>
       </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132617575</v>
+        <v>132617552</v>
       </c>
       <c r="B79" t="n">
-        <v>57950</v>
+        <v>57955</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100110</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9488,7 +9502,7 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -9498,13 +9512,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>672681</v>
+        <v>672968</v>
       </c>
       <c r="R79" t="n">
-        <v>6981300</v>
+        <v>6981202</v>
       </c>
       <c r="S79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9533,7 +9547,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9543,12 +9557,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Sång i över en minut.</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9575,10 +9584,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132617585</v>
+        <v>132623275</v>
       </c>
       <c r="B80" t="n">
-        <v>80398</v>
+        <v>101338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9586,26 +9595,31 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -9613,13 +9627,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>672635</v>
+        <v>672670</v>
       </c>
       <c r="R80" t="n">
-        <v>6981376</v>
+        <v>6981289</v>
       </c>
       <c r="S80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9648,7 +9662,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9658,7 +9672,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9671,40 +9685,25 @@
       <c r="AG80" t="b">
         <v>0</v>
       </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132623284</v>
+        <v>132623257</v>
       </c>
       <c r="B81" t="n">
-        <v>97995</v>
+        <v>101338</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9712,37 +9711,45 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>672622</v>
+        <v>672951</v>
       </c>
       <c r="R81" t="n">
-        <v>6981351</v>
+        <v>6981191</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9771,7 +9778,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9781,7 +9788,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9790,6 +9797,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9808,51 +9816,48 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132617559</v>
+        <v>132623284</v>
       </c>
       <c r="B82" t="n">
-        <v>80438</v>
+        <v>97995</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>672887</v>
+        <v>672622</v>
       </c>
       <c r="R82" t="n">
-        <v>6981335</v>
+        <v>6981351</v>
       </c>
       <c r="S82" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9881,7 +9886,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9891,7 +9896,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9900,76 +9905,55 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132617552</v>
+        <v>132617585</v>
       </c>
       <c r="B83" t="n">
-        <v>57955</v>
+        <v>80398</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9977,13 +9961,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>672968</v>
+        <v>672635</v>
       </c>
       <c r="R83" t="n">
-        <v>6981202</v>
+        <v>6981376</v>
       </c>
       <c r="S83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10012,7 +9996,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10022,7 +10006,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10031,8 +10015,24 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10049,32 +10049,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132617587</v>
+        <v>132617594</v>
       </c>
       <c r="B84" t="n">
-        <v>80398</v>
+        <v>91918</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10087,10 +10087,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>672655</v>
+        <v>672755</v>
       </c>
       <c r="R84" t="n">
-        <v>6981378</v>
+        <v>6981496</v>
       </c>
       <c r="S84" t="n">
         <v>3</v>
@@ -10122,7 +10122,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10132,7 +10132,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10144,21 +10144,6 @@
       <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10175,37 +10160,42 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132617594</v>
+        <v>132623255</v>
       </c>
       <c r="B85" t="n">
-        <v>91918</v>
+        <v>101338</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -10213,13 +10203,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>672755</v>
+        <v>672955</v>
       </c>
       <c r="R85" t="n">
-        <v>6981496</v>
+        <v>6981134</v>
       </c>
       <c r="S85" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10248,7 +10238,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10258,7 +10248,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10274,22 +10264,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132623255</v>
+        <v>132617587</v>
       </c>
       <c r="B86" t="n">
-        <v>101338</v>
+        <v>80398</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10297,31 +10287,26 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>222498</v>
+        <v>229497</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -10329,13 +10314,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>672955</v>
+        <v>672655</v>
       </c>
       <c r="R86" t="n">
-        <v>6981134</v>
+        <v>6981378</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10364,7 +10349,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10374,7 +10359,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10387,15 +10372,30 @@
       <c r="AG86" t="b">
         <v>0</v>
       </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -10630,48 +10630,51 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132617562</v>
+        <v>132623270</v>
       </c>
       <c r="B89" t="n">
-        <v>91881</v>
+        <v>79333</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>672869</v>
+        <v>672831</v>
       </c>
       <c r="R89" t="n">
-        <v>6981366</v>
+        <v>6981355</v>
       </c>
       <c r="S89" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10700,7 +10703,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10710,7 +10713,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10719,18 +10722,34 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -10844,37 +10863,42 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132623270</v>
+        <v>132623291</v>
       </c>
       <c r="B91" t="n">
-        <v>79333</v>
+        <v>101338</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -10882,10 +10906,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>672831</v>
+        <v>672630</v>
       </c>
       <c r="R91" t="n">
-        <v>6981355</v>
+        <v>6981380</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10917,7 +10941,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10927,7 +10951,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10939,21 +10963,6 @@
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
@@ -10970,37 +10979,42 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132617565</v>
+        <v>132623304</v>
       </c>
       <c r="B92" t="n">
-        <v>80438</v>
+        <v>101338</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -11008,13 +11022,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>672833</v>
+        <v>672732</v>
       </c>
       <c r="R92" t="n">
-        <v>6981355</v>
+        <v>6981161</v>
       </c>
       <c r="S92" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11043,7 +11057,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11053,12 +11067,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:09</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Växandes på björk.</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11071,40 +11080,25 @@
       <c r="AG92" t="b">
         <v>0</v>
       </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132623291</v>
+        <v>132617562</v>
       </c>
       <c r="B93" t="n">
-        <v>101338</v>
+        <v>91881</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11112,45 +11106,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>672630</v>
+        <v>672869</v>
       </c>
       <c r="R93" t="n">
-        <v>6981380</v>
+        <v>6981366</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11179,7 +11165,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11189,7 +11175,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11198,61 +11184,55 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132623304</v>
+        <v>132617565</v>
       </c>
       <c r="B94" t="n">
-        <v>101338</v>
+        <v>80438</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11260,13 +11240,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>672732</v>
+        <v>672833</v>
       </c>
       <c r="R94" t="n">
-        <v>6981161</v>
+        <v>6981355</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11295,7 +11275,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11305,7 +11285,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Växandes på björk.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11318,15 +11303,30 @@
       <c r="AG94" t="b">
         <v>0</v>
       </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -11565,7 +11565,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132617563</v>
+        <v>132617570</v>
       </c>
       <c r="B97" t="n">
         <v>97995</v>
@@ -11600,10 +11600,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>672858</v>
+        <v>672723</v>
       </c>
       <c r="R97" t="n">
-        <v>6981365</v>
+        <v>6981408</v>
       </c>
       <c r="S97" t="n">
         <v>3</v>
@@ -11635,7 +11635,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11645,7 +11645,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11672,7 +11672,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132617570</v>
+        <v>132623299</v>
       </c>
       <c r="B98" t="n">
         <v>97995</v>
@@ -11707,13 +11707,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>672723</v>
+        <v>672709</v>
       </c>
       <c r="R98" t="n">
-        <v>6981408</v>
+        <v>6981494</v>
       </c>
       <c r="S98" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11767,19 +11767,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132623299</v>
+        <v>132617563</v>
       </c>
       <c r="B99" t="n">
         <v>97995</v>
@@ -11814,13 +11814,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>672709</v>
+        <v>672858</v>
       </c>
       <c r="R99" t="n">
-        <v>6981494</v>
+        <v>6981365</v>
       </c>
       <c r="S99" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11874,12 +11874,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>

--- a/artfynd/A 13423-2026 artfynd.xlsx
+++ b/artfynd/A 13423-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132617597</v>
+        <v>132617547</v>
       </c>
       <c r="B2" t="n">
-        <v>91881</v>
+        <v>79333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672762</v>
+        <v>672932</v>
       </c>
       <c r="R2" t="n">
-        <v>6981535</v>
+        <v>6981174</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132617578</v>
+        <v>132617597</v>
       </c>
       <c r="B3" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672651</v>
+        <v>672762</v>
       </c>
       <c r="R3" t="n">
-        <v>6981280</v>
+        <v>6981535</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132617547</v>
+        <v>132617578</v>
       </c>
       <c r="B4" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672932</v>
+        <v>672651</v>
       </c>
       <c r="R4" t="n">
-        <v>6981174</v>
+        <v>6981280</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,42 +996,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132623293</v>
+        <v>132617572</v>
       </c>
       <c r="B5" t="n">
-        <v>101338</v>
+        <v>57955</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1039,13 +1039,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>672629</v>
+        <v>672701</v>
       </c>
       <c r="R5" t="n">
-        <v>6981435</v>
+        <v>6981350</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,75 +1093,66 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132623296</v>
+        <v>132617551</v>
       </c>
       <c r="B6" t="n">
-        <v>101338</v>
+        <v>91918</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>672649</v>
+        <v>672976</v>
       </c>
       <c r="R6" t="n">
-        <v>6981516</v>
+        <v>6981217</v>
       </c>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,7 +1181,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1200,7 +1191,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,51 +1200,50 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132617551</v>
+        <v>132623279</v>
       </c>
       <c r="B7" t="n">
-        <v>91918</v>
+        <v>97995</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1263,13 +1253,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>672976</v>
+        <v>672637</v>
       </c>
       <c r="R7" t="n">
-        <v>6981217</v>
+        <v>6981289</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1298,7 +1288,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1308,7 +1298,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1323,54 +1313,54 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132617572</v>
+        <v>132623296</v>
       </c>
       <c r="B8" t="n">
-        <v>57955</v>
+        <v>101338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1378,13 +1368,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>672701</v>
+        <v>672649</v>
       </c>
       <c r="R8" t="n">
-        <v>6981350</v>
+        <v>6981516</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,7 +1403,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1423,7 +1413,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,28 +1422,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132623279</v>
+        <v>132623293</v>
       </c>
       <c r="B9" t="n">
-        <v>97995</v>
+        <v>101338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,34 +1452,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>672637</v>
+        <v>672629</v>
       </c>
       <c r="R9" t="n">
-        <v>6981289</v>
+        <v>6981435</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1520,7 +1519,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1530,7 +1529,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,6 +1538,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1557,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132617554</v>
+        <v>132617550</v>
       </c>
       <c r="B10" t="n">
-        <v>91918</v>
+        <v>57955</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,34 +1568,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672912</v>
+        <v>672983</v>
       </c>
       <c r="R10" t="n">
-        <v>6981315</v>
+        <v>6981247</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1627,7 +1635,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1637,7 +1645,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1912,10 +1920,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132617550</v>
+        <v>132617554</v>
       </c>
       <c r="B13" t="n">
-        <v>57955</v>
+        <v>91918</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,42 +1931,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672983</v>
+        <v>672912</v>
       </c>
       <c r="R13" t="n">
-        <v>6981247</v>
+        <v>6981315</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2027,10 +2027,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132623301</v>
+        <v>132617579</v>
       </c>
       <c r="B14" t="n">
-        <v>97995</v>
+        <v>91881</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2038,21 +2038,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2062,13 +2062,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672767</v>
+        <v>672651</v>
       </c>
       <c r="R14" t="n">
-        <v>6981492</v>
+        <v>6981280</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2122,22 +2122,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132623282</v>
+        <v>132623301</v>
       </c>
       <c r="B15" t="n">
-        <v>101338</v>
+        <v>97995</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,42 +2145,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672633</v>
+        <v>672767</v>
       </c>
       <c r="R15" t="n">
-        <v>6981324</v>
+        <v>6981492</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2212,7 +2204,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2222,7 +2214,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,7 +2223,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2250,10 +2241,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132617579</v>
+        <v>132623282</v>
       </c>
       <c r="B16" t="n">
-        <v>91881</v>
+        <v>101338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,37 +2252,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672651</v>
+        <v>672633</v>
       </c>
       <c r="R16" t="n">
-        <v>6981280</v>
+        <v>6981324</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2320,7 +2319,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2330,7 +2329,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2339,50 +2338,51 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132617590</v>
+        <v>132617581</v>
       </c>
       <c r="B17" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672706</v>
+        <v>672612</v>
       </c>
       <c r="R17" t="n">
-        <v>6981525</v>
+        <v>6981244</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2464,32 +2464,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132617581</v>
+        <v>132617590</v>
       </c>
       <c r="B18" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672612</v>
+        <v>672706</v>
       </c>
       <c r="R18" t="n">
-        <v>6981244</v>
+        <v>6981525</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2571,10 +2571,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132617601</v>
+        <v>132623302</v>
       </c>
       <c r="B19" t="n">
-        <v>80398</v>
+        <v>101338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,26 +2582,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2609,13 +2614,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672548</v>
+        <v>672746</v>
       </c>
       <c r="R19" t="n">
-        <v>6981599</v>
+        <v>6981560</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2644,7 +2649,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2654,7 +2659,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2667,40 +2672,25 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132617593</v>
+        <v>132617600</v>
       </c>
       <c r="B20" t="n">
-        <v>91881</v>
+        <v>101338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,21 +2698,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2732,13 +2722,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>672724</v>
+        <v>672651</v>
       </c>
       <c r="R20" t="n">
-        <v>6981448</v>
+        <v>6981546</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2767,7 +2757,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2777,7 +2767,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2804,10 +2794,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132617588</v>
+        <v>132623268</v>
       </c>
       <c r="B21" t="n">
-        <v>91881</v>
+        <v>101338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2815,37 +2805,45 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>672671</v>
+        <v>672837</v>
       </c>
       <c r="R21" t="n">
-        <v>6981418</v>
+        <v>6981360</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2874,7 +2872,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2884,7 +2882,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2893,28 +2891,29 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132617548</v>
+        <v>132617601</v>
       </c>
       <c r="B22" t="n">
-        <v>91881</v>
+        <v>80398</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2922,34 +2921,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>672935</v>
+        <v>672548</v>
       </c>
       <c r="R22" t="n">
-        <v>6981231</v>
+        <v>6981599</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2981,7 +2983,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2991,7 +2993,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3000,8 +3002,24 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3018,10 +3036,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132623302</v>
+        <v>132617593</v>
       </c>
       <c r="B23" t="n">
-        <v>101338</v>
+        <v>91881</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3029,45 +3047,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672746</v>
+        <v>672724</v>
       </c>
       <c r="R23" t="n">
-        <v>6981560</v>
+        <v>6981448</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3096,7 +3106,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3106,7 +3116,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3115,29 +3125,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132617600</v>
+        <v>132617588</v>
       </c>
       <c r="B24" t="n">
-        <v>101338</v>
+        <v>91881</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3145,21 +3154,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3169,13 +3178,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>672651</v>
+        <v>672671</v>
       </c>
       <c r="R24" t="n">
-        <v>6981546</v>
+        <v>6981418</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3204,7 +3213,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3214,7 +3223,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3241,10 +3250,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132623268</v>
+        <v>132617548</v>
       </c>
       <c r="B25" t="n">
-        <v>101338</v>
+        <v>91881</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3252,45 +3261,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>672837</v>
+        <v>672935</v>
       </c>
       <c r="R25" t="n">
-        <v>6981360</v>
+        <v>6981231</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3319,7 +3320,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3329,7 +3330,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3338,51 +3339,50 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132617568</v>
+        <v>132617580</v>
       </c>
       <c r="B26" t="n">
-        <v>97995</v>
+        <v>91918</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>672748</v>
+        <v>672623</v>
       </c>
       <c r="R26" t="n">
-        <v>6981368</v>
+        <v>6981252</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3427,7 +3427,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3464,10 +3464,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132623266</v>
+        <v>132623295</v>
       </c>
       <c r="B27" t="n">
-        <v>97989</v>
+        <v>101338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3475,33 +3475,45 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221944</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>672878</v>
+        <v>672594</v>
       </c>
       <c r="R27" t="n">
-        <v>6981334</v>
+        <v>6981486</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3530,7 +3542,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3540,7 +3552,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3561,55 +3573,63 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132617580</v>
+        <v>132623272</v>
       </c>
       <c r="B28" t="n">
-        <v>91918</v>
+        <v>101338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>672623</v>
+        <v>672787</v>
       </c>
       <c r="R28" t="n">
-        <v>6981252</v>
+        <v>6981316</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3638,7 +3658,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3648,7 +3668,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3657,18 +3677,19 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3802,10 +3823,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132623295</v>
+        <v>132617568</v>
       </c>
       <c r="B30" t="n">
-        <v>101338</v>
+        <v>97995</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3813,45 +3834,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672594</v>
+        <v>672748</v>
       </c>
       <c r="R30" t="n">
-        <v>6981486</v>
+        <v>6981368</v>
       </c>
       <c r="S30" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3880,7 +3893,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3890,7 +3903,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3899,29 +3912,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132623272</v>
+        <v>132623266</v>
       </c>
       <c r="B31" t="n">
-        <v>101338</v>
+        <v>97989</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3929,45 +3941,33 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>221944</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>672787</v>
+        <v>672878</v>
       </c>
       <c r="R31" t="n">
-        <v>6981316</v>
+        <v>6981334</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4141,10 +4141,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132617596</v>
+        <v>132617586</v>
       </c>
       <c r="B33" t="n">
-        <v>97995</v>
+        <v>91881</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4152,21 +4152,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4176,10 +4176,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>672810</v>
+        <v>672660</v>
       </c>
       <c r="R33" t="n">
-        <v>6981546</v>
+        <v>6981395</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4248,42 +4248,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132623274</v>
+        <v>132617582</v>
       </c>
       <c r="B34" t="n">
-        <v>101338</v>
+        <v>57955</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4291,13 +4291,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>672744</v>
+        <v>672612</v>
       </c>
       <c r="R34" t="n">
-        <v>6981271</v>
+        <v>6981238</v>
       </c>
       <c r="S34" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4345,29 +4345,28 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132617586</v>
+        <v>132617596</v>
       </c>
       <c r="B35" t="n">
-        <v>91881</v>
+        <v>97995</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4375,21 +4374,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4399,10 +4398,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>672660</v>
+        <v>672810</v>
       </c>
       <c r="R35" t="n">
-        <v>6981395</v>
+        <v>6981546</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -4434,7 +4433,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4444,7 +4443,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4471,42 +4470,42 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132617582</v>
+        <v>132623274</v>
       </c>
       <c r="B36" t="n">
-        <v>57955</v>
+        <v>101338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4514,13 +4513,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>672612</v>
+        <v>672744</v>
       </c>
       <c r="R36" t="n">
-        <v>6981238</v>
+        <v>6981271</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4549,7 +4548,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4559,7 +4558,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4568,18 +4567,19 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4702,32 +4702,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132617564</v>
+        <v>132623290</v>
       </c>
       <c r="B38" t="n">
-        <v>80438</v>
+        <v>97995</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4737,13 +4737,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672831</v>
+        <v>672621</v>
       </c>
       <c r="R38" t="n">
-        <v>6981363</v>
+        <v>6981383</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4797,57 +4797,60 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132617599</v>
+        <v>132617557</v>
       </c>
       <c r="B39" t="n">
-        <v>79333</v>
+        <v>80398</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>672664</v>
+        <v>672878</v>
       </c>
       <c r="R39" t="n">
-        <v>6981552</v>
+        <v>6981324</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4879,7 +4882,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4889,7 +4892,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4898,8 +4901,24 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4916,32 +4935,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132623290</v>
+        <v>132617599</v>
       </c>
       <c r="B40" t="n">
-        <v>97995</v>
+        <v>79333</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4951,13 +4970,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672621</v>
+        <v>672664</v>
       </c>
       <c r="R40" t="n">
-        <v>6981383</v>
+        <v>6981552</v>
       </c>
       <c r="S40" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4986,7 +5005,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4996,7 +5015,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5011,60 +5030,57 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132617557</v>
+        <v>132617564</v>
       </c>
       <c r="B41" t="n">
-        <v>80398</v>
+        <v>80438</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>672878</v>
+        <v>672831</v>
       </c>
       <c r="R41" t="n">
-        <v>6981324</v>
+        <v>6981363</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -5096,7 +5112,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5106,7 +5122,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5115,24 +5131,8 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5149,51 +5149,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132617607</v>
+        <v>132617558</v>
       </c>
       <c r="B42" t="n">
-        <v>79333</v>
+        <v>80311</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>672712</v>
+        <v>672873</v>
       </c>
       <c r="R42" t="n">
-        <v>6981164</v>
+        <v>6981339</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5222,7 +5219,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5232,7 +5229,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5241,24 +5238,8 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5275,42 +5256,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132623256</v>
+        <v>132617607</v>
       </c>
       <c r="B43" t="n">
-        <v>101338</v>
+        <v>79333</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5318,13 +5294,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672930</v>
+        <v>672712</v>
       </c>
       <c r="R43" t="n">
-        <v>6981133</v>
+        <v>6981164</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5353,7 +5329,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5363,7 +5339,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5376,63 +5352,86 @@
       <c r="AG43" t="b">
         <v>0</v>
       </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132617558</v>
+        <v>132623256</v>
       </c>
       <c r="B44" t="n">
-        <v>80311</v>
+        <v>101338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>392</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672873</v>
+        <v>672930</v>
       </c>
       <c r="R44" t="n">
-        <v>6981339</v>
+        <v>6981133</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5461,7 +5460,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5471,7 +5470,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5480,18 +5479,19 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5605,42 +5605,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132623254</v>
+        <v>132617567</v>
       </c>
       <c r="B46" t="n">
-        <v>101338</v>
+        <v>80438</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5648,13 +5643,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>672976</v>
+        <v>672776</v>
       </c>
       <c r="R46" t="n">
-        <v>6981122</v>
+        <v>6981332</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5683,7 +5678,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5693,7 +5688,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5706,57 +5701,72 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132623294</v>
+        <v>132617576</v>
       </c>
       <c r="B47" t="n">
-        <v>101338</v>
+        <v>57958</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5764,13 +5774,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>672601</v>
+        <v>672684</v>
       </c>
       <c r="R47" t="n">
-        <v>6981439</v>
+        <v>6981289</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5799,7 +5809,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5809,7 +5819,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5818,26 +5833,25 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132623300</v>
+        <v>132623254</v>
       </c>
       <c r="B48" t="n">
         <v>101338</v>
@@ -5880,13 +5894,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>672758</v>
+        <v>672976</v>
       </c>
       <c r="R48" t="n">
-        <v>6981513</v>
+        <v>6981122</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5915,7 +5929,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5925,7 +5939,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5953,7 +5967,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132617546</v>
+        <v>132623294</v>
       </c>
       <c r="B49" t="n">
         <v>101338</v>
@@ -5982,19 +5996,27 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672949</v>
+        <v>672601</v>
       </c>
       <c r="R49" t="n">
-        <v>6981130</v>
+        <v>6981439</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6023,7 +6045,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6033,7 +6055,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6042,55 +6064,61 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132617567</v>
+        <v>132623300</v>
       </c>
       <c r="B50" t="n">
-        <v>80438</v>
+        <v>101338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6098,13 +6126,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>672776</v>
+        <v>672758</v>
       </c>
       <c r="R50" t="n">
-        <v>6981332</v>
+        <v>6981513</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6133,7 +6161,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6143,7 +6171,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6156,83 +6184,60 @@
       <c r="AG50" t="b">
         <v>0</v>
       </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132617576</v>
+        <v>132617546</v>
       </c>
       <c r="B51" t="n">
-        <v>57958</v>
+        <v>101338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672684</v>
+        <v>672949</v>
       </c>
       <c r="R51" t="n">
-        <v>6981289</v>
+        <v>6981130</v>
       </c>
       <c r="S51" t="n">
         <v>3</v>
@@ -6264,7 +6269,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6274,12 +6279,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6306,46 +6306,41 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132617589</v>
+        <v>132617595</v>
       </c>
       <c r="B52" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6353,13 +6348,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672627</v>
+        <v>672745</v>
       </c>
       <c r="R52" t="n">
-        <v>6981425</v>
+        <v>6981544</v>
       </c>
       <c r="S52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6388,7 +6383,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6398,7 +6393,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6426,56 +6421,68 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132623292</v>
+        <v>132617603</v>
       </c>
       <c r="B53" t="n">
-        <v>101338</v>
+        <v>57958</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Edsätter, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>672655</v>
+        <v>672617</v>
       </c>
       <c r="R53" t="n">
-        <v>6981418</v>
+        <v>6981488</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6504,7 +6511,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6514,7 +6521,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6523,29 +6530,28 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132617566</v>
+        <v>132623292</v>
       </c>
       <c r="B54" t="n">
-        <v>80398</v>
+        <v>101338</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6553,26 +6559,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6580,13 +6591,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672774</v>
+        <v>672655</v>
       </c>
       <c r="R54" t="n">
-        <v>6981334</v>
+        <v>6981418</v>
       </c>
       <c r="S54" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6615,7 +6626,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6625,7 +6636,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6638,71 +6649,52 @@
       <c r="AG54" t="b">
         <v>0</v>
       </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132617595</v>
+        <v>132617566</v>
       </c>
       <c r="B55" t="n">
-        <v>79333</v>
+        <v>80398</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6710,13 +6702,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672745</v>
+        <v>672774</v>
       </c>
       <c r="R55" t="n">
-        <v>6981544</v>
+        <v>6981334</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6745,7 +6737,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6755,7 +6747,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6767,6 +6759,21 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6783,65 +6790,57 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132617603</v>
+        <v>132617589</v>
       </c>
       <c r="B56" t="n">
-        <v>57958</v>
+        <v>99130</v>
    